--- a/बजेट माग estimate/नगर बजेट estimate/तल्लो नंग्लेद्वारे चिहानपाटी/V-devithaan.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/तल्लो नंग्लेद्वारे चिहानपाटी/V-devithaan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3946A2BC-13CD-4013-9918-6E2AB497E011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A8E425-C59D-47CC-835F-E70F2E3528E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$103</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">V!$A$1:$K$111</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">WCR!$A$1:$K$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">WCR!$A$1:$K$49</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">V!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">WCR!$1:$12</definedName>
@@ -749,88 +749,12 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -877,6 +801,82 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1142,247 +1142,12 @@
             <v>-13% VAT for excavator</v>
           </cell>
         </row>
-        <row r="14">
-          <cell r="A14">
-            <v>2</v>
-          </cell>
-          <cell r="B14" t="str">
-            <v>Providing and laying of hand pack locally available Stone soling with 150 to 200 mm thick stones and packing with smaller stone on prepared surface as per Drawing and Technical Specifications.</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="G16">
-            <v>25.601950624809511</v>
-          </cell>
-          <cell r="H16" t="str">
-            <v>cum</v>
-          </cell>
-          <cell r="I16">
-            <v>4458.5200000000004</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="B17" t="str">
-            <v>-13% VAT for block stone</v>
-          </cell>
-          <cell r="J17">
-            <v>9863.3460530326138</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19">
-            <v>3</v>
-          </cell>
-          <cell r="B19" t="str">
-            <v>Providing and laying of Plain/Reinforced Cement Concrete in Foundation complete as per Drawing and Technical Specifications., RCC Grade M 20</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="G21">
-            <v>25.601950624809511</v>
-          </cell>
-          <cell r="H21" t="str">
-            <v>cum</v>
-          </cell>
-          <cell r="I21">
-            <v>12000.5</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22" t="str">
-            <v>-13% VAT for cement</v>
-          </cell>
-          <cell r="J22">
-            <v>15064.010752819264</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23" t="str">
-            <v>-13% VAT for sand</v>
-          </cell>
-          <cell r="J23">
-            <v>4755.5418469978658</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="B24" t="str">
-            <v>-13% VAT for aggregate</v>
-          </cell>
-          <cell r="J24">
-            <v>9828.1198171289252</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="B25" t="str">
-            <v>-13% VAT for water</v>
-          </cell>
-          <cell r="J25">
-            <v>171.95976836330388</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="B26" t="str">
-            <v>-13% VAT for formwork</v>
-          </cell>
-          <cell r="J26">
-            <v>1536.18872295032</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28">
-            <v>4</v>
-          </cell>
-          <cell r="B28" t="str">
-            <v xml:space="preserve">Providing and laying , fitting and placing HYSD bar reinforcement in sub-structure complete as per Drawing and Technical Specifications and instruction of site engineer  </v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="G31">
-            <v>0.69012345679012344</v>
-          </cell>
-          <cell r="H31" t="str">
-            <v>tonne</v>
-          </cell>
-          <cell r="I31">
-            <v>124355</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="B32" t="str">
-            <v>-13% VAT for HYSD bar</v>
-          </cell>
-          <cell r="J32">
-            <v>9868.7654320987658</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="B33" t="str">
-            <v>-13% VAT for binding wire</v>
-          </cell>
-          <cell r="J33">
-            <v>86.127407407407404</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35">
-            <v>5</v>
-          </cell>
-          <cell r="B35" t="str">
-            <v>Provisional sum for lab tests</v>
-          </cell>
-          <cell r="G35">
-            <v>1</v>
-          </cell>
-          <cell r="H35" t="str">
-            <v>PS</v>
-          </cell>
-          <cell r="I35">
-            <v>5000</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37">
-            <v>6</v>
-          </cell>
-          <cell r="B37" t="str">
-            <v>Information board (सुचना पाटि)</v>
-          </cell>
-          <cell r="G37">
-            <v>1</v>
-          </cell>
-          <cell r="H37" t="str">
-            <v>no.</v>
-          </cell>
-          <cell r="I37">
-            <v>500</v>
-          </cell>
-        </row>
       </sheetData>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="26">
           <cell r="G26">
             <v>22.511609090584113</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="G46">
-            <v>19.640222480358585</v>
-          </cell>
-          <cell r="I46">
-            <v>4458.5200000000004</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="J47">
-            <v>7566.544976248997</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="G66">
-            <v>27.673017548078754</v>
-          </cell>
-          <cell r="I66">
-            <v>12000.5</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="J67">
-            <v>16282.612212494889</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="J68">
-            <v>5140.2408711415901</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="J69">
-            <v>10623.164467025954</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="J70">
-            <v>185.8704345312623</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="J71">
-            <v>1660.4585373338598</v>
-          </cell>
-        </row>
-        <row r="102">
-          <cell r="G102">
-            <v>0.7214972839506173</v>
-          </cell>
-          <cell r="I102">
-            <v>124355</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="J103">
-            <v>10317.411160493828</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="J104">
-            <v>90.042861037037042</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="G106">
-            <v>1</v>
-          </cell>
-          <cell r="I106">
-            <v>5000</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="G108">
-            <v>1</v>
-          </cell>
-          <cell r="I108">
-            <v>500</v>
           </cell>
         </row>
       </sheetData>
@@ -1698,113 +1463,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
     </row>
     <row r="2" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
     </row>
     <row r="5" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
+      <c r="K5" s="78"/>
     </row>
     <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="48" t="s">
+      <c r="H6" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
+      <c r="B7" s="70"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="56" t="s">
+      <c r="H7" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -3901,11 +3666,11 @@
       <c r="B98" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C98" s="53">
+      <c r="C98" s="68">
         <f>J96</f>
         <v>786973.54597297299</v>
       </c>
-      <c r="D98" s="54"/>
+      <c r="D98" s="69"/>
       <c r="E98" s="9">
         <v>100</v>
       </c>
@@ -3927,21 +3692,21 @@
       <c r="B99" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C99" s="57">
+      <c r="C99" s="72">
         <v>700000</v>
       </c>
-      <c r="D99" s="58"/>
+      <c r="D99" s="73"/>
       <c r="E99" s="9"/>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B100" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C100" s="57">
+      <c r="C100" s="72">
         <f>C99-C102-C103</f>
         <v>665000</v>
       </c>
-      <c r="D100" s="58"/>
+      <c r="D100" s="73"/>
       <c r="E100" s="9">
         <f>C100/C98*100</f>
         <v>84.500934421858958</v>
@@ -3951,11 +3716,11 @@
       <c r="B101" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C101" s="59">
+      <c r="C101" s="74">
         <f>C98-C100</f>
         <v>121973.54597297299</v>
       </c>
-      <c r="D101" s="59"/>
+      <c r="D101" s="74"/>
       <c r="E101" s="9">
         <f>100-E100</f>
         <v>15.499065578141042</v>
@@ -3965,11 +3730,11 @@
       <c r="B102" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C102" s="53">
+      <c r="C102" s="68">
         <f>C99*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D102" s="54"/>
+      <c r="D102" s="69"/>
       <c r="E102" s="9">
         <v>3</v>
       </c>
@@ -3978,17 +3743,24 @@
       <c r="B103" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C103" s="53">
+      <c r="C103" s="68">
         <f>C99*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D103" s="54"/>
+      <c r="D103" s="69"/>
       <c r="E103" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C102:D102"/>
     <mergeCell ref="C103:D103"/>
     <mergeCell ref="A7:F7"/>
@@ -3997,13 +3769,6 @@
     <mergeCell ref="C99:D99"/>
     <mergeCell ref="C100:D100"/>
     <mergeCell ref="C101:D101"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -4015,7 +3780,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C7C7C3A-4B53-4873-A254-2981ED93CBDA}">
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.28515625" customWidth="1"/>
@@ -4033,203 +3798,203 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
-      <c r="K1" s="60"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
+      <c r="G1" s="88"/>
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="88"/>
+      <c r="K1" s="88"/>
     </row>
     <row r="2" spans="1:13" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="89" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-      <c r="J2" s="61"/>
-      <c r="K2" s="61"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
     </row>
     <row r="3" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="90" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
-      <c r="I3" s="62"/>
-      <c r="J3" s="62"/>
-      <c r="K3" s="62"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="90"/>
+      <c r="D3" s="90"/>
+      <c r="E3" s="90"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="90"/>
+      <c r="H3" s="90"/>
+      <c r="I3" s="90"/>
+      <c r="J3" s="90"/>
+      <c r="K3" s="90"/>
     </row>
     <row r="4" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="62" t="s">
+      <c r="A4" s="90" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="62"/>
-      <c r="C4" s="62"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="62"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="90"/>
+      <c r="I4" s="90"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="90"/>
     </row>
     <row r="5" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="91" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="63"/>
-      <c r="C5" s="63"/>
-      <c r="D5" s="63"/>
-      <c r="E5" s="63"/>
-      <c r="F5" s="63"/>
-      <c r="G5" s="63"/>
-      <c r="H5" s="63"/>
-      <c r="I5" s="63"/>
-      <c r="J5" s="63"/>
-      <c r="K5" s="63"/>
+      <c r="B5" s="91"/>
+      <c r="C5" s="91"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="91"/>
+      <c r="F5" s="91"/>
+      <c r="G5" s="91"/>
+      <c r="H5" s="91"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="91"/>
+      <c r="K5" s="91"/>
     </row>
     <row r="6" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="65">
-        <f>F34</f>
-        <v>720242.30001415103</v>
-      </c>
-      <c r="D6" s="66"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64" t="s">
+      <c r="B6" s="47"/>
+      <c r="C6" s="92">
+        <f>F49</f>
+        <v>786973.54597297299</v>
+      </c>
+      <c r="D6" s="93"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="I6" s="64"/>
-      <c r="J6" s="65">
-        <f>I34</f>
-        <v>744767.80140564521</v>
-      </c>
-      <c r="K6" s="66"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="92">
+        <f>I49</f>
+        <v>803383.79487942101</v>
+      </c>
+      <c r="K6" s="93"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="68" t="s">
+      <c r="A7" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="F7" s="69"/>
-      <c r="G7" s="69"/>
-      <c r="I7" s="70" t="s">
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="I7" s="85" t="s">
         <v>87</v>
       </c>
-      <c r="J7" s="70"/>
-      <c r="K7" s="70"/>
+      <c r="J7" s="85"/>
+      <c r="K7" s="85"/>
     </row>
     <row r="8" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="47" t="str">
+      <c r="A8" s="79" t="str">
         <f>estimate!A6</f>
         <v xml:space="preserve">Project:- तल्लो नाङ्गलेद्वारे चिहानपाटी </v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="47"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="47"/>
-      <c r="I8" s="71" t="s">
+      <c r="B8" s="79"/>
+      <c r="C8" s="79"/>
+      <c r="D8" s="79"/>
+      <c r="E8" s="79"/>
+      <c r="F8" s="79"/>
+      <c r="I8" s="86" t="s">
         <v>88</v>
       </c>
-      <c r="J8" s="71"/>
-      <c r="K8" s="71"/>
+      <c r="J8" s="86"/>
+      <c r="K8" s="86"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="72" t="s">
+      <c r="A9" s="87" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="72"/>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="I9" s="71" t="s">
+      <c r="B9" s="87"/>
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="I9" s="86" t="s">
         <v>89</v>
       </c>
-      <c r="J9" s="71"/>
-      <c r="K9" s="71"/>
+      <c r="J9" s="86"/>
+      <c r="K9" s="86"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="73" t="s">
+      <c r="A11" s="82" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="73" t="s">
+      <c r="B11" s="82" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="73" t="s">
+      <c r="C11" s="82" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="74" t="s">
+      <c r="D11" s="83" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74" t="s">
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="73" t="s">
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="82" t="s">
         <v>94</v>
       </c>
-      <c r="K11" s="75" t="s">
+      <c r="K11" s="81" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="73"/>
-      <c r="B12" s="73"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="76" t="s">
+      <c r="A12" s="82"/>
+      <c r="B12" s="82"/>
+      <c r="C12" s="82"/>
+      <c r="D12" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="76" t="s">
+      <c r="E12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="F12" s="76" t="s">
+      <c r="F12" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="G12" s="76" t="s">
+      <c r="G12" s="50" t="s">
         <v>96</v>
       </c>
-      <c r="H12" s="76" t="s">
+      <c r="H12" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="76" t="s">
+      <c r="I12" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="73"/>
-      <c r="K12" s="75"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="81"/>
     </row>
     <row r="13" spans="1:13" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="77">
+      <c r="A13" s="51">
         <f>estimate!A9</f>
         <v>1</v>
       </c>
@@ -4237,620 +4002,1047 @@
         <f>estimate!B9</f>
         <v>sfnf] kmnfd] kfO{ksf] 6«; agfO{ h8fg ug]{ sfd</v>
       </c>
-      <c r="C13" s="78" t="str">
+      <c r="C13" s="52" t="str">
         <f>estimate!H25</f>
         <v>Kg</v>
       </c>
-      <c r="D13" s="78">
+      <c r="D13" s="52">
         <f>estimate!G25</f>
         <v>800.41415726912533</v>
       </c>
-      <c r="E13" s="78">
+      <c r="E13" s="52">
         <f>estimate!I25</f>
         <v>182.51</v>
       </c>
-      <c r="F13" s="78">
+      <c r="F13" s="52">
         <f>D13*E13</f>
         <v>146083.58784318806</v>
       </c>
-      <c r="G13" s="78">
+      <c r="G13" s="52">
         <f>V!G32</f>
-        <v>911.28087270141191</v>
-      </c>
-      <c r="H13" s="78">
+        <v>880.06056639235987</v>
+      </c>
+      <c r="H13" s="52">
         <f>V!I32</f>
         <v>182.51</v>
       </c>
-      <c r="I13" s="78">
+      <c r="I13" s="52">
         <f>G13*H13</f>
-        <v>166317.87207673467</v>
-      </c>
-      <c r="J13" s="79">
+        <v>160619.8539722696</v>
+      </c>
+      <c r="J13" s="53">
         <f>I13-F13</f>
-        <v>20234.284233546612</v>
-      </c>
-      <c r="K13" s="80"/>
+        <v>14536.266129081545</v>
+      </c>
+      <c r="K13" s="54"/>
       <c r="M13" s="36">
         <f>1.25*F13</f>
         <v>182604.48480398508</v>
       </c>
     </row>
     <row r="14" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="77"/>
-      <c r="B14" s="81" t="str">
+      <c r="A14" s="51"/>
+      <c r="B14" s="55" t="str">
         <f>[4]estimate!B12</f>
         <v>-13% VAT for excavator</v>
       </c>
-      <c r="C14" s="78"/>
-      <c r="D14" s="78"/>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78">
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52">
         <f>estimate!J26</f>
         <v>10281.332528276465</v>
       </c>
-      <c r="G14" s="78"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="78">
+      <c r="G14" s="52"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52">
         <f>V!J33</f>
-        <v>11705.417244076765</v>
-      </c>
-      <c r="J14" s="79">
+        <v>11304.391915023165</v>
+      </c>
+      <c r="J14" s="53">
         <f>I14-F14</f>
-        <v>1424.0847158002998</v>
-      </c>
-      <c r="K14" s="80"/>
+        <v>1023.0593867466996</v>
+      </c>
+      <c r="K14" s="54"/>
       <c r="M14" s="36">
         <f t="shared" ref="M14" si="0">1.25*F14</f>
         <v>12851.665660345581</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="82"/>
-      <c r="B15" s="83"/>
-      <c r="C15" s="78"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="78"/>
-      <c r="J15" s="79"/>
-      <c r="K15" s="80"/>
-    </row>
-    <row r="16" spans="1:13" s="36" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="77">
-        <f>[4]estimate!A14</f>
+      <c r="A15" s="56"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="52"/>
+      <c r="I15" s="52"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="54"/>
+    </row>
+    <row r="16" spans="1:13" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="51">
+        <f>estimate!A28</f>
         <v>2</v>
       </c>
-      <c r="B16" s="84" t="str">
-        <f>[4]estimate!B14</f>
-        <v>Providing and laying of hand pack locally available Stone soling with 150 to 200 mm thick stones and packing with smaller stone on prepared surface as per Drawing and Technical Specifications.</v>
-      </c>
-      <c r="C16" s="78" t="str">
-        <f>[4]estimate!H16</f>
-        <v>cum</v>
-      </c>
-      <c r="D16" s="78">
-        <f>[4]estimate!G16</f>
-        <v>25.601950624809511</v>
-      </c>
-      <c r="E16" s="78">
-        <f>[4]estimate!I16</f>
-        <v>4458.5200000000004</v>
-      </c>
-      <c r="F16" s="78">
+      <c r="B16" s="39" t="str">
+        <f>estimate!B28</f>
+        <v>)=$! dL=dL=afSnf] sf]?u]6]8 /+lug ss{6 kftfsf] 5fgf 5fpg] sfd</v>
+      </c>
+      <c r="C16" s="52" t="str">
+        <f>estimate!H31</f>
+        <v>sqm</v>
+      </c>
+      <c r="D16" s="52">
+        <f>estimate!G31</f>
+        <v>31.907480203597579</v>
+      </c>
+      <c r="E16" s="52">
+        <f>estimate!I31</f>
+        <v>1112.58</v>
+      </c>
+      <c r="F16" s="52">
         <f>D16*E16</f>
-        <v>114146.80889972571</v>
-      </c>
-      <c r="G16" s="78">
-        <f>[4]V!G46</f>
-        <v>19.640222480358585</v>
-      </c>
-      <c r="H16" s="78">
-        <f>[4]V!I46</f>
-        <v>4458.5200000000004</v>
-      </c>
-      <c r="I16" s="78">
+        <v>35499.624324918594</v>
+      </c>
+      <c r="G16" s="52">
+        <f>V!G38</f>
+        <v>32.154877291241462</v>
+      </c>
+      <c r="H16" s="52">
+        <f>V!I38</f>
+        <v>1112.58</v>
+      </c>
+      <c r="I16" s="52">
         <f>G16*H16</f>
-        <v>87566.324733128364</v>
-      </c>
-      <c r="J16" s="79">
+        <v>35774.873376689422</v>
+      </c>
+      <c r="J16" s="53">
         <f>I16-F16</f>
-        <v>-26580.484166597351</v>
-      </c>
-      <c r="K16" s="80"/>
+        <v>275.24905177082837</v>
+      </c>
+      <c r="K16" s="54"/>
       <c r="M16" s="36">
-        <f t="shared" ref="M16:M30" si="1">1.25*F16</f>
-        <v>142683.51112465715</v>
+        <f t="shared" ref="M16:M44" si="1">1.25*F16</f>
+        <v>44374.530406148246</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="77"/>
-      <c r="B17" s="81" t="str">
-        <f>[4]estimate!B17</f>
-        <v>-13% VAT for block stone</v>
-      </c>
-      <c r="C17" s="78"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78">
-        <f>[4]estimate!J17</f>
-        <v>9863.3460530326138</v>
-      </c>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="78">
-        <f>[4]V!J47</f>
-        <v>7566.544976248997</v>
-      </c>
-      <c r="J17" s="79">
+      <c r="A17" s="51"/>
+      <c r="B17" s="55" t="str">
+        <f>estimate!B32</f>
+        <v>-13% VAT for sheet</v>
+      </c>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52">
+        <f>estimate!J32</f>
+        <v>2924.5984748122914</v>
+      </c>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52">
+        <f>V!J39</f>
+        <v>2947.2745727234869</v>
+      </c>
+      <c r="J17" s="53">
         <f>I17-F17</f>
-        <v>-2296.8010767836167</v>
-      </c>
-      <c r="K17" s="80"/>
+        <v>22.676097911195484</v>
+      </c>
+      <c r="K17" s="54"/>
       <c r="M17" s="36">
         <f t="shared" si="1"/>
-        <v>12329.182566290767</v>
+        <v>3655.7480935153644</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="77"/>
-      <c r="B18" s="84"/>
-      <c r="C18" s="78"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="79"/>
-      <c r="K18" s="80"/>
-    </row>
-    <row r="19" spans="1:13" s="36" customFormat="1" ht="63" x14ac:dyDescent="0.25">
-      <c r="A19" s="77">
-        <f>[4]estimate!A19</f>
+      <c r="A18" s="51"/>
+      <c r="B18" s="55" t="str">
+        <f>estimate!B33</f>
+        <v>-13% VAT for nut bolt</v>
+      </c>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52">
+        <f>estimate!J33</f>
+        <v>424.6486771596293</v>
+      </c>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52">
+        <f>V!J40</f>
+        <v>427.94122314980984</v>
+      </c>
+      <c r="J18" s="53">
+        <f t="shared" ref="J18:J20" si="2">I18-F18</f>
+        <v>3.2925459901805425</v>
+      </c>
+      <c r="K18" s="54"/>
+    </row>
+    <row r="19" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="51"/>
+      <c r="B19" s="55" t="str">
+        <f>estimate!B34</f>
+        <v>-13% VAT for j-hook</v>
+      </c>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52">
+        <f>estimate!J34</f>
+        <v>144.43654786203126</v>
+      </c>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52">
+        <f>V!J41</f>
+        <v>145.55644768058147</v>
+      </c>
+      <c r="J19" s="53">
+        <f t="shared" si="2"/>
+        <v>1.1198998185502091</v>
+      </c>
+      <c r="K19" s="54"/>
+    </row>
+    <row r="20" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="51"/>
+      <c r="B20" s="55" t="str">
+        <f>estimate!B35</f>
+        <v>-13% VAT for bitumen washer</v>
+      </c>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52">
+        <f>estimate!J35</f>
+        <v>68.441545036716803</v>
+      </c>
+      <c r="G20" s="52"/>
+      <c r="H20" s="52"/>
+      <c r="I20" s="52">
+        <f>V!J42</f>
+        <v>68.972211789712929</v>
+      </c>
+      <c r="J20" s="53">
+        <f t="shared" si="2"/>
+        <v>0.53066675299612598</v>
+      </c>
+      <c r="K20" s="54"/>
+    </row>
+    <row r="21" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="51"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="53"/>
+      <c r="K21" s="54"/>
+    </row>
+    <row r="22" spans="1:13" s="36" customFormat="1" ht="63" x14ac:dyDescent="0.25">
+      <c r="A22" s="51">
+        <f>estimate!A37</f>
         <v>3</v>
       </c>
-      <c r="B19" s="84" t="str">
-        <f>[4]estimate!B19</f>
-        <v>Providing and laying of Plain/Reinforced Cement Concrete in Foundation complete as per Drawing and Technical Specifications., RCC Grade M 20</v>
-      </c>
-      <c r="C19" s="78" t="str">
-        <f>[4]estimate!H21</f>
+      <c r="B22" s="58" t="str">
+        <f>estimate!B37</f>
+        <v>Earthwork Excavation in Cutting., Roadway Excavation in all types of Soil by Mechanical  Means ., Road way Excavation in  all types of soil as per Drawing and technical specifications  including  removal of stumps and other deleterious matter, all lifts and lead as per Drawing and instruction of the Engineer.</v>
+      </c>
+      <c r="C22" s="52" t="str">
+        <f>estimate!H43</f>
         <v>cum</v>
       </c>
-      <c r="D19" s="78">
-        <f>[4]estimate!G21</f>
-        <v>25.601950624809511</v>
-      </c>
-      <c r="E19" s="78">
-        <f>[4]estimate!I21</f>
-        <v>12000.5</v>
-      </c>
-      <c r="F19" s="78">
-        <f>D19*E19</f>
-        <v>307236.20847302652</v>
-      </c>
-      <c r="G19" s="78">
-        <f>[4]V!G66</f>
-        <v>27.673017548078754</v>
-      </c>
-      <c r="H19" s="78">
-        <f>[4]V!I66</f>
-        <v>12000.5</v>
-      </c>
-      <c r="I19" s="78">
-        <f>G19*H19</f>
-        <v>332090.04708571907</v>
-      </c>
-      <c r="J19" s="79">
-        <f>I19-F19</f>
-        <v>24853.838612692547</v>
-      </c>
-      <c r="K19" s="80"/>
-      <c r="M19" s="36">
+      <c r="D22" s="52">
+        <f>estimate!G43</f>
+        <v>23.190224931423352</v>
+      </c>
+      <c r="E22" s="52">
+        <f>estimate!I43</f>
+        <v>62.95</v>
+      </c>
+      <c r="F22" s="52">
+        <f>D22*E22</f>
+        <v>1459.8246594331001</v>
+      </c>
+      <c r="G22" s="52">
+        <f>V!G50</f>
+        <v>23.338318500457184</v>
+      </c>
+      <c r="H22" s="52">
+        <f>V!I50</f>
+        <v>62.95</v>
+      </c>
+      <c r="I22" s="52">
+        <f>G22*H22</f>
+        <v>1469.1471496037798</v>
+      </c>
+      <c r="J22" s="53">
+        <f>I22-F22</f>
+        <v>9.3224901706796572</v>
+      </c>
+      <c r="K22" s="54"/>
+      <c r="M22" s="36">
         <f t="shared" si="1"/>
-        <v>384045.26059128315</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="77"/>
-      <c r="B20" s="81" t="str">
-        <f>[4]estimate!B22</f>
-        <v>-13% VAT for cement</v>
-      </c>
-      <c r="C20" s="78"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="78"/>
-      <c r="F20" s="78">
-        <f>[4]estimate!J22</f>
-        <v>15064.010752819264</v>
-      </c>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="78">
-        <f>[4]V!J67</f>
-        <v>16282.612212494889</v>
-      </c>
-      <c r="J20" s="79">
-        <f>I20-F20</f>
-        <v>1218.6014596756249</v>
-      </c>
-      <c r="K20" s="80"/>
-      <c r="M20" s="36">
+        <v>1824.7808242913752</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="51"/>
+      <c r="B23" s="55" t="str">
+        <f>estimate!B44</f>
+        <v>-13% VAT for excavator</v>
+      </c>
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52">
+        <f>estimate!J44</f>
+        <v>155.86150176409637</v>
+      </c>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52">
+        <f>V!J51</f>
+        <v>156.85683864157275</v>
+      </c>
+      <c r="J23" s="53">
+        <f>I23-F23</f>
+        <v>0.995336877476376</v>
+      </c>
+      <c r="K23" s="54"/>
+      <c r="M23" s="36">
         <f t="shared" si="1"/>
-        <v>18830.013441024079</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="77"/>
-      <c r="B21" s="81" t="str">
-        <f>[4]estimate!B23</f>
-        <v>-13% VAT for sand</v>
-      </c>
-      <c r="C21" s="78"/>
-      <c r="D21" s="78"/>
-      <c r="E21" s="78"/>
-      <c r="F21" s="78">
-        <f>[4]estimate!J23</f>
-        <v>4755.5418469978658</v>
-      </c>
-      <c r="G21" s="78"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="78">
-        <f>[4]V!J68</f>
-        <v>5140.2408711415901</v>
-      </c>
-      <c r="J21" s="79">
-        <f t="shared" ref="J21:J24" si="2">I21-F21</f>
-        <v>384.69902414372427</v>
-      </c>
-      <c r="K21" s="80"/>
-    </row>
-    <row r="22" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="77"/>
-      <c r="B22" s="81" t="str">
-        <f>[4]estimate!B24</f>
-        <v>-13% VAT for aggregate</v>
-      </c>
-      <c r="C22" s="78"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="78">
-        <f>[4]estimate!J24</f>
-        <v>9828.1198171289252</v>
-      </c>
-      <c r="G22" s="78"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="78">
-        <f>[4]V!J69</f>
-        <v>10623.164467025954</v>
-      </c>
-      <c r="J22" s="79">
-        <f t="shared" si="2"/>
-        <v>795.04464989702865</v>
-      </c>
-      <c r="K22" s="80"/>
-    </row>
-    <row r="23" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="77"/>
-      <c r="B23" s="81" t="str">
-        <f>[4]estimate!B25</f>
-        <v>-13% VAT for water</v>
-      </c>
-      <c r="C23" s="78"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78">
-        <f>[4]estimate!J25</f>
-        <v>171.95976836330388</v>
-      </c>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78">
-        <f>[4]V!J70</f>
-        <v>185.8704345312623</v>
-      </c>
-      <c r="J23" s="79">
-        <f t="shared" si="2"/>
-        <v>13.910666167958425</v>
-      </c>
-      <c r="K23" s="80"/>
-    </row>
-    <row r="24" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="77"/>
-      <c r="B24" s="81" t="str">
-        <f>[4]estimate!B26</f>
-        <v>-13% VAT for formwork</v>
-      </c>
-      <c r="C24" s="78"/>
-      <c r="D24" s="78"/>
-      <c r="E24" s="78"/>
-      <c r="F24" s="78">
-        <f>[4]estimate!J26</f>
-        <v>1536.18872295032</v>
-      </c>
-      <c r="G24" s="78"/>
-      <c r="H24" s="78"/>
-      <c r="I24" s="78">
-        <f>[4]V!J71</f>
-        <v>1660.4585373338598</v>
-      </c>
-      <c r="J24" s="79">
-        <f t="shared" si="2"/>
-        <v>124.26981438353982</v>
-      </c>
-      <c r="K24" s="80"/>
-    </row>
-    <row r="25" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="82"/>
-      <c r="B25" s="83"/>
-      <c r="C25" s="78"/>
-      <c r="D25" s="78"/>
-      <c r="E25" s="78"/>
-      <c r="F25" s="78"/>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
-      <c r="I25" s="78"/>
-      <c r="J25" s="79"/>
-      <c r="K25" s="80"/>
-    </row>
-    <row r="26" spans="1:13" s="36" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="77">
-        <f>[4]estimate!A28</f>
+        <v>194.82687720512047</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="56"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="53"/>
+      <c r="K24" s="54"/>
+    </row>
+    <row r="25" spans="1:13" s="36" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="51">
+        <f>estimate!A46</f>
         <v>4</v>
       </c>
-      <c r="B26" s="84" t="str">
-        <f>[4]estimate!B28</f>
-        <v xml:space="preserve">Providing and laying , fitting and placing HYSD bar reinforcement in sub-structure complete as per Drawing and Technical Specifications and instruction of site engineer  </v>
-      </c>
-      <c r="C26" s="78" t="str">
-        <f>[4]estimate!H31</f>
-        <v>tonne</v>
-      </c>
-      <c r="D26" s="78">
-        <f>[4]estimate!G31</f>
-        <v>0.69012345679012344</v>
-      </c>
-      <c r="E26" s="78">
-        <f>[4]estimate!I31</f>
-        <v>124355</v>
-      </c>
-      <c r="F26" s="78">
-        <f>D26*E26</f>
-        <v>85820.3024691358</v>
-      </c>
-      <c r="G26" s="78">
-        <f>[4]V!G102</f>
-        <v>0.7214972839506173</v>
-      </c>
-      <c r="H26" s="78">
-        <f>[4]V!I102</f>
-        <v>124355</v>
-      </c>
-      <c r="I26" s="78">
-        <f>G26*H26</f>
-        <v>89721.794745679013</v>
-      </c>
-      <c r="J26" s="79">
+      <c r="B25" s="58" t="str">
+        <f>estimate!B46</f>
+        <v>Providing and laying of hand pack locally available Stone soling with 150 to 200 mm thick stones and packing with smaller stone on prepared surface as per Drawing and Technical Specifications.</v>
+      </c>
+      <c r="C25" s="52" t="str">
+        <f>estimate!H54</f>
+        <v>cum</v>
+      </c>
+      <c r="D25" s="52">
+        <f>estimate!G54</f>
+        <v>5.6868977985150151</v>
+      </c>
+      <c r="E25" s="52">
+        <f>estimate!I54</f>
+        <v>4458.5200000000004</v>
+      </c>
+      <c r="F25" s="52">
+        <f>D25*E25</f>
+        <v>25355.147572635167</v>
+      </c>
+      <c r="G25" s="52">
+        <f>V!G61</f>
+        <v>6.1153717601949502</v>
+      </c>
+      <c r="H25" s="52">
+        <f>V!I61</f>
+        <v>4458.5200000000004</v>
+      </c>
+      <c r="I25" s="52">
+        <f>G25*H25</f>
+        <v>27265.507300264391</v>
+      </c>
+      <c r="J25" s="53">
+        <f>I25-F25</f>
+        <v>1910.3597276292239</v>
+      </c>
+      <c r="K25" s="54"/>
+      <c r="M25" s="36">
+        <f t="shared" si="1"/>
+        <v>31693.934465793958</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="51"/>
+      <c r="B26" s="55" t="str">
+        <f>estimate!B55</f>
+        <v>-13% VAT for stone</v>
+      </c>
+      <c r="C26" s="52"/>
+      <c r="D26" s="52"/>
+      <c r="E26" s="52"/>
+      <c r="F26" s="52">
+        <f>estimate!J55</f>
+        <v>2284.8171943283714</v>
+      </c>
+      <c r="G26" s="52"/>
+      <c r="H26" s="52"/>
+      <c r="I26" s="52">
+        <f>V!J62</f>
+        <v>2456.9645951879311</v>
+      </c>
+      <c r="J26" s="53">
         <f>I26-F26</f>
-        <v>3901.4922765432129</v>
-      </c>
-      <c r="K26" s="80"/>
+        <v>172.14740085955964</v>
+      </c>
+      <c r="K26" s="54"/>
       <c r="M26" s="36">
         <f t="shared" si="1"/>
-        <v>107275.37808641975</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="77"/>
-      <c r="B27" s="81" t="str">
-        <f>[4]estimate!B32</f>
-        <v>-13% VAT for HYSD bar</v>
-      </c>
-      <c r="C27" s="78"/>
-      <c r="D27" s="78"/>
-      <c r="E27" s="78"/>
-      <c r="F27" s="78">
-        <f>[4]estimate!J32</f>
-        <v>9868.7654320987658</v>
-      </c>
-      <c r="G27" s="78"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="78">
-        <f>[4]V!J103</f>
-        <v>10317.411160493828</v>
-      </c>
-      <c r="J27" s="79">
-        <f>I27-F27</f>
-        <v>448.64572839506218</v>
-      </c>
-      <c r="K27" s="80"/>
-      <c r="M27" s="36">
+        <v>2856.0214929104641</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="56"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="52"/>
+      <c r="D27" s="52"/>
+      <c r="E27" s="52"/>
+      <c r="F27" s="52"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
+      <c r="I27" s="52"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="54"/>
+    </row>
+    <row r="28" spans="1:13" s="36" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="51">
+        <f>estimate!A57</f>
+        <v>5</v>
+      </c>
+      <c r="B28" s="58" t="str">
+        <f>estimate!B57</f>
+        <v>Providing and laying of Plain/Reinforced Cement Concrete in Foundation complete as per Drawing and Technical Specifications, PCC Grade M 15</v>
+      </c>
+      <c r="C28" s="52" t="str">
+        <f>estimate!H67</f>
+        <v>cum</v>
+      </c>
+      <c r="D28" s="52">
+        <f>estimate!G67</f>
+        <v>3.4883371222849764</v>
+      </c>
+      <c r="E28" s="52">
+        <f>estimate!I67</f>
+        <v>10964.46</v>
+      </c>
+      <c r="F28" s="52">
+        <f>D28*E28</f>
+        <v>38247.732843808728</v>
+      </c>
+      <c r="G28" s="52">
+        <f>V!G74</f>
+        <v>3.5631669525323875</v>
+      </c>
+      <c r="H28" s="52">
+        <f>V!I74</f>
+        <v>10964.46</v>
+      </c>
+      <c r="I28" s="52">
+        <f>G28*H28</f>
+        <v>39068.201524363256</v>
+      </c>
+      <c r="J28" s="53">
+        <f>I28-F28</f>
+        <v>820.46868055452796</v>
+      </c>
+      <c r="K28" s="54"/>
+      <c r="M28" s="36">
+        <f t="shared" ref="M28:M29" si="3">1.25*F28</f>
+        <v>47809.666054760906</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="51"/>
+      <c r="B29" s="55" t="str">
+        <f>estimate!B68</f>
+        <v>-13% VAT for cement</v>
+      </c>
+      <c r="C29" s="52"/>
+      <c r="D29" s="52"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="52">
+        <f>estimate!J68</f>
+        <v>1627.0404097761368</v>
+      </c>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
+      <c r="I29" s="52">
+        <f>V!J75</f>
+        <v>1661.942758202104</v>
+      </c>
+      <c r="J29" s="53">
+        <f>I29-F29</f>
+        <v>34.902348425967148</v>
+      </c>
+      <c r="K29" s="54"/>
+      <c r="M29" s="36">
+        <f t="shared" si="3"/>
+        <v>2033.800512220171</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="51"/>
+      <c r="B30" s="55" t="str">
+        <f>estimate!B69</f>
+        <v>-13% VAT for sand</v>
+      </c>
+      <c r="C30" s="52"/>
+      <c r="D30" s="52"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="52">
+        <f>estimate!J69</f>
+        <v>647.95582979473659</v>
+      </c>
+      <c r="G30" s="52"/>
+      <c r="H30" s="52"/>
+      <c r="I30" s="52">
+        <f>V!J76</f>
+        <v>661.85541089932894</v>
+      </c>
+      <c r="J30" s="53">
+        <f t="shared" ref="J30:J33" si="4">I30-F30</f>
+        <v>13.899581104592357</v>
+      </c>
+      <c r="K30" s="54"/>
+    </row>
+    <row r="31" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A31" s="51"/>
+      <c r="B31" s="55" t="str">
+        <f>estimate!B70</f>
+        <v>-13% VAT for aggregate</v>
+      </c>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52">
+        <f>estimate!J70</f>
+        <v>1317.5101872492974</v>
+      </c>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52">
+        <f>V!J77</f>
+        <v>1345.7726688286355</v>
+      </c>
+      <c r="J31" s="53">
+        <f t="shared" si="4"/>
+        <v>28.2624815793381</v>
+      </c>
+      <c r="K31" s="54"/>
+    </row>
+    <row r="32" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="51"/>
+      <c r="B32" s="55" t="str">
+        <f>estimate!B71</f>
+        <v>-13% VAT for formwork</v>
+      </c>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52">
+        <f>estimate!J71</f>
+        <v>191.24017583179665</v>
+      </c>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52">
+        <f>V!J78</f>
+        <v>195.34255166082906</v>
+      </c>
+      <c r="J32" s="53">
+        <f t="shared" si="4"/>
+        <v>4.102375829032411</v>
+      </c>
+      <c r="K32" s="54"/>
+    </row>
+    <row r="33" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="51"/>
+      <c r="B33" s="55" t="str">
+        <f>estimate!B72</f>
+        <v>-13% VAT for water</v>
+      </c>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52">
+        <f>estimate!J72</f>
+        <v>28.115997205616914</v>
+      </c>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="52">
+        <f>V!J79</f>
+        <v>28.719125637411043</v>
+      </c>
+      <c r="J33" s="53">
+        <f t="shared" si="4"/>
+        <v>0.60312843179412923</v>
+      </c>
+      <c r="K33" s="54"/>
+    </row>
+    <row r="34" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="56"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="53"/>
+      <c r="K34" s="54"/>
+    </row>
+    <row r="35" spans="1:13" s="36" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A35" s="51">
+        <f>estimate!A74</f>
+        <v>6</v>
+      </c>
+      <c r="B35" s="58" t="str">
+        <f>estimate!B74</f>
+        <v>Random Rubble Masonry, Providing and laying of Stone Masonry Work in Cement Mortar 1:6 in Foundation complete as per Drawing and Technical Specifications., Using Concrete Mixer</v>
+      </c>
+      <c r="C35" s="52" t="str">
+        <f>estimate!H78</f>
+        <v>cum</v>
+      </c>
+      <c r="D35" s="52">
+        <f>estimate!G78</f>
+        <v>52.438555318500462</v>
+      </c>
+      <c r="E35" s="52">
+        <f>estimate!I78</f>
+        <v>8987.83</v>
+      </c>
+      <c r="F35" s="52">
+        <f>D35*E35</f>
+        <v>471308.82064827799</v>
+      </c>
+      <c r="G35" s="52">
+        <f>V!G86</f>
+        <v>52.465734464637528</v>
+      </c>
+      <c r="H35" s="52">
+        <f>V!I86</f>
+        <v>8987.83</v>
+      </c>
+      <c r="I35" s="52">
+        <f>G35*H35</f>
+        <v>471553.10219330312</v>
+      </c>
+      <c r="J35" s="53">
+        <f>I35-F35</f>
+        <v>244.28154502512189</v>
+      </c>
+      <c r="K35" s="54"/>
+      <c r="M35" s="36">
+        <f t="shared" ref="M35:M36" si="5">1.25*F35</f>
+        <v>589136.02581034752</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A36" s="51"/>
+      <c r="B36" s="55" t="str">
+        <f>estimate!B79</f>
+        <v>-13% VAT for cement</v>
+      </c>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52">
+        <f>estimate!J79</f>
+        <v>7994.9237279579411</v>
+      </c>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52">
+        <f>V!J87</f>
+        <v>7999.0675339616919</v>
+      </c>
+      <c r="J36" s="53">
+        <f>I36-F36</f>
+        <v>4.1438060037507967</v>
+      </c>
+      <c r="K36" s="54"/>
+      <c r="M36" s="36">
+        <f t="shared" si="5"/>
+        <v>9993.6546599474259</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A37" s="51"/>
+      <c r="B37" s="55" t="str">
+        <f>estimate!B80</f>
+        <v>-13% VAT for sand</v>
+      </c>
+      <c r="C37" s="52"/>
+      <c r="D37" s="52"/>
+      <c r="E37" s="52"/>
+      <c r="F37" s="52">
+        <f>estimate!J80</f>
+        <v>9004.4768778221296</v>
+      </c>
+      <c r="G37" s="52"/>
+      <c r="H37" s="52"/>
+      <c r="I37" s="52">
+        <f>V!J88</f>
+        <v>9009.1439399000919</v>
+      </c>
+      <c r="J37" s="53">
+        <f t="shared" ref="J37:J39" si="6">I37-F37</f>
+        <v>4.6670620779623277</v>
+      </c>
+      <c r="K37" s="54"/>
+    </row>
+    <row r="38" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="51"/>
+      <c r="B38" s="55" t="str">
+        <f>estimate!B81</f>
+        <v>-13% VAT for stone</v>
+      </c>
+      <c r="C38" s="52"/>
+      <c r="D38" s="52"/>
+      <c r="E38" s="52"/>
+      <c r="F38" s="52">
+        <f>estimate!J81</f>
+        <v>20190.326759967087</v>
+      </c>
+      <c r="G38" s="52"/>
+      <c r="H38" s="52"/>
+      <c r="I38" s="52">
+        <f>V!J89</f>
+        <v>20200.79149985611</v>
+      </c>
+      <c r="J38" s="53">
+        <f t="shared" si="6"/>
+        <v>10.464739889022894</v>
+      </c>
+      <c r="K38" s="54"/>
+    </row>
+    <row r="39" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="51"/>
+      <c r="B39" s="55" t="str">
+        <f>estimate!B82</f>
+        <v>-13% VAT for water</v>
+      </c>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52">
+        <f>estimate!J82</f>
+        <v>422.65475586711375</v>
+      </c>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="52">
+        <f>V!J90</f>
+        <v>422.87381978497842</v>
+      </c>
+      <c r="J39" s="53">
+        <f t="shared" si="6"/>
+        <v>0.21906391786467339</v>
+      </c>
+      <c r="K39" s="54"/>
+    </row>
+    <row r="40" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="56"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="52"/>
+      <c r="D40" s="52"/>
+      <c r="E40" s="52"/>
+      <c r="F40" s="52"/>
+      <c r="G40" s="52"/>
+      <c r="H40" s="52"/>
+      <c r="I40" s="52"/>
+      <c r="J40" s="53"/>
+      <c r="K40" s="54"/>
+    </row>
+    <row r="41" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="51">
+        <f>estimate!A84</f>
+        <v>7</v>
+      </c>
+      <c r="B41" s="39" t="str">
+        <f>estimate!B84</f>
+        <v>;'Vvf O{6f RofK6f] 5fKg] sfd</v>
+      </c>
+      <c r="C41" s="52" t="str">
+        <f>estimate!H86</f>
+        <v>sqm</v>
+      </c>
+      <c r="D41" s="52">
+        <f>estimate!G86</f>
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="E41" s="52">
+        <f>estimate!I86</f>
+        <v>1017.47</v>
+      </c>
+      <c r="F41" s="52">
+        <f>D41*E41</f>
+        <v>2441.9280000000003</v>
+      </c>
+      <c r="G41" s="52">
+        <f>V!G94</f>
+        <v>0</v>
+      </c>
+      <c r="H41" s="52">
+        <f>V!I94</f>
+        <v>1017.47</v>
+      </c>
+      <c r="I41" s="52">
+        <f>G41*H41</f>
+        <v>0</v>
+      </c>
+      <c r="J41" s="53">
+        <f>I41-F41</f>
+        <v>-2441.9280000000003</v>
+      </c>
+      <c r="K41" s="54"/>
+      <c r="M41" s="36">
+        <f t="shared" ref="M41:M42" si="7">1.25*F41</f>
+        <v>3052.4100000000003</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A42" s="51"/>
+      <c r="B42" s="55" t="str">
+        <f>estimate!B87</f>
+        <v>-13% VAT for brick</v>
+      </c>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52">
+        <f>estimate!J87</f>
+        <v>268.85664000000008</v>
+      </c>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52">
+        <f>V!J95</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="53">
+        <f>I42-F42</f>
+        <v>-268.85664000000008</v>
+      </c>
+      <c r="K42" s="54"/>
+      <c r="M42" s="36">
+        <f t="shared" si="7"/>
+        <v>336.07080000000008</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="56"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="52"/>
+      <c r="D43" s="52"/>
+      <c r="E43" s="52"/>
+      <c r="F43" s="52"/>
+      <c r="G43" s="52"/>
+      <c r="H43" s="52"/>
+      <c r="I43" s="52"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="54"/>
+    </row>
+    <row r="44" spans="1:13" s="36" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A44" s="51">
+        <f>estimate!A89</f>
+        <v>8</v>
+      </c>
+      <c r="B44" s="59" t="str">
+        <f>estimate!B89</f>
+        <v>-High Density Polythene Pipe NS 40 pipe material PE 100, PN 16</v>
+      </c>
+      <c r="C44" s="52" t="str">
+        <f>estimate!H91</f>
+        <v>kg</v>
+      </c>
+      <c r="D44" s="52">
+        <f>estimate!G91</f>
+        <v>24.975000000000001</v>
+      </c>
+      <c r="E44" s="52">
+        <f>estimate!I91</f>
+        <v>287</v>
+      </c>
+      <c r="F44" s="52">
+        <f>D44*E44</f>
+        <v>7167.8250000000007</v>
+      </c>
+      <c r="G44" s="52">
+        <f>V!G99</f>
+        <v>24.975000000000001</v>
+      </c>
+      <c r="H44" s="52">
+        <f>V!I99</f>
+        <v>287</v>
+      </c>
+      <c r="I44" s="52">
+        <f>G44*H44</f>
+        <v>7167.8250000000007</v>
+      </c>
+      <c r="J44" s="53">
+        <f>I44-F44</f>
+        <v>0</v>
+      </c>
+      <c r="K44" s="54"/>
+      <c r="M44" s="36">
         <f t="shared" si="1"/>
-        <v>12335.956790123457</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="77"/>
-      <c r="B28" s="81" t="str">
-        <f>[4]estimate!B33</f>
-        <v>-13% VAT for binding wire</v>
-      </c>
-      <c r="C28" s="78"/>
-      <c r="D28" s="78"/>
-      <c r="E28" s="78"/>
-      <c r="F28" s="78">
-        <f>[4]estimate!J33</f>
-        <v>86.127407407407404</v>
-      </c>
-      <c r="G28" s="78"/>
-      <c r="H28" s="78"/>
-      <c r="I28" s="78">
-        <f>[4]V!J104</f>
-        <v>90.042861037037042</v>
-      </c>
-      <c r="J28" s="79">
-        <f>I28-F28</f>
-        <v>3.9154536296296385</v>
-      </c>
-      <c r="K28" s="80"/>
-    </row>
-    <row r="29" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="82"/>
-      <c r="B29" s="83"/>
-      <c r="C29" s="78"/>
-      <c r="D29" s="78"/>
-      <c r="E29" s="78"/>
-      <c r="F29" s="78"/>
-      <c r="G29" s="78"/>
-      <c r="H29" s="78"/>
-      <c r="I29" s="78"/>
-      <c r="J29" s="79"/>
-      <c r="K29" s="80"/>
-    </row>
-    <row r="30" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="77">
-        <f>[4]estimate!A35</f>
-        <v>5</v>
-      </c>
-      <c r="B30" s="85" t="str">
-        <f>[4]estimate!B35</f>
-        <v>Provisional sum for lab tests</v>
-      </c>
-      <c r="C30" s="78" t="str">
-        <f>[4]estimate!H35</f>
-        <v>PS</v>
-      </c>
-      <c r="D30" s="78">
-        <f>[4]estimate!G35</f>
+        <v>8959.78125</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" s="36" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A45" s="51"/>
+      <c r="B45" s="59" t="str">
+        <f>estimate!B92</f>
+        <v>-13% VAT for material</v>
+      </c>
+      <c r="C45" s="52"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52">
+        <f>estimate!J92</f>
+        <v>931.81725000000017</v>
+      </c>
+      <c r="G45" s="52"/>
+      <c r="H45" s="52"/>
+      <c r="I45" s="52">
+        <f>V!J100</f>
+        <v>931.81725000000017</v>
+      </c>
+      <c r="J45" s="53"/>
+      <c r="K45" s="54"/>
+    </row>
+    <row r="46" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="56"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
+      <c r="F46" s="52"/>
+      <c r="G46" s="52"/>
+      <c r="H46" s="52"/>
+      <c r="I46" s="52"/>
+      <c r="J46" s="53"/>
+      <c r="K46" s="54"/>
+    </row>
+    <row r="47" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="51">
+        <f>estimate!A94</f>
+        <v>9</v>
+      </c>
+      <c r="B47" s="60" t="str">
+        <f>estimate!B94</f>
+        <v>Information board (सुचना पाटि)</v>
+      </c>
+      <c r="C47" s="52" t="str">
+        <f>estimate!H94</f>
+        <v>no.</v>
+      </c>
+      <c r="D47" s="52">
+        <f>estimate!G94</f>
         <v>1</v>
       </c>
-      <c r="E30" s="78">
-        <f>[4]estimate!I35</f>
-        <v>5000</v>
-      </c>
-      <c r="F30" s="78">
-        <f>D30*E30</f>
-        <v>5000</v>
-      </c>
-      <c r="G30" s="78">
-        <f>[4]V!G106</f>
+      <c r="E47" s="52">
+        <f>estimate!I94</f>
+        <v>500</v>
+      </c>
+      <c r="F47" s="52">
+        <f>D47*E47</f>
+        <v>500</v>
+      </c>
+      <c r="G47" s="52">
+        <f>V!G102</f>
         <v>1</v>
       </c>
-      <c r="H30" s="78">
-        <f>[4]V!I106</f>
-        <v>5000</v>
-      </c>
-      <c r="I30" s="78">
-        <f>G30*H30</f>
-        <v>5000</v>
-      </c>
-      <c r="J30" s="79">
-        <f>I30-F30</f>
+      <c r="H47" s="52">
+        <f>V!I102</f>
+        <v>500</v>
+      </c>
+      <c r="I47" s="52">
+        <f>G47*H47</f>
+        <v>500</v>
+      </c>
+      <c r="J47" s="53">
+        <f>I47-F47</f>
         <v>0</v>
       </c>
-      <c r="K30" s="80"/>
-      <c r="M30" s="36">
-        <f t="shared" si="1"/>
-        <v>6250</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="82"/>
-      <c r="B31" s="83"/>
-      <c r="C31" s="78"/>
-      <c r="D31" s="78"/>
-      <c r="E31" s="78"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="78"/>
-      <c r="H31" s="78"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="79"/>
-      <c r="K31" s="80"/>
-    </row>
-    <row r="32" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="77">
-        <f>[4]estimate!A37</f>
-        <v>6</v>
-      </c>
-      <c r="B32" s="86" t="str">
-        <f>[4]estimate!B37</f>
-        <v>Information board (सुचना पाटि)</v>
-      </c>
-      <c r="C32" s="78" t="str">
-        <f>[4]estimate!H37</f>
-        <v>no.</v>
-      </c>
-      <c r="D32" s="78">
-        <f>[4]estimate!G37</f>
-        <v>1</v>
-      </c>
-      <c r="E32" s="78">
-        <f>[4]estimate!I37</f>
-        <v>500</v>
-      </c>
-      <c r="F32" s="78">
-        <f>D32*E32</f>
-        <v>500</v>
-      </c>
-      <c r="G32" s="78">
-        <f>[4]V!G108</f>
-        <v>1</v>
-      </c>
-      <c r="H32" s="78">
-        <f>[4]V!I108</f>
-        <v>500</v>
-      </c>
-      <c r="I32" s="78">
-        <f>G32*H32</f>
-        <v>500</v>
-      </c>
-      <c r="J32" s="79">
-        <f>I32-F32</f>
-        <v>0</v>
-      </c>
-      <c r="K32" s="80"/>
-    </row>
-    <row r="33" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="83"/>
-      <c r="B33" s="83"/>
-      <c r="C33" s="78"/>
-      <c r="D33" s="78"/>
-      <c r="E33" s="78"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="78"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="79"/>
-      <c r="K33" s="80"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="87"/>
-      <c r="B34" s="88" t="s">
+      <c r="K47" s="54"/>
+    </row>
+    <row r="48" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="57"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="52"/>
+      <c r="H48" s="52"/>
+      <c r="I48" s="52"/>
+      <c r="J48" s="53"/>
+      <c r="K48" s="54"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="61"/>
+      <c r="B49" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="88"/>
-      <c r="D34" s="89"/>
-      <c r="E34" s="89"/>
-      <c r="F34" s="89">
-        <f>SUM(F13:F32)</f>
-        <v>720242.30001415103</v>
-      </c>
-      <c r="G34" s="89"/>
-      <c r="H34" s="89"/>
-      <c r="I34" s="89">
-        <f>SUM(I13:I32)</f>
-        <v>744767.80140564521</v>
-      </c>
-      <c r="J34" s="90">
-        <f>I34-F34</f>
-        <v>24525.501391494181</v>
-      </c>
-      <c r="K34" s="87"/>
+      <c r="C49" s="62"/>
+      <c r="D49" s="63"/>
+      <c r="E49" s="63"/>
+      <c r="F49" s="63">
+        <f>SUM(F13:F47)</f>
+        <v>786973.54597297299</v>
+      </c>
+      <c r="G49" s="63"/>
+      <c r="H49" s="63"/>
+      <c r="I49" s="63">
+        <f>SUM(I13:I47)</f>
+        <v>803383.79487942101</v>
+      </c>
+      <c r="J49" s="64">
+        <f>I49-F49</f>
+        <v>16410.248906448018</v>
+      </c>
+      <c r="K49" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="I9:K9"/>
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="B11:B12"/>
@@ -4858,19 +5050,6 @@
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="G11:I11"/>
     <mergeCell ref="J11:J12"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="J6:K6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4905,113 +5084,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
     </row>
     <row r="2" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="77"/>
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="77"/>
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
     </row>
     <row r="5" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
+      <c r="K5" s="78"/>
     </row>
     <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="79" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
+      <c r="B6" s="79"/>
+      <c r="C6" s="79"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="79"/>
+      <c r="F6" s="79"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="48" t="s">
+      <c r="H6" s="80" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="80"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
+      <c r="B7" s="70"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="70"/>
+      <c r="E7" s="70"/>
+      <c r="F7" s="70"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="56" t="s">
+      <c r="H7" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
+      <c r="I7" s="71"/>
+      <c r="J7" s="71"/>
+      <c r="K7" s="71"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -5078,24 +5257,24 @@
       <c r="B10" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="91">
+      <c r="C10" s="65">
         <f>4</f>
         <v>4</v>
       </c>
-      <c r="D10" s="92">
-        <f>(12+1+2)/3.281</f>
-        <v>4.5717768972874122</v>
-      </c>
-      <c r="E10" s="92">
+      <c r="D10" s="66">
+        <f>(12+1)/3.281</f>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E10" s="66">
         <v>6.5</v>
       </c>
-      <c r="F10" s="92">
+      <c r="F10" s="66">
         <f t="shared" ref="F10:F31" si="0">PRODUCT(C10:E10)</f>
-        <v>118.86619932947272</v>
-      </c>
-      <c r="G10" s="92">
+        <v>103.0173727522097</v>
+      </c>
+      <c r="G10" s="66">
         <f t="shared" ref="G10:G31" si="1">F10</f>
-        <v>118.86619932947272</v>
+        <v>103.0173727522097</v>
       </c>
       <c r="H10" s="42"/>
       <c r="I10" s="42"/>
@@ -5109,23 +5288,23 @@
       <c r="B11" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="91">
+      <c r="C11" s="65">
         <v>4</v>
       </c>
-      <c r="D11" s="92">
-        <f>12/3.281</f>
-        <v>3.6574215178299299</v>
-      </c>
-      <c r="E11" s="92">
+      <c r="D11" s="66">
+        <f>11.5/3.281</f>
+        <v>3.5050289545870159</v>
+      </c>
+      <c r="E11" s="66">
         <v>6.5</v>
       </c>
-      <c r="F11" s="92">
+      <c r="F11" s="66">
         <f t="shared" si="0"/>
-        <v>95.092959463578183</v>
-      </c>
-      <c r="G11" s="92">
+        <v>91.130752819262412</v>
+      </c>
+      <c r="G11" s="66">
         <f t="shared" si="1"/>
-        <v>95.092959463578183</v>
+        <v>91.130752819262412</v>
       </c>
       <c r="H11" s="42"/>
       <c r="I11" s="42"/>
@@ -5136,11 +5315,11 @@
       <c r="K11" s="27"/>
       <c r="Q11" s="36">
         <f>PRODUCT(C11:D11)</f>
-        <v>14.629686071319719</v>
+        <v>14.020115818348064</v>
       </c>
       <c r="R11" s="36">
         <f>CONVERT(Q11,"m","ft")</f>
-        <v>47.997657714303543</v>
+        <v>45.997755309540885</v>
       </c>
     </row>
     <row r="12" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -5148,23 +5327,23 @@
       <c r="B12" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="91">
+      <c r="C12" s="65">
         <v>2</v>
       </c>
-      <c r="D12" s="92">
-        <f>12/3.281</f>
-        <v>3.6574215178299299</v>
-      </c>
-      <c r="E12" s="92">
+      <c r="D12" s="66">
+        <f>11.5/3.281</f>
+        <v>3.5050289545870159</v>
+      </c>
+      <c r="E12" s="66">
         <v>6.5</v>
       </c>
-      <c r="F12" s="92">
+      <c r="F12" s="66">
         <f t="shared" si="0"/>
-        <v>47.546479731789091</v>
-      </c>
-      <c r="G12" s="92">
+        <v>45.565376409631206</v>
+      </c>
+      <c r="G12" s="66">
         <f t="shared" si="1"/>
-        <v>47.546479731789091</v>
+        <v>45.565376409631206</v>
       </c>
       <c r="H12" s="42"/>
       <c r="I12" s="42"/>
@@ -5176,23 +5355,22 @@
       <c r="B13" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="91">
+      <c r="C13" s="65">
         <v>4</v>
       </c>
-      <c r="D13" s="92">
-        <f>5.25/3.281</f>
-        <v>1.6001219140505942</v>
-      </c>
-      <c r="E13" s="92">
+      <c r="D13" s="66">
+        <v>1.5</v>
+      </c>
+      <c r="E13" s="66">
         <v>6.5</v>
       </c>
-      <c r="F13" s="92">
+      <c r="F13" s="66">
         <f t="shared" si="0"/>
-        <v>41.60316976531545</v>
-      </c>
-      <c r="G13" s="92">
+        <v>39</v>
+      </c>
+      <c r="G13" s="66">
         <f t="shared" si="1"/>
-        <v>41.60316976531545</v>
+        <v>39</v>
       </c>
       <c r="H13" s="42"/>
       <c r="I13" s="42"/>
@@ -5202,23 +5380,23 @@
     <row r="14" spans="1:18" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="43"/>
-      <c r="C14" s="91">
+      <c r="C14" s="65">
         <v>1</v>
       </c>
-      <c r="D14" s="92">
-        <f>1.5</f>
-        <v>1.5</v>
-      </c>
-      <c r="E14" s="92">
+      <c r="D14" s="66">
+        <f>0.45</f>
+        <v>0.45</v>
+      </c>
+      <c r="E14" s="66">
         <v>6.5</v>
       </c>
-      <c r="F14" s="92">
+      <c r="F14" s="66">
         <f t="shared" ref="F14" si="2">PRODUCT(C14:E14)</f>
-        <v>9.75</v>
-      </c>
-      <c r="G14" s="92">
+        <v>2.9250000000000003</v>
+      </c>
+      <c r="G14" s="66">
         <f t="shared" ref="G14" si="3">F14</f>
-        <v>9.75</v>
+        <v>2.9250000000000003</v>
       </c>
       <c r="H14" s="42"/>
       <c r="I14" s="42">
@@ -5230,24 +5408,24 @@
     </row>
     <row r="15" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="16"/>
-      <c r="B15" s="93" t="s">
+      <c r="B15" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="91">
+      <c r="C15" s="65">
         <v>2</v>
       </c>
-      <c r="D15" s="92">
+      <c r="D15" s="66">
         <f>9/3.281</f>
         <v>2.7430661383724475</v>
       </c>
-      <c r="E15" s="92">
+      <c r="E15" s="66">
         <v>4.43</v>
       </c>
-      <c r="F15" s="92">
+      <c r="F15" s="66">
         <f t="shared" si="0"/>
         <v>24.303565985979883</v>
       </c>
-      <c r="G15" s="92">
+      <c r="G15" s="66">
         <f t="shared" si="1"/>
         <v>24.303565985979883</v>
       </c>
@@ -5264,21 +5442,21 @@
       <c r="B16" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="91">
+      <c r="C16" s="65">
         <v>4</v>
       </c>
-      <c r="D16" s="92">
+      <c r="D16" s="66">
         <f>5.75/3.281</f>
         <v>1.752514477293508</v>
       </c>
-      <c r="E16" s="92">
+      <c r="E16" s="66">
         <v>4.43</v>
       </c>
-      <c r="F16" s="92">
+      <c r="F16" s="66">
         <f t="shared" si="0"/>
         <v>31.054556537640959</v>
       </c>
-      <c r="G16" s="92">
+      <c r="G16" s="66">
         <f t="shared" si="1"/>
         <v>31.054556537640959</v>
       </c>
@@ -5293,21 +5471,21 @@
     <row r="17" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="16"/>
       <c r="B17" s="43"/>
-      <c r="C17" s="91">
+      <c r="C17" s="65">
         <v>4</v>
       </c>
-      <c r="D17" s="92">
+      <c r="D17" s="66">
         <f>77/12/3.281</f>
         <v>1.9557045616173931</v>
       </c>
-      <c r="E17" s="92">
+      <c r="E17" s="66">
         <v>4.43</v>
       </c>
-      <c r="F17" s="92">
+      <c r="F17" s="66">
         <f t="shared" ref="F17" si="4">PRODUCT(C17:E17)</f>
         <v>34.655084831860208</v>
       </c>
-      <c r="G17" s="92">
+      <c r="G17" s="66">
         <f t="shared" ref="G17" si="5">F17</f>
         <v>34.655084831860208</v>
       </c>
@@ -5324,22 +5502,22 @@
       <c r="B18" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="91">
+      <c r="C18" s="65">
         <f>4</f>
         <v>4</v>
       </c>
-      <c r="D18" s="92">
+      <c r="D18" s="66">
         <f>10.67/3.281</f>
         <v>3.2520572996037793</v>
       </c>
-      <c r="E18" s="92">
+      <c r="E18" s="66">
         <v>4.43</v>
       </c>
-      <c r="F18" s="92">
+      <c r="F18" s="66">
         <f t="shared" si="0"/>
         <v>57.626455348978965</v>
       </c>
-      <c r="G18" s="92">
+      <c r="G18" s="66">
         <f t="shared" si="1"/>
         <v>57.626455348978965</v>
       </c>
@@ -5354,22 +5532,22 @@
     <row r="19" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="16"/>
       <c r="B19" s="43"/>
-      <c r="C19" s="91">
+      <c r="C19" s="65">
         <f>4</f>
         <v>4</v>
       </c>
-      <c r="D19" s="92">
+      <c r="D19" s="66">
         <f>15/3.281</f>
         <v>4.5717768972874122</v>
       </c>
-      <c r="E19" s="92">
+      <c r="E19" s="66">
         <v>4.43</v>
       </c>
-      <c r="F19" s="92">
+      <c r="F19" s="66">
         <f t="shared" si="0"/>
         <v>81.011886619932937</v>
       </c>
-      <c r="G19" s="92">
+      <c r="G19" s="66">
         <f t="shared" si="1"/>
         <v>81.011886619932937</v>
       </c>
@@ -5386,22 +5564,22 @@
       <c r="B20" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="91">
+      <c r="C20" s="65">
         <f>4*1</f>
         <v>4</v>
       </c>
-      <c r="D20" s="92">
+      <c r="D20" s="66">
         <f>6.42/3.281</f>
         <v>1.9567205120390123</v>
       </c>
-      <c r="E20" s="92">
+      <c r="E20" s="66">
         <v>4.43</v>
       </c>
-      <c r="F20" s="92">
+      <c r="F20" s="66">
         <f t="shared" si="0"/>
         <v>34.673087473331293</v>
       </c>
-      <c r="G20" s="92">
+      <c r="G20" s="66">
         <f t="shared" si="1"/>
         <v>34.673087473331293</v>
       </c>
@@ -5416,22 +5594,22 @@
     <row r="21" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="16"/>
       <c r="B21" s="43"/>
-      <c r="C21" s="91">
+      <c r="C21" s="65">
         <f>4*2</f>
         <v>8</v>
       </c>
-      <c r="D21" s="92">
+      <c r="D21" s="66">
         <f>6.42/3.281</f>
         <v>1.9567205120390123</v>
       </c>
-      <c r="E21" s="92">
+      <c r="E21" s="66">
         <v>4.43</v>
       </c>
-      <c r="F21" s="92">
+      <c r="F21" s="66">
         <f t="shared" ref="F21" si="6">PRODUCT(C21:E21)</f>
         <v>69.346174946662586</v>
       </c>
-      <c r="G21" s="92">
+      <c r="G21" s="66">
         <f t="shared" ref="G21" si="7">F21</f>
         <v>69.346174946662586</v>
       </c>
@@ -5448,21 +5626,21 @@
       <c r="B22" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="91">
+      <c r="C22" s="65">
         <v>4</v>
       </c>
-      <c r="D22" s="92">
+      <c r="D22" s="66">
         <f>8/12/3.281</f>
         <v>0.20319008432388497</v>
       </c>
-      <c r="E22" s="92">
+      <c r="E22" s="66">
         <v>4.43</v>
       </c>
-      <c r="F22" s="92">
+      <c r="F22" s="66">
         <f t="shared" si="0"/>
         <v>3.6005282942192416</v>
       </c>
-      <c r="G22" s="92">
+      <c r="G22" s="66">
         <f t="shared" si="1"/>
         <v>3.6005282942192416</v>
       </c>
@@ -5477,21 +5655,21 @@
     <row r="23" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="16"/>
       <c r="B23" s="43"/>
-      <c r="C23" s="91">
+      <c r="C23" s="65">
         <v>4</v>
       </c>
-      <c r="D23" s="92">
+      <c r="D23" s="66">
         <f>54/12/3.281</f>
         <v>1.3715330691862238</v>
       </c>
-      <c r="E23" s="92">
+      <c r="E23" s="66">
         <v>4.43</v>
       </c>
-      <c r="F23" s="92">
+      <c r="F23" s="66">
         <f t="shared" si="0"/>
         <v>24.303565985979883</v>
       </c>
-      <c r="G23" s="92">
+      <c r="G23" s="66">
         <f t="shared" si="1"/>
         <v>24.303565985979883</v>
       </c>
@@ -5506,21 +5684,21 @@
     <row r="24" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="43"/>
-      <c r="C24" s="91">
+      <c r="C24" s="65">
         <v>4</v>
       </c>
-      <c r="D24" s="92">
+      <c r="D24" s="66">
         <f>105/12/3.281</f>
         <v>2.6668698567509903</v>
       </c>
-      <c r="E24" s="92">
+      <c r="E24" s="66">
         <v>4.43</v>
       </c>
-      <c r="F24" s="92">
+      <c r="F24" s="66">
         <f t="shared" ref="F24" si="8">PRODUCT(C24:E24)</f>
         <v>47.256933861627545</v>
       </c>
-      <c r="G24" s="92">
+      <c r="G24" s="66">
         <f t="shared" ref="G24" si="9">F24</f>
         <v>47.256933861627545</v>
       </c>
@@ -5537,21 +5715,21 @@
       <c r="B25" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="91">
+      <c r="C25" s="65">
         <v>4</v>
       </c>
-      <c r="D25" s="92">
+      <c r="D25" s="66">
         <f>75/12/3.281</f>
         <v>1.9049070405364217</v>
       </c>
-      <c r="E25" s="92">
+      <c r="E25" s="66">
         <v>4.43</v>
       </c>
-      <c r="F25" s="92">
+      <c r="F25" s="66">
         <f t="shared" si="0"/>
         <v>33.754952758305393</v>
       </c>
-      <c r="G25" s="92">
+      <c r="G25" s="66">
         <f t="shared" si="1"/>
         <v>33.754952758305393</v>
       </c>
@@ -5566,22 +5744,22 @@
     <row r="26" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="43"/>
-      <c r="C26" s="91">
+      <c r="C26" s="65">
         <f>4*2</f>
         <v>8</v>
       </c>
-      <c r="D26" s="92">
+      <c r="D26" s="66">
         <f>(36+37)/12/3.281</f>
         <v>1.8541095194554504</v>
       </c>
-      <c r="E26" s="92">
+      <c r="E26" s="66">
         <v>4.43</v>
       </c>
-      <c r="F26" s="92">
+      <c r="F26" s="66">
         <f t="shared" ref="F26" si="10">PRODUCT(C26:E26)</f>
         <v>65.709641369501156</v>
       </c>
-      <c r="G26" s="92">
+      <c r="G26" s="66">
         <f t="shared" ref="G26" si="11">F26</f>
         <v>65.709641369501156</v>
       </c>
@@ -5739,7 +5917,7 @@
       <c r="F32" s="5"/>
       <c r="G32" s="42">
         <f>SUM(G10:G31)</f>
-        <v>911.28087270141191</v>
+        <v>880.06056639235987</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>40</v>
@@ -5749,7 +5927,7 @@
       </c>
       <c r="J32" s="42">
         <f>G32*I32</f>
-        <v>166317.87207673467</v>
+        <v>160619.8539722696</v>
       </c>
       <c r="K32" s="5"/>
     </row>
@@ -5767,7 +5945,7 @@
       <c r="I33" s="6"/>
       <c r="J33" s="42">
         <f>0.13*G32*(1871.42/18.94)</f>
-        <v>11705.417244076765</v>
+        <v>11304.391915023165</v>
       </c>
       <c r="K33" s="5"/>
     </row>
@@ -5810,17 +5988,17 @@
         <v>4</v>
       </c>
       <c r="D36" s="4">
-        <f>(17+6)/2/3.281</f>
-        <v>3.5050289545870159</v>
+        <f>(15+6)/2/3.281</f>
+        <v>3.2002438281011885</v>
       </c>
       <c r="E36" s="5">
-        <f>6/3.281</f>
-        <v>1.8287107589149649</v>
+        <f>5.583/3.281</f>
+        <v>1.7016153611703748</v>
       </c>
       <c r="F36" s="5"/>
       <c r="G36" s="33">
         <f t="shared" ref="G36:G37" si="12">PRODUCT(C36:F36)</f>
-        <v>25.638736638246993</v>
+        <v>21.782336229550666</v>
       </c>
       <c r="H36" s="7"/>
       <c r="I36" s="6">
@@ -5843,13 +6021,13 @@
         <v>1.5239256324291375</v>
       </c>
       <c r="E37" s="5">
-        <f>6/3.281</f>
-        <v>1.8287107589149649</v>
+        <f>5.583/3.281</f>
+        <v>1.7016153611703748</v>
       </c>
       <c r="F37" s="5"/>
       <c r="G37" s="33">
         <f t="shared" si="12"/>
-        <v>11.147276799237824</v>
+        <v>10.372541061690795</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="6"/>
@@ -5867,7 +6045,7 @@
       <c r="F38" s="5"/>
       <c r="G38" s="42">
         <f>SUM(G36:G37)</f>
-        <v>36.786013437484819</v>
+        <v>32.154877291241462</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>54</v>
@@ -5877,7 +6055,7 @@
       </c>
       <c r="J38" s="42">
         <f>G38*I38</f>
-        <v>40927.38283027686</v>
+        <v>35774.873376689422</v>
       </c>
       <c r="K38" s="5"/>
     </row>
@@ -5895,7 +6073,7 @@
       <c r="I39" s="17"/>
       <c r="J39" s="18">
         <f>0.13*G38*7050.67/10</f>
-        <v>3371.7585377225246</v>
+        <v>2947.2745727234869</v>
       </c>
       <c r="K39" s="17"/>
     </row>
@@ -5913,7 +6091,7 @@
       <c r="I40" s="17"/>
       <c r="J40" s="18">
         <f>0.13*G38*1023.75/10</f>
-        <v>489.57585633612615</v>
+        <v>427.94122314980984</v>
       </c>
       <c r="K40" s="17"/>
     </row>
@@ -5931,7 +6109,7 @@
       <c r="I41" s="17"/>
       <c r="J41" s="18">
         <f>0.13*G38*348.21/10</f>
-        <v>166.52035060786565</v>
+        <v>145.55644768058147</v>
       </c>
       <c r="K41" s="17"/>
     </row>
@@ -5949,7 +6127,7 @@
       <c r="I42" s="17"/>
       <c r="J42" s="18">
         <f>0.13*G38*165/10</f>
-        <v>78.905998823404943</v>
+        <v>68.972211789712929</v>
       </c>
       <c r="K42" s="17"/>
     </row>
@@ -6019,7 +6197,7 @@
       </c>
       <c r="D46" s="33">
         <f>D55</f>
-        <v>7.7720207253886011</v>
+        <v>7.8229198415117347</v>
       </c>
       <c r="E46" s="17">
         <f>E55</f>
@@ -6030,7 +6208,7 @@
       </c>
       <c r="G46" s="33">
         <f t="shared" si="13"/>
-        <v>5.8290155440414511</v>
+        <v>5.8671898811338012</v>
       </c>
       <c r="H46" s="17"/>
       <c r="I46" s="17"/>
@@ -6052,11 +6230,11 @@
         <v>0.6</v>
       </c>
       <c r="F47" s="17">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="G47" s="33">
         <f t="shared" si="13"/>
-        <v>0.86399999999999999</v>
+        <v>0.64800000000000002</v>
       </c>
       <c r="H47" s="17"/>
       <c r="I47" s="17"/>
@@ -6079,12 +6257,11 @@
         <v>0.45</v>
       </c>
       <c r="F48" s="33">
-        <f>0.45+0.075</f>
-        <v>0.52500000000000002</v>
+        <v>0.3</v>
       </c>
       <c r="G48" s="33">
         <f t="shared" si="13"/>
-        <v>2.9522249314233471</v>
+        <v>1.6869856750990553</v>
       </c>
       <c r="H48" s="17"/>
       <c r="I48" s="17"/>
@@ -6106,11 +6283,11 @@
         <v>0.3</v>
       </c>
       <c r="F49" s="33">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G49" s="33">
         <f t="shared" si="13"/>
-        <v>0.26999999999999996</v>
+        <v>0.13499999999999998</v>
       </c>
       <c r="H49" s="17"/>
       <c r="I49" s="17"/>
@@ -6128,7 +6305,7 @@
       <c r="F50" s="5"/>
       <c r="G50" s="42">
         <f>SUM(G45:G49)</f>
-        <v>24.916383419689126</v>
+        <v>23.338318500457184</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>63</v>
@@ -6138,7 +6315,7 @@
       </c>
       <c r="J50" s="42">
         <f>G50*I50</f>
-        <v>1568.4863362694305</v>
+        <v>1469.1471496037798</v>
       </c>
       <c r="K50" s="5"/>
     </row>
@@ -6156,7 +6333,7 @@
       <c r="I51" s="17"/>
       <c r="J51" s="18">
         <f>0.13*G50*18612/360</f>
-        <v>167.46301296373062</v>
+        <v>156.85683864157275</v>
       </c>
       <c r="K51" s="17"/>
     </row>
@@ -6226,7 +6403,7 @@
       </c>
       <c r="D55" s="33">
         <f>D67</f>
-        <v>7.7720207253886011</v>
+        <v>7.8229198415117347</v>
       </c>
       <c r="E55" s="17">
         <f>E67</f>
@@ -6237,7 +6414,7 @@
       </c>
       <c r="G55" s="33">
         <f t="shared" si="14"/>
-        <v>1.1658031088082901</v>
+        <v>1.1734379762267602</v>
       </c>
       <c r="H55" s="17"/>
       <c r="I55" s="17"/>
@@ -6255,19 +6432,17 @@
         <v>4</v>
       </c>
       <c r="D56" s="33">
-        <f>D47</f>
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="E56" s="17">
-        <f>E47</f>
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="F56" s="17">
         <v>0.15</v>
       </c>
       <c r="G56" s="33">
         <f t="shared" si="14"/>
-        <v>0.216</v>
+        <v>0.1215</v>
       </c>
       <c r="H56" s="17"/>
       <c r="I56" s="17"/>
@@ -6285,8 +6460,8 @@
         <v>4</v>
       </c>
       <c r="D57" s="33">
-        <f>10.75/3.281</f>
-        <v>3.2764401097226452</v>
+        <f>11.17/3.281</f>
+        <v>3.4044498628466928</v>
       </c>
       <c r="E57" s="17">
         <v>0.45</v>
@@ -6296,7 +6471,7 @@
       </c>
       <c r="G57" s="33">
         <f t="shared" si="14"/>
-        <v>0.88463882962511431</v>
+        <v>0.91920146296860705</v>
       </c>
       <c r="H57" s="17"/>
       <c r="I57" s="17"/>
@@ -6310,19 +6485,19 @@
         <v>1</v>
       </c>
       <c r="D58" s="33">
-        <f>10.75/3.281</f>
-        <v>3.2764401097226452</v>
+        <f>11.17/3.281</f>
+        <v>3.4044498628466928</v>
       </c>
       <c r="E58" s="33">
-        <f>10.75/3.281</f>
-        <v>3.2764401097226452</v>
+        <f>11.17/3.281</f>
+        <v>3.4044498628466928</v>
       </c>
       <c r="F58" s="17">
         <v>0.15</v>
       </c>
       <c r="G58" s="33">
         <f t="shared" si="14"/>
-        <v>1.6102589688899007</v>
+        <v>1.7385418302955298</v>
       </c>
       <c r="H58" s="17"/>
       <c r="I58" s="17"/>
@@ -6395,7 +6570,7 @@
       <c r="F61" s="5"/>
       <c r="G61" s="42">
         <f>SUM(G54:G60)</f>
-        <v>6.0393913980273588</v>
+        <v>6.1153717601949502</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>63</v>
@@ -6405,7 +6580,7 @@
       </c>
       <c r="J61" s="42">
         <f>G61*I61</f>
-        <v>26926.747335932941</v>
+        <v>27265.507300264391</v>
       </c>
       <c r="K61" s="5"/>
     </row>
@@ -6423,7 +6598,7 @@
       <c r="I62" s="17"/>
       <c r="J62" s="18">
         <f>0.13*G61*15452.64/5</f>
-        <v>2426.4380684131506</v>
+        <v>2456.9645951879311</v>
       </c>
       <c r="K62" s="17"/>
     </row>
@@ -6518,7 +6693,7 @@
       </c>
       <c r="D67" s="33">
         <f>D83</f>
-        <v>7.7720207253886011</v>
+        <v>7.8229198415117347</v>
       </c>
       <c r="E67" s="33">
         <f>F83/2</f>
@@ -6529,7 +6704,7 @@
       </c>
       <c r="G67" s="33">
         <f t="shared" si="15"/>
-        <v>0.3886010362694301</v>
+        <v>0.39114599207558676</v>
       </c>
       <c r="H67" s="17"/>
       <c r="I67" s="17"/>
@@ -6544,7 +6719,7 @@
       </c>
       <c r="D68" s="33">
         <f>D83</f>
-        <v>7.7720207253886011</v>
+        <v>7.8229198415117347</v>
       </c>
       <c r="E68" s="17">
         <v>0.45</v>
@@ -6554,7 +6729,7 @@
       </c>
       <c r="G68" s="33">
         <f t="shared" si="15"/>
-        <v>0.17487046632124353</v>
+        <v>0.17601569643401405</v>
       </c>
       <c r="H68" s="17"/>
       <c r="I68" s="17"/>
@@ -6571,17 +6746,17 @@
         <v>4</v>
       </c>
       <c r="D69" s="33">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="E69" s="17">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="F69" s="17">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="G69" s="33">
         <f t="shared" si="15"/>
-        <v>0.64800000000000002</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="H69" s="17"/>
       <c r="I69" s="17"/>
@@ -6600,18 +6775,18 @@
       </c>
       <c r="D70" s="33">
         <f>D57</f>
-        <v>3.2764401097226452</v>
+        <v>3.4044498628466928</v>
       </c>
       <c r="E70" s="17">
         <f>E57</f>
         <v>0.45</v>
       </c>
-      <c r="F70" s="17">
+      <c r="F70" s="33">
         <v>0.05</v>
       </c>
       <c r="G70" s="33">
         <f t="shared" si="15"/>
-        <v>0.29487960987503808</v>
+        <v>0.30640048765620237</v>
       </c>
       <c r="H70" s="17"/>
       <c r="I70" s="17"/>
@@ -6625,19 +6800,19 @@
         <v>1</v>
       </c>
       <c r="D71" s="33">
-        <f>13.75/3.281</f>
-        <v>4.190795489180128</v>
+        <f>14.17/3.281</f>
+        <v>4.3188052423041752</v>
       </c>
       <c r="E71" s="33">
-        <f>13.75/3.281</f>
-        <v>4.190795489180128</v>
+        <f>14.17/3.281</f>
+        <v>4.3188052423041752</v>
       </c>
       <c r="F71" s="33">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="G71" s="33">
         <f t="shared" si="15"/>
-        <v>1.3172075124099381</v>
+        <v>1.3989059040715519</v>
       </c>
       <c r="H71" s="17"/>
       <c r="I71" s="17"/>
@@ -6710,7 +6885,7 @@
       <c r="F74" s="5"/>
       <c r="G74" s="42">
         <f>SUM(G65:G73)</f>
-        <v>3.8712574971706815</v>
+        <v>3.5631669525323875</v>
       </c>
       <c r="H74" s="7" t="s">
         <v>63</v>
@@ -6720,7 +6895,7 @@
       </c>
       <c r="J74" s="42">
         <f>G74*I74</f>
-        <v>42446.247977428044</v>
+        <v>39068.201524363256</v>
       </c>
       <c r="K74" s="5"/>
     </row>
@@ -6738,7 +6913,7 @@
       <c r="I75" s="17"/>
       <c r="J75" s="18">
         <f>0.13*G74*53818.03/15</f>
-        <v>1805.6432517106243</v>
+        <v>1661.942758202104</v>
       </c>
       <c r="K75" s="17"/>
     </row>
@@ -6756,7 +6931,7 @@
       <c r="I76" s="17"/>
       <c r="J76" s="18">
         <f>0.13*G74*21432.6/15</f>
-        <v>719.08298309345628</v>
+        <v>661.85541089932894</v>
       </c>
       <c r="K76" s="17"/>
     </row>
@@ -6774,7 +6949,7 @@
       <c r="I77" s="17"/>
       <c r="J77" s="18">
         <f>0.13*G74*(25719.12+13573.98+4286.52)/15</f>
-        <v>1462.1353989566944</v>
+        <v>1345.7726688286355</v>
       </c>
       <c r="K77" s="17"/>
     </row>
@@ -6792,7 +6967,7 @@
       <c r="I78" s="17"/>
       <c r="J78" s="18">
         <f>0.13*G74*(6325.7/15)</f>
-        <v>212.23291743205567</v>
+        <v>195.34255166082906</v>
       </c>
       <c r="K78" s="17"/>
     </row>
@@ -6810,7 +6985,7 @@
       <c r="I79" s="17"/>
       <c r="J79" s="18">
         <f>0.13*G74*(310)/5</f>
-        <v>31.202335427195692</v>
+        <v>28.719125637411043</v>
       </c>
       <c r="K79" s="17"/>
     </row>
@@ -6896,8 +7071,8 @@
         <v>1</v>
       </c>
       <c r="D83" s="33">
-        <f>(10.5+15)/3.281</f>
-        <v>7.7720207253886011</v>
+        <f>(10.667+15)/3.281</f>
+        <v>7.8229198415117347</v>
       </c>
       <c r="E83" s="33">
         <f>((F83/2)+0.5)/2</f>
@@ -6908,7 +7083,7 @@
       </c>
       <c r="G83" s="33">
         <f>PRODUCT(C83:F83)</f>
-        <v>11.658031088082902</v>
+        <v>11.734379762267602</v>
       </c>
       <c r="H83" s="17"/>
       <c r="I83" s="17">
@@ -6936,15 +7111,16 @@
         <v>4.3188052423041752</v>
       </c>
       <c r="E84" s="33">
-        <f>E70</f>
-        <v>0.45</v>
+        <f>1.5/3.281</f>
+        <v>0.45717768972874123</v>
       </c>
       <c r="F84" s="33">
-        <v>0.6</v>
+        <f>1.5/3.281</f>
+        <v>0.45717768972874123</v>
       </c>
       <c r="G84" s="33">
         <f>PRODUCT(C84:F84)</f>
-        <v>2.3321548308442548</v>
+        <v>1.8053594054236508</v>
       </c>
       <c r="H84" s="17"/>
       <c r="I84" s="17"/>
@@ -6966,14 +7142,16 @@
         <v>3.4044498628466928</v>
       </c>
       <c r="E85" s="33">
-        <v>0.45</v>
+        <f>1.5/3.281</f>
+        <v>0.45717768972874123</v>
       </c>
       <c r="F85" s="33">
-        <v>0.6</v>
+        <f>1.5/3.281</f>
+        <v>0.45717768972874123</v>
       </c>
       <c r="G85" s="33">
         <f>PRODUCT(C85:F85)</f>
-        <v>1.8384029259372141</v>
+        <v>1.4231379363854748</v>
       </c>
       <c r="H85" s="17"/>
       <c r="I85" s="17"/>
@@ -6995,7 +7173,7 @@
       <c r="F86" s="5"/>
       <c r="G86" s="6">
         <f>SUM(G82:G85)</f>
-        <v>53.331446205425173</v>
+        <v>52.465734464637528</v>
       </c>
       <c r="H86" s="7" t="s">
         <v>63</v>
@@ -7005,7 +7183,7 @@
       </c>
       <c r="J86" s="18">
         <f>G86*I86</f>
-        <v>479333.97214850655</v>
+        <v>471553.10219330312</v>
       </c>
       <c r="K86" s="5"/>
     </row>
@@ -7023,7 +7201,7 @@
       <c r="I87" s="17"/>
       <c r="J87" s="18">
         <f>0.13*G86*(5863.95)/5</f>
-        <v>8131.0562833838758</v>
+        <v>7999.0675339616919</v>
       </c>
       <c r="K87" s="17"/>
     </row>
@@ -7041,7 +7219,7 @@
       <c r="I88" s="17"/>
       <c r="J88" s="18">
         <f>0.13*G86*(6604.416)/5</f>
-        <v>9157.7994721784817</v>
+        <v>9009.1439399000919</v>
       </c>
       <c r="K88" s="17"/>
     </row>
@@ -7059,7 +7237,7 @@
       <c r="I89" s="17"/>
       <c r="J89" s="18">
         <f>0.13*G86*(14808.78)/5</f>
-        <v>20534.115002387382</v>
+        <v>20200.79149985611</v>
       </c>
       <c r="K89" s="17"/>
     </row>
@@ -7077,7 +7255,7 @@
       <c r="I90" s="17"/>
       <c r="J90" s="18">
         <f>0.13*G86*(310)/5</f>
-        <v>429.85145641572689</v>
+        <v>422.87381978497842</v>
       </c>
       <c r="K90" s="17"/>
     </row>
@@ -7354,7 +7532,7 @@
       <c r="I104" s="18"/>
       <c r="J104" s="18">
         <f>SUM(J9:J102)</f>
-        <v>827015.6448276072</v>
+        <v>803389.89058195078</v>
       </c>
       <c r="K104" s="25"/>
     </row>
@@ -7372,11 +7550,11 @@
       <c r="B106" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C106" s="53">
+      <c r="C106" s="68">
         <f>J104</f>
-        <v>827015.6448276072</v>
-      </c>
-      <c r="D106" s="54"/>
+        <v>803389.89058195078</v>
+      </c>
+      <c r="D106" s="69"/>
       <c r="E106" s="9">
         <v>100</v>
       </c>
@@ -7398,49 +7576,49 @@
       <c r="B107" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C107" s="57">
+      <c r="C107" s="72">
         <v>700000</v>
       </c>
-      <c r="D107" s="58"/>
+      <c r="D107" s="73"/>
       <c r="E107" s="9"/>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B108" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C108" s="57">
+      <c r="C108" s="72">
         <f>C107-C110-C111</f>
         <v>665000</v>
       </c>
-      <c r="D108" s="58"/>
+      <c r="D108" s="73"/>
       <c r="E108" s="9">
         <f>C108/C106*100</f>
-        <v>80.409603392523536</v>
+        <v>82.774255413930405</v>
       </c>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B109" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C109" s="59">
+      <c r="C109" s="74">
         <f>C106-C108</f>
-        <v>162015.6448276072</v>
-      </c>
-      <c r="D109" s="59"/>
+        <v>138389.89058195078</v>
+      </c>
+      <c r="D109" s="74"/>
       <c r="E109" s="9">
         <f>100-E108</f>
-        <v>19.590396607476464</v>
+        <v>17.225744586069595</v>
       </c>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B110" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C110" s="53">
+      <c r="C110" s="68">
         <f>C107*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D110" s="54"/>
+      <c r="D110" s="69"/>
       <c r="E110" s="9">
         <v>3</v>
       </c>
@@ -7449,17 +7627,24 @@
       <c r="B111" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C111" s="53">
+      <c r="C111" s="68">
         <f>C107*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D111" s="54"/>
+      <c r="D111" s="69"/>
       <c r="E111" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C110:D110"/>
     <mergeCell ref="C111:D111"/>
     <mergeCell ref="A7:F7"/>
@@ -7468,13 +7653,6 @@
     <mergeCell ref="C107:D107"/>
     <mergeCell ref="C108:D108"/>
     <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>

--- a/बजेट माग estimate/नगर बजेट estimate/तल्लो नंग्लेद्वारे चिहानपाटी/V-devithaan.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/तल्लो नंग्लेद्वारे चिहानपाटी/V-devithaan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50A8E425-C59D-47CC-835F-E70F2E3528E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482DC7D8-631A-4394-97CE-E3A41A48C7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,12 +11,13 @@
     <sheet name="estimate" sheetId="12" r:id="rId1"/>
     <sheet name="WCR" sheetId="13" r:id="rId2"/>
     <sheet name="V" sheetId="14" r:id="rId3"/>
+    <sheet name="With measurement" sheetId="15" state="hidden" r:id="rId4"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
+    <externalReference r:id="rId8"/>
   </externalReferences>
   <definedNames>
     <definedName name="description_103" localSheetId="1">#REF!</definedName>
@@ -24,6 +25,7 @@
     <definedName name="description_124" localSheetId="0">#REF!</definedName>
     <definedName name="description_124" localSheetId="2">#REF!</definedName>
     <definedName name="description_124" localSheetId="1">#REF!</definedName>
+    <definedName name="description_124" localSheetId="3">#REF!</definedName>
     <definedName name="description_124">#REF!</definedName>
     <definedName name="description_247" localSheetId="1">#REF!</definedName>
     <definedName name="description_247">[1]Abstract!$B$22</definedName>
@@ -40,10 +42,12 @@
     <definedName name="description_310" localSheetId="0">#REF!</definedName>
     <definedName name="description_310" localSheetId="2">#REF!</definedName>
     <definedName name="description_310" localSheetId="1">#REF!</definedName>
+    <definedName name="description_310" localSheetId="3">#REF!</definedName>
     <definedName name="description_310">#REF!</definedName>
     <definedName name="description_312" localSheetId="0">#REF!</definedName>
     <definedName name="description_312" localSheetId="2">#REF!</definedName>
     <definedName name="description_312" localSheetId="1">#REF!</definedName>
+    <definedName name="description_312" localSheetId="3">#REF!</definedName>
     <definedName name="description_312">#REF!</definedName>
     <definedName name="description_4">#REF!</definedName>
     <definedName name="description_5" localSheetId="1">#REF!</definedName>
@@ -51,12 +55,14 @@
     <definedName name="description_6" localSheetId="0">#REF!</definedName>
     <definedName name="description_6" localSheetId="2">#REF!</definedName>
     <definedName name="description_6" localSheetId="1">#REF!</definedName>
+    <definedName name="description_6" localSheetId="3">#REF!</definedName>
     <definedName name="description_6">#REF!</definedName>
     <definedName name="description_759" localSheetId="1">#REF!</definedName>
     <definedName name="description_759">[1]Abstract!$B$278</definedName>
     <definedName name="description_781" localSheetId="0">#REF!</definedName>
     <definedName name="description_781" localSheetId="2">#REF!</definedName>
     <definedName name="description_781" localSheetId="1">#REF!</definedName>
+    <definedName name="description_781" localSheetId="3">#REF!</definedName>
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783" localSheetId="1">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
@@ -65,9 +71,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$103</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">V!$A$1:$K$111</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">WCR!$A$1:$K$49</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'With measurement'!$A$1:$K$111</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">V!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">WCR!$1:$12</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'With measurement'!$1:$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -87,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="100">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -536,7 +544,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -552,12 +560,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -629,7 +631,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -793,14 +795,23 @@
     </xf>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -821,31 +832,22 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -860,23 +862,88 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="43" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1463,113 +1530,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="67"/>
     </row>
     <row r="2" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
+      <c r="B2" s="68"/>
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="69" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
     </row>
     <row r="5" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
-      <c r="K5" s="78"/>
+      <c r="B5" s="70"/>
+      <c r="C5" s="70"/>
+      <c r="D5" s="70"/>
+      <c r="E5" s="70"/>
+      <c r="F5" s="70"/>
+      <c r="G5" s="70"/>
+      <c r="H5" s="70"/>
+      <c r="I5" s="70"/>
+      <c r="J5" s="70"/>
+      <c r="K5" s="70"/>
     </row>
     <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="65"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="65"/>
+      <c r="F6" s="65"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="80" t="s">
+      <c r="H6" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="66"/>
+      <c r="K6" s="66"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="70" t="s">
+      <c r="A7" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
+      <c r="B7" s="73"/>
+      <c r="C7" s="73"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="73"/>
+      <c r="F7" s="73"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="71" t="s">
+      <c r="H7" s="74" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="71"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="74"/>
+      <c r="K7" s="74"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -3666,11 +3733,11 @@
       <c r="B98" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C98" s="68">
+      <c r="C98" s="71">
         <f>J96</f>
         <v>786973.54597297299</v>
       </c>
-      <c r="D98" s="69"/>
+      <c r="D98" s="72"/>
       <c r="E98" s="9">
         <v>100</v>
       </c>
@@ -3692,21 +3759,21 @@
       <c r="B99" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C99" s="72">
+      <c r="C99" s="75">
         <v>700000</v>
       </c>
-      <c r="D99" s="73"/>
+      <c r="D99" s="76"/>
       <c r="E99" s="9"/>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B100" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C100" s="72">
+      <c r="C100" s="75">
         <f>C99-C102-C103</f>
         <v>665000</v>
       </c>
-      <c r="D100" s="73"/>
+      <c r="D100" s="76"/>
       <c r="E100" s="9">
         <f>C100/C98*100</f>
         <v>84.500934421858958</v>
@@ -3716,11 +3783,11 @@
       <c r="B101" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C101" s="74">
+      <c r="C101" s="77">
         <f>C98-C100</f>
         <v>121973.54597297299</v>
       </c>
-      <c r="D101" s="74"/>
+      <c r="D101" s="77"/>
       <c r="E101" s="9">
         <f>100-E100</f>
         <v>15.499065578141042</v>
@@ -3730,11 +3797,11 @@
       <c r="B102" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C102" s="68">
+      <c r="C102" s="71">
         <f>C99*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D102" s="69"/>
+      <c r="D102" s="72"/>
       <c r="E102" s="9">
         <v>3</v>
       </c>
@@ -3743,24 +3810,17 @@
       <c r="B103" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C103" s="68">
+      <c r="C103" s="71">
         <f>C99*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D103" s="69"/>
+      <c r="D103" s="72"/>
       <c r="E103" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C102:D102"/>
     <mergeCell ref="C103:D103"/>
     <mergeCell ref="A7:F7"/>
@@ -3769,6 +3829,13 @@
     <mergeCell ref="C99:D99"/>
     <mergeCell ref="C100:D100"/>
     <mergeCell ref="C101:D101"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -3798,90 +3865,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="88"/>
-      <c r="K1" s="88"/>
+      <c r="B1" s="80"/>
+      <c r="C1" s="80"/>
+      <c r="D1" s="80"/>
+      <c r="E1" s="80"/>
+      <c r="F1" s="80"/>
+      <c r="G1" s="80"/>
+      <c r="H1" s="80"/>
+      <c r="I1" s="80"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="80"/>
     </row>
     <row r="2" spans="1:13" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="89" t="s">
+      <c r="A2" s="81" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="89"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
     </row>
     <row r="3" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="90" t="s">
+      <c r="A3" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="90"/>
-      <c r="C3" s="90"/>
-      <c r="D3" s="90"/>
-      <c r="E3" s="90"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="90"/>
-      <c r="I3" s="90"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="90"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
     </row>
     <row r="4" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="90" t="s">
+      <c r="A4" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="90"/>
-      <c r="G4" s="90"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="90"/>
-      <c r="K4" s="90"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="82"/>
+      <c r="J4" s="82"/>
+      <c r="K4" s="82"/>
     </row>
     <row r="5" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="91" t="s">
+      <c r="A5" s="83" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="91"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="91"/>
-      <c r="E5" s="91"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="91"/>
-      <c r="H5" s="91"/>
-      <c r="I5" s="91"/>
-      <c r="J5" s="91"/>
-      <c r="K5" s="91"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="83"/>
+      <c r="K5" s="83"/>
     </row>
     <row r="6" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>84</v>
       </c>
       <c r="B6" s="47"/>
-      <c r="C6" s="92">
+      <c r="C6" s="78">
         <f>F49</f>
         <v>786973.54597297299</v>
       </c>
-      <c r="D6" s="93"/>
+      <c r="D6" s="79"/>
       <c r="E6" s="48"/>
       <c r="F6" s="47"/>
       <c r="G6" s="47"/>
@@ -3889,11 +3956,11 @@
         <v>85</v>
       </c>
       <c r="I6" s="47"/>
-      <c r="J6" s="92">
+      <c r="J6" s="78">
         <f>I49</f>
-        <v>803383.79487942101</v>
-      </c>
-      <c r="K6" s="93"/>
+        <v>805280.71818867093</v>
+      </c>
+      <c r="K6" s="79"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
@@ -3911,15 +3978,15 @@
       <c r="K7" s="85"/>
     </row>
     <row r="8" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="79" t="str">
+      <c r="A8" s="65" t="str">
         <f>estimate!A6</f>
         <v xml:space="preserve">Project:- तल्लो नाङ्गलेद्वारे चिहानपाटी </v>
       </c>
-      <c r="B8" s="79"/>
-      <c r="C8" s="79"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="79"/>
-      <c r="F8" s="79"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
       <c r="I8" s="86" t="s">
         <v>88</v>
       </c>
@@ -3942,36 +4009,36 @@
       <c r="K9" s="86"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="82" t="s">
+      <c r="A11" s="89" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="82" t="s">
+      <c r="B11" s="89" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="82" t="s">
+      <c r="C11" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="83" t="s">
+      <c r="D11" s="90" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83" t="s">
+      <c r="E11" s="90"/>
+      <c r="F11" s="90"/>
+      <c r="G11" s="90" t="s">
         <v>93</v>
       </c>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="82" t="s">
+      <c r="H11" s="90"/>
+      <c r="I11" s="90"/>
+      <c r="J11" s="89" t="s">
         <v>94</v>
       </c>
-      <c r="K11" s="81" t="s">
+      <c r="K11" s="88" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="82"/>
-      <c r="B12" s="82"/>
-      <c r="C12" s="82"/>
+      <c r="A12" s="89"/>
+      <c r="B12" s="89"/>
+      <c r="C12" s="89"/>
       <c r="D12" s="50" t="s">
         <v>96</v>
       </c>
@@ -3990,8 +4057,8 @@
       <c r="I12" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="82"/>
-      <c r="K12" s="81"/>
+      <c r="J12" s="89"/>
+      <c r="K12" s="88"/>
     </row>
     <row r="13" spans="1:13" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
@@ -4424,7 +4491,7 @@
       <c r="J27" s="53"/>
       <c r="K27" s="54"/>
     </row>
-    <row r="28" spans="1:13" s="36" customFormat="1" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" s="36" customFormat="1" ht="63" x14ac:dyDescent="0.25">
       <c r="A28" s="51">
         <f>estimate!A57</f>
         <v>5</v>
@@ -4451,7 +4518,7 @@
       </c>
       <c r="G28" s="52">
         <f>V!G74</f>
-        <v>3.5631669525323875</v>
+        <v>3.4956669525323871</v>
       </c>
       <c r="H28" s="52">
         <f>V!I74</f>
@@ -4459,11 +4526,11 @@
       </c>
       <c r="I28" s="52">
         <f>G28*H28</f>
-        <v>39068.201524363256</v>
+        <v>38328.100474363251</v>
       </c>
       <c r="J28" s="53">
         <f>I28-F28</f>
-        <v>820.46868055452796</v>
+        <v>80.367630554523203</v>
       </c>
       <c r="K28" s="54"/>
       <c r="M28" s="36">
@@ -4488,11 +4555,11 @@
       <c r="H29" s="52"/>
       <c r="I29" s="52">
         <f>V!J75</f>
-        <v>1661.942758202104</v>
+        <v>1630.4592106521038</v>
       </c>
       <c r="J29" s="53">
         <f>I29-F29</f>
-        <v>34.902348425967148</v>
+        <v>3.4188008759670083</v>
       </c>
       <c r="K29" s="54"/>
       <c r="M29" s="36">
@@ -4517,11 +4584,11 @@
       <c r="H30" s="52"/>
       <c r="I30" s="52">
         <f>V!J76</f>
-        <v>661.85541089932894</v>
+        <v>649.31733989932889</v>
       </c>
       <c r="J30" s="53">
         <f t="shared" ref="J30:J33" si="4">I30-F30</f>
-        <v>13.899581104592357</v>
+        <v>1.3615101045922984</v>
       </c>
       <c r="K30" s="54"/>
     </row>
@@ -4542,11 +4609,11 @@
       <c r="H31" s="52"/>
       <c r="I31" s="52">
         <f>V!J77</f>
-        <v>1345.7726688286355</v>
+        <v>1320.2785911286353</v>
       </c>
       <c r="J31" s="53">
         <f t="shared" si="4"/>
-        <v>28.2624815793381</v>
+        <v>2.7684038793379386</v>
       </c>
       <c r="K31" s="54"/>
     </row>
@@ -4567,11 +4634,11 @@
       <c r="H32" s="52"/>
       <c r="I32" s="52">
         <f>V!J78</f>
-        <v>195.34255166082906</v>
+        <v>191.64201716082906</v>
       </c>
       <c r="J32" s="53">
         <f t="shared" si="4"/>
-        <v>4.102375829032411</v>
+        <v>0.40184132903240766</v>
       </c>
       <c r="K32" s="54"/>
     </row>
@@ -4592,11 +4659,11 @@
       <c r="H33" s="52"/>
       <c r="I33" s="52">
         <f>V!J79</f>
-        <v>28.719125637411043</v>
+        <v>28.175075637411044</v>
       </c>
       <c r="J33" s="53">
         <f t="shared" si="4"/>
-        <v>0.60312843179412923</v>
+        <v>5.9078431794130637E-2</v>
       </c>
       <c r="K33" s="54"/>
     </row>
@@ -4804,7 +4871,7 @@
       </c>
       <c r="G41" s="52">
         <f>V!G94</f>
-        <v>0</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="H41" s="52">
         <f>V!I94</f>
@@ -4812,11 +4879,11 @@
       </c>
       <c r="I41" s="52">
         <f>G41*H41</f>
-        <v>0</v>
+        <v>2441.9280000000003</v>
       </c>
       <c r="J41" s="53">
         <f>I41-F41</f>
-        <v>-2441.9280000000003</v>
+        <v>0</v>
       </c>
       <c r="K41" s="54"/>
       <c r="M41" s="36">
@@ -4841,11 +4908,11 @@
       <c r="H42" s="52"/>
       <c r="I42" s="52">
         <f>V!J95</f>
-        <v>0</v>
+        <v>268.85664000000008</v>
       </c>
       <c r="J42" s="53">
         <f>I42-F42</f>
-        <v>-268.85664000000008</v>
+        <v>0</v>
       </c>
       <c r="K42" s="54"/>
       <c r="M42" s="36">
@@ -5020,16 +5087,29 @@
       <c r="H49" s="63"/>
       <c r="I49" s="63">
         <f>SUM(I13:I47)</f>
-        <v>803383.79487942101</v>
+        <v>805280.71818867093</v>
       </c>
       <c r="J49" s="64">
         <f>I49-F49</f>
-        <v>16410.248906448018</v>
+        <v>18307.172215697938</v>
       </c>
       <c r="K49" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="I9:K9"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="A1:K1"/>
@@ -5037,19 +5117,6 @@
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
     <mergeCell ref="A5:K5"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:J12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5084,235 +5151,230 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
     </row>
     <row r="2" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="92" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="77"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="77" t="s">
+      <c r="A4" s="93" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="77"/>
-      <c r="C4" s="77"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="77"/>
-      <c r="G4" s="77"/>
-      <c r="H4" s="77"/>
-      <c r="I4" s="77"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
+      <c r="B4" s="93"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
     </row>
     <row r="5" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="94" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
-      <c r="K5" s="78"/>
+      <c r="B5" s="94"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="94"/>
+      <c r="G5" s="94"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="94"/>
+      <c r="K5" s="94"/>
     </row>
     <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="95" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="79"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="79"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="79"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="80" t="s">
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="96"/>
+      <c r="H6" s="97" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="70" t="s">
+      <c r="A7" s="98" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="70"/>
-      <c r="C7" s="70"/>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="71" t="s">
+      <c r="B7" s="98"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="98"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="100" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="71"/>
-      <c r="J7" s="71"/>
-      <c r="K7" s="71"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="100"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="102" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="103" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="103" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="J8" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="K8" s="104" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
+      <c r="A9" s="105">
         <v>1</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="106" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="107" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="108" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="41" t="s">
+      <c r="F9" s="108" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="41"/>
-      <c r="H9" s="7"/>
+      <c r="G9" s="108"/>
+      <c r="H9" s="109"/>
       <c r="I9" s="6"/>
-      <c r="J9" s="42"/>
-      <c r="K9" s="5"/>
+      <c r="J9" s="110"/>
+      <c r="K9" s="111"/>
     </row>
     <row r="10" spans="1:18" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="16"/>
-      <c r="B10" s="43" t="s">
+      <c r="A10" s="112"/>
+      <c r="B10" s="113" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="65">
+      <c r="C10" s="114">
         <f>4</f>
         <v>4</v>
       </c>
-      <c r="D10" s="66">
+      <c r="D10" s="115">
         <f>(12+1)/3.281</f>
         <v>3.9622066443157573</v>
       </c>
-      <c r="E10" s="66">
+      <c r="E10" s="115">
         <v>6.5</v>
       </c>
-      <c r="F10" s="66">
+      <c r="F10" s="115">
         <f t="shared" ref="F10:F31" si="0">PRODUCT(C10:E10)</f>
         <v>103.0173727522097</v>
       </c>
-      <c r="G10" s="66">
+      <c r="G10" s="115">
         <f t="shared" ref="G10:G31" si="1">F10</f>
         <v>103.0173727522097</v>
       </c>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="K10" s="27"/>
+      <c r="H10" s="110"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="110"/>
+      <c r="K10" s="116"/>
     </row>
     <row r="11" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="16"/>
-      <c r="B11" s="43" t="s">
+      <c r="A11" s="112"/>
+      <c r="B11" s="113" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="65">
+      <c r="C11" s="114">
         <v>4</v>
       </c>
-      <c r="D11" s="66">
+      <c r="D11" s="115">
         <f>11.5/3.281</f>
         <v>3.5050289545870159</v>
       </c>
-      <c r="E11" s="66">
+      <c r="E11" s="115">
         <v>6.5</v>
       </c>
-      <c r="F11" s="66">
+      <c r="F11" s="115">
         <f t="shared" si="0"/>
         <v>91.130752819262412</v>
       </c>
-      <c r="G11" s="66">
+      <c r="G11" s="115">
         <f t="shared" si="1"/>
         <v>91.130752819262412</v>
       </c>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42">
-        <f>20/3.281</f>
-        <v>6.0957025297165499</v>
-      </c>
-      <c r="K11" s="27"/>
+      <c r="H11" s="110"/>
+      <c r="I11" s="110"/>
+      <c r="J11" s="110"/>
+      <c r="K11" s="116"/>
       <c r="Q11" s="36">
         <f>PRODUCT(C11:D11)</f>
         <v>14.020115818348064</v>
@@ -5323,631 +5385,590 @@
       </c>
     </row>
     <row r="12" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
-      <c r="B12" s="43" t="s">
+      <c r="A12" s="112"/>
+      <c r="B12" s="113" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="65">
+      <c r="C12" s="114">
         <v>2</v>
       </c>
-      <c r="D12" s="66">
+      <c r="D12" s="115">
         <f>11.5/3.281</f>
         <v>3.5050289545870159</v>
       </c>
-      <c r="E12" s="66">
+      <c r="E12" s="115">
         <v>6.5</v>
       </c>
-      <c r="F12" s="66">
+      <c r="F12" s="115">
         <f t="shared" si="0"/>
         <v>45.565376409631206</v>
       </c>
-      <c r="G12" s="66">
+      <c r="G12" s="115">
         <f t="shared" si="1"/>
         <v>45.565376409631206</v>
       </c>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
-      <c r="K12" s="27"/>
+      <c r="H12" s="110"/>
+      <c r="I12" s="110"/>
+      <c r="J12" s="110"/>
+      <c r="K12" s="116"/>
     </row>
     <row r="13" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="16"/>
-      <c r="B13" s="43" t="s">
+      <c r="A13" s="112"/>
+      <c r="B13" s="113" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="65">
+      <c r="C13" s="114">
         <v>4</v>
       </c>
-      <c r="D13" s="66">
+      <c r="D13" s="115">
         <v>1.5</v>
       </c>
-      <c r="E13" s="66">
+      <c r="E13" s="115">
         <v>6.5</v>
       </c>
-      <c r="F13" s="66">
+      <c r="F13" s="115">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="G13" s="66">
+      <c r="G13" s="115">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="42"/>
-      <c r="K13" s="27"/>
+      <c r="H13" s="110"/>
+      <c r="I13" s="110"/>
+      <c r="J13" s="110"/>
+      <c r="K13" s="116"/>
     </row>
     <row r="14" spans="1:18" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16"/>
-      <c r="B14" s="43"/>
-      <c r="C14" s="65">
+      <c r="A14" s="112"/>
+      <c r="B14" s="113"/>
+      <c r="C14" s="114">
         <v>1</v>
       </c>
-      <c r="D14" s="66">
+      <c r="D14" s="115">
         <f>0.45</f>
         <v>0.45</v>
       </c>
-      <c r="E14" s="66">
+      <c r="E14" s="115">
         <v>6.5</v>
       </c>
-      <c r="F14" s="66">
+      <c r="F14" s="115">
         <f t="shared" ref="F14" si="2">PRODUCT(C14:E14)</f>
         <v>2.9250000000000003</v>
       </c>
-      <c r="G14" s="66">
+      <c r="G14" s="115">
         <f t="shared" ref="G14" si="3">F14</f>
         <v>2.9250000000000003</v>
       </c>
-      <c r="H14" s="42"/>
-      <c r="I14" s="42">
-        <f>22/12</f>
-        <v>1.8333333333333333</v>
-      </c>
-      <c r="J14" s="42"/>
-      <c r="K14" s="27"/>
+      <c r="H14" s="110"/>
+      <c r="I14" s="110"/>
+      <c r="J14" s="110"/>
+      <c r="K14" s="116"/>
     </row>
     <row r="15" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
-      <c r="B15" s="67" t="s">
+      <c r="A15" s="112"/>
+      <c r="B15" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="65">
+      <c r="C15" s="114">
         <v>2</v>
       </c>
-      <c r="D15" s="66">
+      <c r="D15" s="115">
         <f>9/3.281</f>
         <v>2.7430661383724475</v>
       </c>
-      <c r="E15" s="66">
+      <c r="E15" s="115">
         <v>4.43</v>
       </c>
-      <c r="F15" s="66">
+      <c r="F15" s="115">
         <f t="shared" si="0"/>
         <v>24.303565985979883</v>
       </c>
-      <c r="G15" s="66">
+      <c r="G15" s="115">
         <f t="shared" si="1"/>
         <v>24.303565985979883</v>
       </c>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42">
-        <f>110/12</f>
-        <v>9.1666666666666661</v>
-      </c>
-      <c r="J15" s="42"/>
-      <c r="K15" s="27"/>
+      <c r="H15" s="110"/>
+      <c r="I15" s="110"/>
+      <c r="J15" s="110"/>
+      <c r="K15" s="116"/>
     </row>
     <row r="16" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="16"/>
-      <c r="B16" s="43" t="s">
+      <c r="A16" s="112"/>
+      <c r="B16" s="113" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="65">
+      <c r="C16" s="114">
         <v>4</v>
       </c>
-      <c r="D16" s="66">
+      <c r="D16" s="115">
         <f>5.75/3.281</f>
         <v>1.752514477293508</v>
       </c>
-      <c r="E16" s="66">
+      <c r="E16" s="115">
         <v>4.43</v>
       </c>
-      <c r="F16" s="66">
+      <c r="F16" s="115">
         <f t="shared" si="0"/>
         <v>31.054556537640959</v>
       </c>
-      <c r="G16" s="66">
+      <c r="G16" s="115">
         <f t="shared" si="1"/>
         <v>31.054556537640959</v>
       </c>
-      <c r="H16" s="42"/>
-      <c r="I16" s="42">
-        <f>71/12</f>
-        <v>5.916666666666667</v>
-      </c>
-      <c r="J16" s="42"/>
-      <c r="K16" s="27"/>
+      <c r="H16" s="110"/>
+      <c r="I16" s="110"/>
+      <c r="J16" s="110"/>
+      <c r="K16" s="116"/>
     </row>
     <row r="17" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="16"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="65">
+      <c r="A17" s="112"/>
+      <c r="B17" s="113"/>
+      <c r="C17" s="114">
         <v>4</v>
       </c>
-      <c r="D17" s="66">
+      <c r="D17" s="115">
         <f>77/12/3.281</f>
         <v>1.9557045616173931</v>
       </c>
-      <c r="E17" s="66">
+      <c r="E17" s="115">
         <v>4.43</v>
       </c>
-      <c r="F17" s="66">
+      <c r="F17" s="115">
         <f t="shared" ref="F17" si="4">PRODUCT(C17:E17)</f>
         <v>34.655084831860208</v>
       </c>
-      <c r="G17" s="66">
+      <c r="G17" s="115">
         <f t="shared" ref="G17" si="5">F17</f>
         <v>34.655084831860208</v>
       </c>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42">
-        <f>77/12</f>
-        <v>6.416666666666667</v>
-      </c>
-      <c r="J17" s="42"/>
-      <c r="K17" s="27"/>
+      <c r="H17" s="110"/>
+      <c r="I17" s="110"/>
+      <c r="J17" s="110"/>
+      <c r="K17" s="116"/>
     </row>
     <row r="18" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="16"/>
-      <c r="B18" s="43" t="s">
+      <c r="A18" s="112"/>
+      <c r="B18" s="113" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="65">
+      <c r="C18" s="114">
         <f>4</f>
         <v>4</v>
       </c>
-      <c r="D18" s="66">
+      <c r="D18" s="115">
         <f>10.67/3.281</f>
         <v>3.2520572996037793</v>
       </c>
-      <c r="E18" s="66">
+      <c r="E18" s="115">
         <v>4.43</v>
       </c>
-      <c r="F18" s="66">
+      <c r="F18" s="115">
         <f t="shared" si="0"/>
         <v>57.626455348978965</v>
       </c>
-      <c r="G18" s="66">
+      <c r="G18" s="115">
         <f t="shared" si="1"/>
         <v>57.626455348978965</v>
       </c>
-      <c r="H18" s="42"/>
-      <c r="I18" s="42">
-        <f>128/12</f>
-        <v>10.666666666666666</v>
-      </c>
-      <c r="J18" s="42"/>
-      <c r="K18" s="27"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="110"/>
+      <c r="J18" s="110"/>
+      <c r="K18" s="116"/>
     </row>
     <row r="19" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="16"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="65">
+      <c r="A19" s="112"/>
+      <c r="B19" s="113"/>
+      <c r="C19" s="114">
         <f>4</f>
         <v>4</v>
       </c>
-      <c r="D19" s="66">
+      <c r="D19" s="115">
         <f>15/3.281</f>
         <v>4.5717768972874122</v>
       </c>
-      <c r="E19" s="66">
+      <c r="E19" s="115">
         <v>4.43</v>
       </c>
-      <c r="F19" s="66">
+      <c r="F19" s="115">
         <f t="shared" si="0"/>
         <v>81.011886619932937</v>
       </c>
-      <c r="G19" s="66">
+      <c r="G19" s="115">
         <f t="shared" si="1"/>
         <v>81.011886619932937</v>
       </c>
-      <c r="H19" s="42"/>
-      <c r="I19" s="42">
-        <f>183/12</f>
-        <v>15.25</v>
-      </c>
-      <c r="J19" s="42"/>
-      <c r="K19" s="27"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="116"/>
     </row>
     <row r="20" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="16"/>
-      <c r="B20" s="43" t="s">
+      <c r="A20" s="112"/>
+      <c r="B20" s="113" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="65">
+      <c r="C20" s="114">
         <f>4*1</f>
         <v>4</v>
       </c>
-      <c r="D20" s="66">
+      <c r="D20" s="115">
         <f>6.42/3.281</f>
         <v>1.9567205120390123</v>
       </c>
-      <c r="E20" s="66">
+      <c r="E20" s="115">
         <v>4.43</v>
       </c>
-      <c r="F20" s="66">
+      <c r="F20" s="115">
         <f t="shared" si="0"/>
         <v>34.673087473331293</v>
       </c>
-      <c r="G20" s="66">
+      <c r="G20" s="115">
         <f t="shared" si="1"/>
         <v>34.673087473331293</v>
       </c>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42">
-        <f>82/12</f>
-        <v>6.833333333333333</v>
-      </c>
-      <c r="J20" s="42"/>
-      <c r="K20" s="27"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="116"/>
     </row>
     <row r="21" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="16"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="65">
+      <c r="A21" s="112"/>
+      <c r="B21" s="113"/>
+      <c r="C21" s="114">
         <f>4*2</f>
         <v>8</v>
       </c>
-      <c r="D21" s="66">
+      <c r="D21" s="115">
         <f>6.42/3.281</f>
         <v>1.9567205120390123</v>
       </c>
-      <c r="E21" s="66">
+      <c r="E21" s="115">
         <v>4.43</v>
       </c>
-      <c r="F21" s="66">
+      <c r="F21" s="115">
         <f t="shared" ref="F21" si="6">PRODUCT(C21:E21)</f>
         <v>69.346174946662586</v>
       </c>
-      <c r="G21" s="66">
+      <c r="G21" s="115">
         <f t="shared" ref="G21" si="7">F21</f>
         <v>69.346174946662586</v>
       </c>
-      <c r="H21" s="42"/>
-      <c r="I21" s="42">
-        <f>(38+41)/12</f>
-        <v>6.583333333333333</v>
-      </c>
-      <c r="J21" s="42"/>
-      <c r="K21" s="27"/>
+      <c r="H21" s="110"/>
+      <c r="I21" s="110"/>
+      <c r="J21" s="110"/>
+      <c r="K21" s="116"/>
     </row>
     <row r="22" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="16"/>
-      <c r="B22" s="43" t="s">
+      <c r="A22" s="112"/>
+      <c r="B22" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="65">
+      <c r="C22" s="114">
         <v>4</v>
       </c>
-      <c r="D22" s="66">
+      <c r="D22" s="115">
         <f>8/12/3.281</f>
         <v>0.20319008432388497</v>
       </c>
-      <c r="E22" s="66">
+      <c r="E22" s="115">
         <v>4.43</v>
       </c>
-      <c r="F22" s="66">
+      <c r="F22" s="115">
         <f t="shared" si="0"/>
         <v>3.6005282942192416</v>
       </c>
-      <c r="G22" s="66">
+      <c r="G22" s="115">
         <f t="shared" si="1"/>
         <v>3.6005282942192416</v>
       </c>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42">
-        <f>8/12</f>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="J22" s="42"/>
-      <c r="K22" s="27"/>
+      <c r="H22" s="110"/>
+      <c r="I22" s="110"/>
+      <c r="J22" s="110"/>
+      <c r="K22" s="116"/>
     </row>
     <row r="23" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="16"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="65">
+      <c r="A23" s="112"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="114">
         <v>4</v>
       </c>
-      <c r="D23" s="66">
+      <c r="D23" s="115">
         <f>54/12/3.281</f>
         <v>1.3715330691862238</v>
       </c>
-      <c r="E23" s="66">
+      <c r="E23" s="115">
         <v>4.43</v>
       </c>
-      <c r="F23" s="66">
+      <c r="F23" s="115">
         <f t="shared" si="0"/>
         <v>24.303565985979883</v>
       </c>
-      <c r="G23" s="66">
+      <c r="G23" s="115">
         <f t="shared" si="1"/>
         <v>24.303565985979883</v>
       </c>
-      <c r="H23" s="42"/>
-      <c r="I23" s="42">
-        <f>54/12</f>
-        <v>4.5</v>
-      </c>
-      <c r="J23" s="42"/>
-      <c r="K23" s="27"/>
+      <c r="H23" s="110"/>
+      <c r="I23" s="110"/>
+      <c r="J23" s="110"/>
+      <c r="K23" s="116"/>
     </row>
     <row r="24" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="16"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="65">
+      <c r="A24" s="112"/>
+      <c r="B24" s="113"/>
+      <c r="C24" s="114">
         <v>4</v>
       </c>
-      <c r="D24" s="66">
+      <c r="D24" s="115">
         <f>105/12/3.281</f>
         <v>2.6668698567509903</v>
       </c>
-      <c r="E24" s="66">
+      <c r="E24" s="115">
         <v>4.43</v>
       </c>
-      <c r="F24" s="66">
+      <c r="F24" s="115">
         <f t="shared" ref="F24" si="8">PRODUCT(C24:E24)</f>
         <v>47.256933861627545</v>
       </c>
-      <c r="G24" s="66">
+      <c r="G24" s="115">
         <f t="shared" ref="G24" si="9">F24</f>
         <v>47.256933861627545</v>
       </c>
-      <c r="H24" s="42"/>
-      <c r="I24" s="42">
-        <f>105/12</f>
-        <v>8.75</v>
-      </c>
-      <c r="J24" s="42"/>
-      <c r="K24" s="27"/>
+      <c r="H24" s="110"/>
+      <c r="I24" s="110"/>
+      <c r="J24" s="110"/>
+      <c r="K24" s="116"/>
     </row>
     <row r="25" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="16"/>
-      <c r="B25" s="43" t="s">
+      <c r="A25" s="112"/>
+      <c r="B25" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="65">
+      <c r="C25" s="114">
         <v>4</v>
       </c>
-      <c r="D25" s="66">
+      <c r="D25" s="115">
         <f>75/12/3.281</f>
         <v>1.9049070405364217</v>
       </c>
-      <c r="E25" s="66">
+      <c r="E25" s="115">
         <v>4.43</v>
       </c>
-      <c r="F25" s="66">
+      <c r="F25" s="115">
         <f t="shared" si="0"/>
         <v>33.754952758305393</v>
       </c>
-      <c r="G25" s="66">
+      <c r="G25" s="115">
         <f t="shared" si="1"/>
         <v>33.754952758305393</v>
       </c>
-      <c r="H25" s="42"/>
-      <c r="I25" s="42">
-        <f>75/12</f>
-        <v>6.25</v>
-      </c>
-      <c r="J25" s="42"/>
-      <c r="K25" s="27"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="110"/>
+      <c r="J25" s="110"/>
+      <c r="K25" s="116"/>
     </row>
     <row r="26" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="16"/>
-      <c r="B26" s="43"/>
-      <c r="C26" s="65">
+      <c r="A26" s="112"/>
+      <c r="B26" s="113"/>
+      <c r="C26" s="114">
         <f>4*2</f>
         <v>8</v>
       </c>
-      <c r="D26" s="66">
+      <c r="D26" s="115">
         <f>(36+37)/12/3.281</f>
         <v>1.8541095194554504</v>
       </c>
-      <c r="E26" s="66">
+      <c r="E26" s="115">
         <v>4.43</v>
       </c>
-      <c r="F26" s="66">
+      <c r="F26" s="115">
         <f t="shared" ref="F26" si="10">PRODUCT(C26:E26)</f>
         <v>65.709641369501156</v>
       </c>
-      <c r="G26" s="66">
+      <c r="G26" s="115">
         <f t="shared" ref="G26" si="11">F26</f>
         <v>65.709641369501156</v>
       </c>
-      <c r="H26" s="42"/>
-      <c r="I26" s="42">
-        <f>(36+37)/12</f>
-        <v>6.083333333333333</v>
-      </c>
-      <c r="J26" s="42"/>
-      <c r="K26" s="27"/>
+      <c r="H26" s="110"/>
+      <c r="I26" s="110"/>
+      <c r="J26" s="110"/>
+      <c r="K26" s="116"/>
     </row>
     <row r="27" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="16"/>
-      <c r="B27" s="43" t="s">
+      <c r="A27" s="112"/>
+      <c r="B27" s="113" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="44">
+      <c r="C27" s="114">
         <v>1</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="115">
         <f>6/3.281</f>
         <v>1.8287107589149649</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="115">
         <v>3.01</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="115">
         <f t="shared" si="0"/>
         <v>5.5044193843340441</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="115">
         <f t="shared" si="1"/>
         <v>5.5044193843340441</v>
       </c>
-      <c r="H27" s="42"/>
-      <c r="I27" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="J27" s="42"/>
-      <c r="K27" s="27"/>
+      <c r="H27" s="110"/>
+      <c r="I27" s="110"/>
+      <c r="J27" s="110"/>
+      <c r="K27" s="116"/>
     </row>
     <row r="28" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="16"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="44">
+      <c r="A28" s="112"/>
+      <c r="B28" s="113"/>
+      <c r="C28" s="114">
         <v>4</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="115">
         <v>1.5</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="115">
         <v>3.01</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="115">
         <f t="shared" si="0"/>
         <v>18.059999999999999</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="115">
         <f t="shared" si="1"/>
         <v>18.059999999999999</v>
       </c>
-      <c r="H28" s="42"/>
-      <c r="I28" s="42"/>
-      <c r="J28" s="42"/>
-      <c r="K28" s="27"/>
+      <c r="H28" s="110"/>
+      <c r="I28" s="110"/>
+      <c r="J28" s="110"/>
+      <c r="K28" s="116"/>
     </row>
     <row r="29" spans="1:11" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="16"/>
-      <c r="B29" s="43" t="s">
+      <c r="A29" s="112"/>
+      <c r="B29" s="113" t="s">
         <v>99</v>
       </c>
-      <c r="C29" s="44">
+      <c r="C29" s="114">
         <v>1</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="115">
         <f>(7+65/12+76/12+74/12+6)/3.281</f>
         <v>9.4229401605201666</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="115">
         <v>2.2599999999999998</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="115">
         <f t="shared" si="0"/>
         <v>21.295844762775573</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="115">
         <f t="shared" si="1"/>
         <v>21.295844762775573</v>
       </c>
-      <c r="H29" s="42"/>
-      <c r="I29" s="42"/>
-      <c r="J29" s="42"/>
-      <c r="K29" s="27"/>
+      <c r="H29" s="110"/>
+      <c r="I29" s="110"/>
+      <c r="J29" s="110"/>
+      <c r="K29" s="116"/>
     </row>
     <row r="30" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="16"/>
-      <c r="B30" s="43"/>
-      <c r="C30" s="44">
+      <c r="A30" s="112"/>
+      <c r="B30" s="113"/>
+      <c r="C30" s="114">
         <v>2</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="115">
         <f>(69+72+75+64+82)/12/3.281</f>
         <v>9.1943513156557959</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="115">
         <v>2.2599999999999998</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="115">
         <f t="shared" si="0"/>
         <v>41.558467946764196</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="115">
         <f t="shared" si="1"/>
         <v>41.558467946764196</v>
       </c>
-      <c r="H30" s="42"/>
-      <c r="I30" s="42"/>
-      <c r="J30" s="42"/>
-      <c r="K30" s="27"/>
+      <c r="H30" s="110"/>
+      <c r="I30" s="110"/>
+      <c r="J30" s="110"/>
+      <c r="K30" s="116"/>
     </row>
     <row r="31" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="16"/>
-      <c r="B31" s="43"/>
-      <c r="C31" s="44">
+      <c r="A31" s="112"/>
+      <c r="B31" s="113"/>
+      <c r="C31" s="114">
         <v>1</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="115">
         <f>82/12/3.281</f>
         <v>2.0826983643198211</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="115">
         <v>2.2599999999999998</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="115">
         <f t="shared" si="0"/>
         <v>4.7068983033627951</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="115">
         <f t="shared" si="1"/>
         <v>4.7068983033627951</v>
       </c>
-      <c r="H31" s="42"/>
-      <c r="I31" s="42"/>
-      <c r="J31" s="42"/>
-      <c r="K31" s="27"/>
+      <c r="H31" s="110"/>
+      <c r="I31" s="110"/>
+      <c r="J31" s="110"/>
+      <c r="K31" s="116"/>
     </row>
     <row r="32" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="43" t="s">
+      <c r="A32" s="105"/>
+      <c r="B32" s="113" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="3"/>
+      <c r="C32" s="107"/>
       <c r="D32" s="4"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="42">
+      <c r="E32" s="111"/>
+      <c r="F32" s="111"/>
+      <c r="G32" s="110">
         <f>SUM(G10:G31)</f>
         <v>880.06056639235987</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="H32" s="109" t="s">
         <v>40</v>
       </c>
       <c r="I32" s="6">
         <v>182.51</v>
       </c>
-      <c r="J32" s="42">
+      <c r="J32" s="110">
         <f>G32*I32</f>
         <v>160619.8539722696</v>
       </c>
-      <c r="K32" s="5"/>
+      <c r="K32" s="111"/>
     </row>
     <row r="33" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2"/>
-      <c r="B33" s="43" t="s">
+      <c r="A33" s="105"/>
+      <c r="B33" s="113" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="3"/>
+      <c r="C33" s="107"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="7"/>
+      <c r="E33" s="111"/>
+      <c r="F33" s="111"/>
+      <c r="G33" s="110"/>
+      <c r="H33" s="109"/>
       <c r="I33" s="6"/>
-      <c r="J33" s="42">
+      <c r="J33" s="110">
         <f>0.13*G32*(1871.42/18.94)</f>
         <v>11304.391915023165</v>
       </c>
-      <c r="K33" s="5"/>
+      <c r="K33" s="111"/>
     </row>
     <row r="34" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
@@ -6001,10 +6022,7 @@
         <v>21.782336229550666</v>
       </c>
       <c r="H36" s="7"/>
-      <c r="I36" s="6">
-        <f>183/12</f>
-        <v>15.25</v>
-      </c>
+      <c r="I36" s="6"/>
       <c r="J36" s="42"/>
       <c r="K36" s="5"/>
     </row>
@@ -6177,7 +6195,7 @@
         <f>E54</f>
         <v>1.75</v>
       </c>
-      <c r="F45" s="17">
+      <c r="F45" s="33">
         <v>0.9</v>
       </c>
       <c r="G45" s="33">
@@ -6199,7 +6217,7 @@
         <f>D55</f>
         <v>7.8229198415117347</v>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="33">
         <f>E55</f>
         <v>1</v>
       </c>
@@ -6226,7 +6244,7 @@
       <c r="D47" s="33">
         <v>0.6</v>
       </c>
-      <c r="E47" s="17">
+      <c r="E47" s="33">
         <v>0.6</v>
       </c>
       <c r="F47" s="17">
@@ -6279,7 +6297,7 @@
       <c r="D49" s="33">
         <v>0.3</v>
       </c>
-      <c r="E49" s="17">
+      <c r="E49" s="33">
         <v>0.3</v>
       </c>
       <c r="F49" s="33">
@@ -6405,7 +6423,7 @@
         <f>D67</f>
         <v>7.8229198415117347</v>
       </c>
-      <c r="E55" s="17">
+      <c r="E55" s="33">
         <f>E67</f>
         <v>1</v>
       </c>
@@ -6863,11 +6881,11 @@
         <v>0.3</v>
       </c>
       <c r="F73" s="33">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="G73" s="33">
         <f t="shared" si="15"/>
-        <v>0.20249999999999999</v>
+        <v>0.13499999999999998</v>
       </c>
       <c r="H73" s="17"/>
       <c r="I73" s="17"/>
@@ -6885,7 +6903,7 @@
       <c r="F74" s="5"/>
       <c r="G74" s="42">
         <f>SUM(G65:G73)</f>
-        <v>3.5631669525323875</v>
+        <v>3.4956669525323871</v>
       </c>
       <c r="H74" s="7" t="s">
         <v>63</v>
@@ -6895,7 +6913,7 @@
       </c>
       <c r="J74" s="42">
         <f>G74*I74</f>
-        <v>39068.201524363256</v>
+        <v>38328.100474363251</v>
       </c>
       <c r="K74" s="5"/>
     </row>
@@ -6913,7 +6931,7 @@
       <c r="I75" s="17"/>
       <c r="J75" s="18">
         <f>0.13*G74*53818.03/15</f>
-        <v>1661.942758202104</v>
+        <v>1630.4592106521038</v>
       </c>
       <c r="K75" s="17"/>
     </row>
@@ -6931,7 +6949,7 @@
       <c r="I76" s="17"/>
       <c r="J76" s="18">
         <f>0.13*G74*21432.6/15</f>
-        <v>661.85541089932894</v>
+        <v>649.31733989932889</v>
       </c>
       <c r="K76" s="17"/>
     </row>
@@ -6949,7 +6967,7 @@
       <c r="I77" s="17"/>
       <c r="J77" s="18">
         <f>0.13*G74*(25719.12+13573.98+4286.52)/15</f>
-        <v>1345.7726688286355</v>
+        <v>1320.2785911286353</v>
       </c>
       <c r="K77" s="17"/>
     </row>
@@ -6967,7 +6985,7 @@
       <c r="I78" s="17"/>
       <c r="J78" s="18">
         <f>0.13*G74*(6325.7/15)</f>
-        <v>195.34255166082906</v>
+        <v>191.64201716082906</v>
       </c>
       <c r="K78" s="17"/>
     </row>
@@ -6985,7 +7003,7 @@
       <c r="I79" s="17"/>
       <c r="J79" s="18">
         <f>0.13*G74*(310)/5</f>
-        <v>28.719125637411043</v>
+        <v>28.175075637411044</v>
       </c>
       <c r="K79" s="17"/>
     </row>
@@ -7044,10 +7062,7 @@
         <v>37.502857360560803</v>
       </c>
       <c r="H82" s="17"/>
-      <c r="I82" s="17">
-        <f>31.25/3.281</f>
-        <v>9.5245352026821095</v>
-      </c>
+      <c r="I82" s="17"/>
       <c r="J82" s="17"/>
       <c r="K82" s="17"/>
       <c r="M82" s="33">
@@ -7086,10 +7101,7 @@
         <v>11.734379762267602</v>
       </c>
       <c r="H83" s="17"/>
-      <c r="I83" s="17">
-        <f>(10.75+15)/3.281</f>
-        <v>7.8482170070100574</v>
-      </c>
+      <c r="I83" s="17"/>
       <c r="J83" s="17"/>
       <c r="K83" s="17"/>
       <c r="M83" s="35"/>
@@ -7295,19 +7307,19 @@
         <v>69</v>
       </c>
       <c r="C93" s="17">
-        <v>0</v>
-      </c>
-      <c r="D93" s="17">
+        <v>1</v>
+      </c>
+      <c r="D93" s="33">
         <f>1.5</f>
         <v>1.5</v>
       </c>
-      <c r="E93" s="17">
+      <c r="E93" s="33">
         <v>1.6</v>
       </c>
       <c r="F93" s="17"/>
       <c r="G93" s="33">
         <f>PRODUCT(C93:F93)</f>
-        <v>0</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="H93" s="17"/>
       <c r="I93" s="17"/>
@@ -7325,7 +7337,7 @@
       <c r="F94" s="5"/>
       <c r="G94" s="6">
         <f>SUM(G93)</f>
-        <v>0</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="H94" s="7" t="s">
         <v>54</v>
@@ -7335,7 +7347,7 @@
       </c>
       <c r="J94" s="18">
         <f>G94*I94</f>
-        <v>0</v>
+        <v>2441.9280000000003</v>
       </c>
       <c r="K94" s="5"/>
     </row>
@@ -7353,7 +7365,7 @@
       <c r="I95" s="17"/>
       <c r="J95" s="18">
         <f>0.13*G94*(8617.2)/10</f>
-        <v>0</v>
+        <v>268.85664000000008</v>
       </c>
       <c r="K95" s="17"/>
     </row>
@@ -7532,7 +7544,7 @@
       <c r="I104" s="18"/>
       <c r="J104" s="18">
         <f>SUM(J9:J102)</f>
-        <v>803389.89058195078</v>
+        <v>805280.71818867093</v>
       </c>
       <c r="K104" s="25"/>
     </row>
@@ -7550,11 +7562,11 @@
       <c r="B106" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C106" s="68">
+      <c r="C106" s="71">
         <f>J104</f>
-        <v>803389.89058195078</v>
-      </c>
-      <c r="D106" s="69"/>
+        <v>805280.71818867093</v>
+      </c>
+      <c r="D106" s="72"/>
       <c r="E106" s="9">
         <v>100</v>
       </c>
@@ -7576,49 +7588,49 @@
       <c r="B107" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C107" s="72">
+      <c r="C107" s="75">
         <v>700000</v>
       </c>
-      <c r="D107" s="73"/>
+      <c r="D107" s="76"/>
       <c r="E107" s="9"/>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B108" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C108" s="72">
+      <c r="C108" s="75">
         <f>C107-C110-C111</f>
         <v>665000</v>
       </c>
-      <c r="D108" s="73"/>
+      <c r="D108" s="76"/>
       <c r="E108" s="9">
         <f>C108/C106*100</f>
-        <v>82.774255413930405</v>
+        <v>82.579898534736273</v>
       </c>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B109" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C109" s="74">
+      <c r="C109" s="77">
         <f>C106-C108</f>
-        <v>138389.89058195078</v>
-      </c>
-      <c r="D109" s="74"/>
+        <v>140280.71818867093</v>
+      </c>
+      <c r="D109" s="77"/>
       <c r="E109" s="9">
         <f>100-E108</f>
-        <v>17.225744586069595</v>
+        <v>17.420101465263727</v>
       </c>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B110" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C110" s="68">
+      <c r="C110" s="71">
         <f>C107*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D110" s="69"/>
+      <c r="D110" s="72"/>
       <c r="E110" s="9">
         <v>3</v>
       </c>
@@ -7627,24 +7639,17 @@
       <c r="B111" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C111" s="68">
+      <c r="C111" s="71">
         <f>C107*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D111" s="69"/>
+      <c r="D111" s="72"/>
       <c r="E111" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C110:D110"/>
     <mergeCell ref="C111:D111"/>
     <mergeCell ref="A7:F7"/>
@@ -7653,6 +7658,2612 @@
     <mergeCell ref="C107:D107"/>
     <mergeCell ref="C108:D108"/>
     <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{599ED376-89D8-4E35-8A2B-E6A997628D72}">
+  <dimension ref="A1:S111"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="19" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="19" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="19"/>
+    <col min="8" max="8" width="5" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" style="19" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" style="19"/>
+    <col min="13" max="16" width="0" style="19" hidden="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="91"/>
+      <c r="H1" s="91"/>
+      <c r="I1" s="91"/>
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+    </row>
+    <row r="2" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="92" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="92"/>
+      <c r="C2" s="92"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="93" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="93"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="93" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="93"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
+      <c r="H4" s="93"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="93"/>
+    </row>
+    <row r="5" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="94" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="94"/>
+      <c r="C5" s="94"/>
+      <c r="D5" s="94"/>
+      <c r="E5" s="94"/>
+      <c r="F5" s="94"/>
+      <c r="G5" s="94"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="94"/>
+      <c r="K5" s="94"/>
+    </row>
+    <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="95" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="95"/>
+      <c r="C6" s="95"/>
+      <c r="D6" s="95"/>
+      <c r="E6" s="95"/>
+      <c r="F6" s="95"/>
+      <c r="G6" s="96"/>
+      <c r="H6" s="97" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="97"/>
+      <c r="J6" s="97"/>
+      <c r="K6" s="97"/>
+    </row>
+    <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="98" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="98"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="98"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="100" t="s">
+        <v>78</v>
+      </c>
+      <c r="I7" s="100"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="100"/>
+    </row>
+    <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="101" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="102" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="103" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="103" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="103" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="103" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="103" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="103" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="104" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="105">
+        <v>1</v>
+      </c>
+      <c r="B9" s="106" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="107" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="108" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="108"/>
+      <c r="H9" s="109"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="110"/>
+      <c r="K9" s="111"/>
+    </row>
+    <row r="10" spans="1:18" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="112"/>
+      <c r="B10" s="113" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="114">
+        <f>4</f>
+        <v>4</v>
+      </c>
+      <c r="D10" s="115">
+        <f>(12+1)/3.281</f>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E10" s="115">
+        <v>6.5</v>
+      </c>
+      <c r="F10" s="115">
+        <f t="shared" ref="F10:F31" si="0">PRODUCT(C10:E10)</f>
+        <v>103.0173727522097</v>
+      </c>
+      <c r="G10" s="115">
+        <f t="shared" ref="G10:G31" si="1">F10</f>
+        <v>103.0173727522097</v>
+      </c>
+      <c r="H10" s="110"/>
+      <c r="I10" s="110"/>
+      <c r="J10" s="110" t="s">
+        <v>97</v>
+      </c>
+      <c r="K10" s="116"/>
+    </row>
+    <row r="11" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="112"/>
+      <c r="B11" s="113" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="114">
+        <v>4</v>
+      </c>
+      <c r="D11" s="115">
+        <f>11.5/3.281</f>
+        <v>3.5050289545870159</v>
+      </c>
+      <c r="E11" s="115">
+        <v>6.5</v>
+      </c>
+      <c r="F11" s="115">
+        <f t="shared" si="0"/>
+        <v>91.130752819262412</v>
+      </c>
+      <c r="G11" s="115">
+        <f t="shared" si="1"/>
+        <v>91.130752819262412</v>
+      </c>
+      <c r="H11" s="110"/>
+      <c r="I11" s="110"/>
+      <c r="J11" s="110">
+        <f>20/3.281</f>
+        <v>6.0957025297165499</v>
+      </c>
+      <c r="K11" s="116"/>
+      <c r="Q11" s="36">
+        <f>PRODUCT(C11:D11)</f>
+        <v>14.020115818348064</v>
+      </c>
+      <c r="R11" s="36">
+        <f>CONVERT(Q11,"m","ft")</f>
+        <v>45.997755309540885</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="112"/>
+      <c r="B12" s="113" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="114">
+        <v>2</v>
+      </c>
+      <c r="D12" s="115">
+        <f>11.5/3.281</f>
+        <v>3.5050289545870159</v>
+      </c>
+      <c r="E12" s="115">
+        <v>6.5</v>
+      </c>
+      <c r="F12" s="115">
+        <f t="shared" si="0"/>
+        <v>45.565376409631206</v>
+      </c>
+      <c r="G12" s="115">
+        <f t="shared" si="1"/>
+        <v>45.565376409631206</v>
+      </c>
+      <c r="H12" s="110"/>
+      <c r="I12" s="110"/>
+      <c r="J12" s="110"/>
+      <c r="K12" s="116"/>
+    </row>
+    <row r="13" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="112"/>
+      <c r="B13" s="113" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="114">
+        <v>4</v>
+      </c>
+      <c r="D13" s="115">
+        <v>1.5</v>
+      </c>
+      <c r="E13" s="115">
+        <v>6.5</v>
+      </c>
+      <c r="F13" s="115">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="G13" s="115">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="H13" s="110"/>
+      <c r="I13" s="110"/>
+      <c r="J13" s="110"/>
+      <c r="K13" s="116"/>
+    </row>
+    <row r="14" spans="1:18" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="112"/>
+      <c r="B14" s="113"/>
+      <c r="C14" s="114">
+        <v>1</v>
+      </c>
+      <c r="D14" s="115">
+        <f>0.45</f>
+        <v>0.45</v>
+      </c>
+      <c r="E14" s="115">
+        <v>6.5</v>
+      </c>
+      <c r="F14" s="115">
+        <f t="shared" si="0"/>
+        <v>2.9250000000000003</v>
+      </c>
+      <c r="G14" s="115">
+        <f t="shared" si="1"/>
+        <v>2.9250000000000003</v>
+      </c>
+      <c r="H14" s="110"/>
+      <c r="I14" s="110">
+        <f>22/12</f>
+        <v>1.8333333333333333</v>
+      </c>
+      <c r="J14" s="110"/>
+      <c r="K14" s="116"/>
+    </row>
+    <row r="15" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="112"/>
+      <c r="B15" s="113" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="114">
+        <v>2</v>
+      </c>
+      <c r="D15" s="115">
+        <f>9/3.281</f>
+        <v>2.7430661383724475</v>
+      </c>
+      <c r="E15" s="115">
+        <v>4.43</v>
+      </c>
+      <c r="F15" s="115">
+        <f t="shared" si="0"/>
+        <v>24.303565985979883</v>
+      </c>
+      <c r="G15" s="115">
+        <f t="shared" si="1"/>
+        <v>24.303565985979883</v>
+      </c>
+      <c r="H15" s="110"/>
+      <c r="I15" s="110">
+        <f>110/12</f>
+        <v>9.1666666666666661</v>
+      </c>
+      <c r="J15" s="110"/>
+      <c r="K15" s="116"/>
+    </row>
+    <row r="16" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="112"/>
+      <c r="B16" s="113" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="114">
+        <v>4</v>
+      </c>
+      <c r="D16" s="115">
+        <f>5.75/3.281</f>
+        <v>1.752514477293508</v>
+      </c>
+      <c r="E16" s="115">
+        <v>4.43</v>
+      </c>
+      <c r="F16" s="115">
+        <f t="shared" si="0"/>
+        <v>31.054556537640959</v>
+      </c>
+      <c r="G16" s="115">
+        <f t="shared" si="1"/>
+        <v>31.054556537640959</v>
+      </c>
+      <c r="H16" s="110"/>
+      <c r="I16" s="110">
+        <f>71/12</f>
+        <v>5.916666666666667</v>
+      </c>
+      <c r="J16" s="110"/>
+      <c r="K16" s="116"/>
+    </row>
+    <row r="17" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="112"/>
+      <c r="B17" s="113"/>
+      <c r="C17" s="114">
+        <v>4</v>
+      </c>
+      <c r="D17" s="115">
+        <f>77/12/3.281</f>
+        <v>1.9557045616173931</v>
+      </c>
+      <c r="E17" s="115">
+        <v>4.43</v>
+      </c>
+      <c r="F17" s="115">
+        <f t="shared" si="0"/>
+        <v>34.655084831860208</v>
+      </c>
+      <c r="G17" s="115">
+        <f t="shared" si="1"/>
+        <v>34.655084831860208</v>
+      </c>
+      <c r="H17" s="110"/>
+      <c r="I17" s="110">
+        <f>77/12</f>
+        <v>6.416666666666667</v>
+      </c>
+      <c r="J17" s="110"/>
+      <c r="K17" s="116"/>
+    </row>
+    <row r="18" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="112"/>
+      <c r="B18" s="113" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="114">
+        <f>4</f>
+        <v>4</v>
+      </c>
+      <c r="D18" s="115">
+        <f>10.67/3.281</f>
+        <v>3.2520572996037793</v>
+      </c>
+      <c r="E18" s="115">
+        <v>4.43</v>
+      </c>
+      <c r="F18" s="115">
+        <f t="shared" si="0"/>
+        <v>57.626455348978965</v>
+      </c>
+      <c r="G18" s="115">
+        <f t="shared" si="1"/>
+        <v>57.626455348978965</v>
+      </c>
+      <c r="H18" s="110"/>
+      <c r="I18" s="110">
+        <f>128/12</f>
+        <v>10.666666666666666</v>
+      </c>
+      <c r="J18" s="110"/>
+      <c r="K18" s="116"/>
+    </row>
+    <row r="19" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="112"/>
+      <c r="B19" s="113"/>
+      <c r="C19" s="114">
+        <f>4</f>
+        <v>4</v>
+      </c>
+      <c r="D19" s="115">
+        <f>15/3.281</f>
+        <v>4.5717768972874122</v>
+      </c>
+      <c r="E19" s="115">
+        <v>4.43</v>
+      </c>
+      <c r="F19" s="115">
+        <f t="shared" si="0"/>
+        <v>81.011886619932937</v>
+      </c>
+      <c r="G19" s="115">
+        <f t="shared" si="1"/>
+        <v>81.011886619932937</v>
+      </c>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110">
+        <f>183/12</f>
+        <v>15.25</v>
+      </c>
+      <c r="J19" s="110"/>
+      <c r="K19" s="116"/>
+    </row>
+    <row r="20" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="112"/>
+      <c r="B20" s="113" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="114">
+        <f>4*1</f>
+        <v>4</v>
+      </c>
+      <c r="D20" s="115">
+        <f>6.42/3.281</f>
+        <v>1.9567205120390123</v>
+      </c>
+      <c r="E20" s="115">
+        <v>4.43</v>
+      </c>
+      <c r="F20" s="115">
+        <f t="shared" si="0"/>
+        <v>34.673087473331293</v>
+      </c>
+      <c r="G20" s="115">
+        <f t="shared" si="1"/>
+        <v>34.673087473331293</v>
+      </c>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110">
+        <f>82/12</f>
+        <v>6.833333333333333</v>
+      </c>
+      <c r="J20" s="110"/>
+      <c r="K20" s="116"/>
+    </row>
+    <row r="21" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="112"/>
+      <c r="B21" s="113"/>
+      <c r="C21" s="114">
+        <f>4*2</f>
+        <v>8</v>
+      </c>
+      <c r="D21" s="115">
+        <f>6.42/3.281</f>
+        <v>1.9567205120390123</v>
+      </c>
+      <c r="E21" s="115">
+        <v>4.43</v>
+      </c>
+      <c r="F21" s="115">
+        <f t="shared" si="0"/>
+        <v>69.346174946662586</v>
+      </c>
+      <c r="G21" s="115">
+        <f t="shared" si="1"/>
+        <v>69.346174946662586</v>
+      </c>
+      <c r="H21" s="110"/>
+      <c r="I21" s="110">
+        <f>(38+41)/12</f>
+        <v>6.583333333333333</v>
+      </c>
+      <c r="J21" s="110"/>
+      <c r="K21" s="116"/>
+    </row>
+    <row r="22" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="112"/>
+      <c r="B22" s="113" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="114">
+        <v>4</v>
+      </c>
+      <c r="D22" s="115">
+        <f>8/12/3.281</f>
+        <v>0.20319008432388497</v>
+      </c>
+      <c r="E22" s="115">
+        <v>4.43</v>
+      </c>
+      <c r="F22" s="115">
+        <f t="shared" si="0"/>
+        <v>3.6005282942192416</v>
+      </c>
+      <c r="G22" s="115">
+        <f t="shared" si="1"/>
+        <v>3.6005282942192416</v>
+      </c>
+      <c r="H22" s="110"/>
+      <c r="I22" s="110">
+        <f>8/12</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="J22" s="110"/>
+      <c r="K22" s="116"/>
+    </row>
+    <row r="23" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="112"/>
+      <c r="B23" s="113"/>
+      <c r="C23" s="114">
+        <v>4</v>
+      </c>
+      <c r="D23" s="115">
+        <f>54/12/3.281</f>
+        <v>1.3715330691862238</v>
+      </c>
+      <c r="E23" s="115">
+        <v>4.43</v>
+      </c>
+      <c r="F23" s="115">
+        <f t="shared" si="0"/>
+        <v>24.303565985979883</v>
+      </c>
+      <c r="G23" s="115">
+        <f t="shared" si="1"/>
+        <v>24.303565985979883</v>
+      </c>
+      <c r="H23" s="110"/>
+      <c r="I23" s="110">
+        <f>54/12</f>
+        <v>4.5</v>
+      </c>
+      <c r="J23" s="110"/>
+      <c r="K23" s="116"/>
+    </row>
+    <row r="24" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="112"/>
+      <c r="B24" s="113"/>
+      <c r="C24" s="114">
+        <v>4</v>
+      </c>
+      <c r="D24" s="115">
+        <f>105/12/3.281</f>
+        <v>2.6668698567509903</v>
+      </c>
+      <c r="E24" s="115">
+        <v>4.43</v>
+      </c>
+      <c r="F24" s="115">
+        <f t="shared" si="0"/>
+        <v>47.256933861627545</v>
+      </c>
+      <c r="G24" s="115">
+        <f t="shared" si="1"/>
+        <v>47.256933861627545</v>
+      </c>
+      <c r="H24" s="110"/>
+      <c r="I24" s="110">
+        <f>105/12</f>
+        <v>8.75</v>
+      </c>
+      <c r="J24" s="110"/>
+      <c r="K24" s="116"/>
+    </row>
+    <row r="25" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="112"/>
+      <c r="B25" s="113" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="114">
+        <v>4</v>
+      </c>
+      <c r="D25" s="115">
+        <f>75/12/3.281</f>
+        <v>1.9049070405364217</v>
+      </c>
+      <c r="E25" s="115">
+        <v>4.43</v>
+      </c>
+      <c r="F25" s="115">
+        <f t="shared" si="0"/>
+        <v>33.754952758305393</v>
+      </c>
+      <c r="G25" s="115">
+        <f t="shared" si="1"/>
+        <v>33.754952758305393</v>
+      </c>
+      <c r="H25" s="110"/>
+      <c r="I25" s="110">
+        <f>75/12</f>
+        <v>6.25</v>
+      </c>
+      <c r="J25" s="110"/>
+      <c r="K25" s="116"/>
+    </row>
+    <row r="26" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="112"/>
+      <c r="B26" s="113"/>
+      <c r="C26" s="114">
+        <f>4*2</f>
+        <v>8</v>
+      </c>
+      <c r="D26" s="115">
+        <f>(36+37)/12/3.281</f>
+        <v>1.8541095194554504</v>
+      </c>
+      <c r="E26" s="115">
+        <v>4.43</v>
+      </c>
+      <c r="F26" s="115">
+        <f t="shared" si="0"/>
+        <v>65.709641369501156</v>
+      </c>
+      <c r="G26" s="115">
+        <f t="shared" si="1"/>
+        <v>65.709641369501156</v>
+      </c>
+      <c r="H26" s="110"/>
+      <c r="I26" s="110">
+        <f>(36+37)/12</f>
+        <v>6.083333333333333</v>
+      </c>
+      <c r="J26" s="110"/>
+      <c r="K26" s="116"/>
+    </row>
+    <row r="27" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="112"/>
+      <c r="B27" s="113" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="114">
+        <v>1</v>
+      </c>
+      <c r="D27" s="115">
+        <f>6/3.281</f>
+        <v>1.8287107589149649</v>
+      </c>
+      <c r="E27" s="115">
+        <v>3.01</v>
+      </c>
+      <c r="F27" s="115">
+        <f t="shared" si="0"/>
+        <v>5.5044193843340441</v>
+      </c>
+      <c r="G27" s="115">
+        <f t="shared" si="1"/>
+        <v>5.5044193843340441</v>
+      </c>
+      <c r="H27" s="110"/>
+      <c r="I27" s="110" t="s">
+        <v>98</v>
+      </c>
+      <c r="J27" s="110"/>
+      <c r="K27" s="116"/>
+    </row>
+    <row r="28" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="112"/>
+      <c r="B28" s="113"/>
+      <c r="C28" s="114">
+        <v>4</v>
+      </c>
+      <c r="D28" s="115">
+        <v>1.5</v>
+      </c>
+      <c r="E28" s="115">
+        <v>3.01</v>
+      </c>
+      <c r="F28" s="115">
+        <f t="shared" si="0"/>
+        <v>18.059999999999999</v>
+      </c>
+      <c r="G28" s="115">
+        <f t="shared" si="1"/>
+        <v>18.059999999999999</v>
+      </c>
+      <c r="H28" s="110"/>
+      <c r="I28" s="110"/>
+      <c r="J28" s="110"/>
+      <c r="K28" s="116"/>
+    </row>
+    <row r="29" spans="1:11" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="112"/>
+      <c r="B29" s="113" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="114">
+        <v>1</v>
+      </c>
+      <c r="D29" s="115">
+        <f>(7+65/12+76/12+74/12+6)/3.281</f>
+        <v>9.4229401605201666</v>
+      </c>
+      <c r="E29" s="115">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="F29" s="115">
+        <f t="shared" si="0"/>
+        <v>21.295844762775573</v>
+      </c>
+      <c r="G29" s="115">
+        <f t="shared" si="1"/>
+        <v>21.295844762775573</v>
+      </c>
+      <c r="H29" s="110"/>
+      <c r="I29" s="110"/>
+      <c r="J29" s="110"/>
+      <c r="K29" s="116"/>
+    </row>
+    <row r="30" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="112"/>
+      <c r="B30" s="113"/>
+      <c r="C30" s="114">
+        <v>2</v>
+      </c>
+      <c r="D30" s="115">
+        <f>(69+72+75+64+82)/12/3.281</f>
+        <v>9.1943513156557959</v>
+      </c>
+      <c r="E30" s="115">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="F30" s="115">
+        <f t="shared" si="0"/>
+        <v>41.558467946764196</v>
+      </c>
+      <c r="G30" s="115">
+        <f t="shared" si="1"/>
+        <v>41.558467946764196</v>
+      </c>
+      <c r="H30" s="110"/>
+      <c r="I30" s="110"/>
+      <c r="J30" s="110"/>
+      <c r="K30" s="116"/>
+    </row>
+    <row r="31" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="112"/>
+      <c r="B31" s="113"/>
+      <c r="C31" s="114">
+        <v>1</v>
+      </c>
+      <c r="D31" s="115">
+        <f>82/12/3.281</f>
+        <v>2.0826983643198211</v>
+      </c>
+      <c r="E31" s="115">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="F31" s="115">
+        <f t="shared" si="0"/>
+        <v>4.7068983033627951</v>
+      </c>
+      <c r="G31" s="115">
+        <f t="shared" si="1"/>
+        <v>4.7068983033627951</v>
+      </c>
+      <c r="H31" s="110"/>
+      <c r="I31" s="110"/>
+      <c r="J31" s="110"/>
+      <c r="K31" s="116"/>
+    </row>
+    <row r="32" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="105"/>
+      <c r="B32" s="113" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="107"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="111"/>
+      <c r="F32" s="111"/>
+      <c r="G32" s="110">
+        <f>SUM(G10:G31)</f>
+        <v>880.06056639235987</v>
+      </c>
+      <c r="H32" s="109" t="s">
+        <v>40</v>
+      </c>
+      <c r="I32" s="6">
+        <v>182.51</v>
+      </c>
+      <c r="J32" s="110">
+        <f>G32*I32</f>
+        <v>160619.8539722696</v>
+      </c>
+      <c r="K32" s="111"/>
+    </row>
+    <row r="33" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="105"/>
+      <c r="B33" s="113" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="107"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="111"/>
+      <c r="F33" s="111"/>
+      <c r="G33" s="110"/>
+      <c r="H33" s="109"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="110">
+        <f>0.13*G32*(1871.42/18.94)</f>
+        <v>11304.391915023165</v>
+      </c>
+      <c r="K33" s="111"/>
+    </row>
+    <row r="34" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="5"/>
+    </row>
+    <row r="35" spans="1:11" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>2</v>
+      </c>
+      <c r="B35" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="5"/>
+    </row>
+    <row r="36" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="3">
+        <v>4</v>
+      </c>
+      <c r="D36" s="4">
+        <f>(15+6)/2/3.281</f>
+        <v>3.2002438281011885</v>
+      </c>
+      <c r="E36" s="5">
+        <f>5.583/3.281</f>
+        <v>1.7016153611703748</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="33">
+        <f t="shared" ref="G36:G37" si="2">PRODUCT(C36:F36)</f>
+        <v>21.782336229550666</v>
+      </c>
+      <c r="H36" s="7"/>
+      <c r="I36" s="6">
+        <f>183/12</f>
+        <v>15.25</v>
+      </c>
+      <c r="J36" s="42"/>
+      <c r="K36" s="5"/>
+    </row>
+    <row r="37" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="3">
+        <v>4</v>
+      </c>
+      <c r="D37" s="4">
+        <f>5/3.281</f>
+        <v>1.5239256324291375</v>
+      </c>
+      <c r="E37" s="5">
+        <f>5.583/3.281</f>
+        <v>1.7016153611703748</v>
+      </c>
+      <c r="F37" s="5"/>
+      <c r="G37" s="33">
+        <f t="shared" si="2"/>
+        <v>10.372541061690795</v>
+      </c>
+      <c r="H37" s="7"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="5"/>
+    </row>
+    <row r="38" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="42">
+        <f>SUM(G36:G37)</f>
+        <v>32.154877291241462</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I38" s="6">
+        <v>1112.58</v>
+      </c>
+      <c r="J38" s="42">
+        <f>G38*I38</f>
+        <v>35774.873376689422</v>
+      </c>
+      <c r="K38" s="5"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="16"/>
+      <c r="B39" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="18">
+        <f>0.13*G38*7050.67/10</f>
+        <v>2947.2745727234869</v>
+      </c>
+      <c r="K39" s="17"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="16"/>
+      <c r="B40" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="18">
+        <f>0.13*G38*1023.75/10</f>
+        <v>427.94122314980984</v>
+      </c>
+      <c r="K40" s="17"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="16"/>
+      <c r="B41" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="18">
+        <f>0.13*G38*348.21/10</f>
+        <v>145.55644768058147</v>
+      </c>
+      <c r="K41" s="17"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="16"/>
+      <c r="B42" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="18">
+        <f>0.13*G38*165/10</f>
+        <v>68.972211789712929</v>
+      </c>
+      <c r="K42" s="17"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="16"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="17"/>
+    </row>
+    <row r="44" spans="1:11" ht="150" x14ac:dyDescent="0.25">
+      <c r="A44" s="16">
+        <v>3</v>
+      </c>
+      <c r="B44" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="17"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="16"/>
+      <c r="B45" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C45" s="17">
+        <v>1</v>
+      </c>
+      <c r="D45" s="33">
+        <f>D54</f>
+        <v>9.5245352026821095</v>
+      </c>
+      <c r="E45" s="17">
+        <f>E54</f>
+        <v>1.75</v>
+      </c>
+      <c r="F45" s="33">
+        <v>0.9</v>
+      </c>
+      <c r="G45" s="33">
+        <f t="shared" ref="G45:G49" si="3">PRODUCT(C45:F45)</f>
+        <v>15.001142944224325</v>
+      </c>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="17"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="16"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="17">
+        <v>1</v>
+      </c>
+      <c r="D46" s="33">
+        <f>D55</f>
+        <v>7.8229198415117347</v>
+      </c>
+      <c r="E46" s="33">
+        <f>E55</f>
+        <v>1</v>
+      </c>
+      <c r="F46" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="G46" s="33">
+        <f t="shared" si="3"/>
+        <v>5.8671898811338012</v>
+      </c>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="17"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="16"/>
+      <c r="B47" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" s="17">
+        <v>4</v>
+      </c>
+      <c r="D47" s="33">
+        <v>0.6</v>
+      </c>
+      <c r="E47" s="33">
+        <v>0.6</v>
+      </c>
+      <c r="F47" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="G47" s="33">
+        <f t="shared" si="3"/>
+        <v>0.64800000000000002</v>
+      </c>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="17"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="16"/>
+      <c r="B48" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="17">
+        <v>4</v>
+      </c>
+      <c r="D48" s="33">
+        <f>10.25/3.281</f>
+        <v>3.1240475464797317</v>
+      </c>
+      <c r="E48" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F48" s="33">
+        <v>0.3</v>
+      </c>
+      <c r="G48" s="33">
+        <f t="shared" si="3"/>
+        <v>1.6869856750990553</v>
+      </c>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="17"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="16"/>
+      <c r="B49" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="17">
+        <v>5</v>
+      </c>
+      <c r="D49" s="33">
+        <v>0.3</v>
+      </c>
+      <c r="E49" s="33">
+        <v>0.3</v>
+      </c>
+      <c r="F49" s="33">
+        <v>0.3</v>
+      </c>
+      <c r="G49" s="33">
+        <f t="shared" si="3"/>
+        <v>0.13499999999999998</v>
+      </c>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="17"/>
+    </row>
+    <row r="50" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2"/>
+      <c r="B50" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="42">
+        <f>SUM(G45:G49)</f>
+        <v>23.338318500457184</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I50" s="6">
+        <v>62.95</v>
+      </c>
+      <c r="J50" s="42">
+        <f>G50*I50</f>
+        <v>1469.1471496037798</v>
+      </c>
+      <c r="K50" s="5"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="16"/>
+      <c r="B51" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="18">
+        <f>0.13*G50*18612/360</f>
+        <v>156.85683864157275</v>
+      </c>
+      <c r="K51" s="17"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="16"/>
+      <c r="B52" s="32"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="17"/>
+    </row>
+    <row r="53" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="A53" s="16">
+        <v>4</v>
+      </c>
+      <c r="B53" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="17"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="16"/>
+      <c r="B54" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" s="17">
+        <v>1</v>
+      </c>
+      <c r="D54" s="33">
+        <f>D65</f>
+        <v>9.5245352026821095</v>
+      </c>
+      <c r="E54" s="17">
+        <f>E65</f>
+        <v>1.75</v>
+      </c>
+      <c r="F54" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="G54" s="33">
+        <f t="shared" ref="G54:G60" si="4">PRODUCT(C54:F54)</f>
+        <v>2.5001904907040537</v>
+      </c>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="17"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="16"/>
+      <c r="B55" s="32"/>
+      <c r="C55" s="17">
+        <v>1</v>
+      </c>
+      <c r="D55" s="33">
+        <f>D67</f>
+        <v>7.8229198415117347</v>
+      </c>
+      <c r="E55" s="33">
+        <f>E67</f>
+        <v>1</v>
+      </c>
+      <c r="F55" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="G55" s="33">
+        <f t="shared" si="4"/>
+        <v>1.1734379762267602</v>
+      </c>
+      <c r="H55" s="17"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="17"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="16"/>
+      <c r="B56" s="32" t="str">
+        <f>B47</f>
+        <v>-for footing of vertical post</v>
+      </c>
+      <c r="C56" s="17">
+        <f>C47</f>
+        <v>4</v>
+      </c>
+      <c r="D56" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="E56" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F56" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="G56" s="33">
+        <f t="shared" si="4"/>
+        <v>0.1215</v>
+      </c>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="17"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="16"/>
+      <c r="B57" s="32" t="str">
+        <f>B48</f>
+        <v>-for plinth level</v>
+      </c>
+      <c r="C57" s="17">
+        <f>C48</f>
+        <v>4</v>
+      </c>
+      <c r="D57" s="33">
+        <f>11.17/3.281</f>
+        <v>3.4044498628466928</v>
+      </c>
+      <c r="E57" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F57" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="G57" s="33">
+        <f t="shared" si="4"/>
+        <v>0.91920146296860705</v>
+      </c>
+      <c r="H57" s="17"/>
+      <c r="I57" s="17"/>
+      <c r="J57" s="18"/>
+      <c r="K57" s="17"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="16"/>
+      <c r="B58" s="32"/>
+      <c r="C58" s="17">
+        <v>1</v>
+      </c>
+      <c r="D58" s="33">
+        <f>11.17/3.281</f>
+        <v>3.4044498628466928</v>
+      </c>
+      <c r="E58" s="33">
+        <f>11.17/3.281</f>
+        <v>3.4044498628466928</v>
+      </c>
+      <c r="F58" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="G58" s="33">
+        <f t="shared" si="4"/>
+        <v>1.7385418302955298</v>
+      </c>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="17"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="16"/>
+      <c r="B59" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" s="17">
+        <v>-1</v>
+      </c>
+      <c r="D59" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="E59" s="33">
+        <v>1.8</v>
+      </c>
+      <c r="F59" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="G59" s="33">
+        <f t="shared" si="4"/>
+        <v>-0.40500000000000003</v>
+      </c>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="17"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="16"/>
+      <c r="B60" s="32" t="str">
+        <f>B49</f>
+        <v>-for railing</v>
+      </c>
+      <c r="C60" s="17">
+        <v>5</v>
+      </c>
+      <c r="D60" s="33">
+        <f>D49</f>
+        <v>0.3</v>
+      </c>
+      <c r="E60" s="33">
+        <f>E49</f>
+        <v>0.3</v>
+      </c>
+      <c r="F60" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="G60" s="33">
+        <f t="shared" si="4"/>
+        <v>6.7499999999999991E-2</v>
+      </c>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="17"/>
+    </row>
+    <row r="61" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2"/>
+      <c r="B61" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="42">
+        <f>SUM(G54:G60)</f>
+        <v>6.1153717601949502</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I61" s="6">
+        <v>4458.5200000000004</v>
+      </c>
+      <c r="J61" s="42">
+        <f>G61*I61</f>
+        <v>27265.507300264391</v>
+      </c>
+      <c r="K61" s="5"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="16"/>
+      <c r="B62" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="18">
+        <f>0.13*G61*15452.64/5</f>
+        <v>2456.9645951879311</v>
+      </c>
+      <c r="K62" s="17"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="16"/>
+      <c r="B63" s="45"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="17"/>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="18"/>
+      <c r="K63" s="17"/>
+    </row>
+    <row r="64" spans="1:11" ht="78.75" x14ac:dyDescent="0.25">
+      <c r="A64" s="16">
+        <v>5</v>
+      </c>
+      <c r="B64" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="17"/>
+      <c r="G64" s="17"/>
+      <c r="H64" s="17"/>
+      <c r="I64" s="17"/>
+      <c r="J64" s="17"/>
+      <c r="K64" s="17"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="16"/>
+      <c r="B65" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C65" s="17">
+        <v>1</v>
+      </c>
+      <c r="D65" s="33">
+        <f>D82</f>
+        <v>9.5245352026821095</v>
+      </c>
+      <c r="E65" s="33">
+        <f>F82/2</f>
+        <v>1.75</v>
+      </c>
+      <c r="F65" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="G65" s="33">
+        <f t="shared" ref="G65:G73" si="5">PRODUCT(C65:F65)</f>
+        <v>0.83339683023468469</v>
+      </c>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
+      <c r="J65" s="18"/>
+      <c r="K65" s="17"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="16"/>
+      <c r="B66" s="32"/>
+      <c r="C66" s="17">
+        <v>1</v>
+      </c>
+      <c r="D66" s="33">
+        <f>D65</f>
+        <v>9.5245352026821095</v>
+      </c>
+      <c r="E66" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F66" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="G66" s="33">
+        <f t="shared" si="5"/>
+        <v>0.21430204206034748</v>
+      </c>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="18"/>
+      <c r="K66" s="17"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="16"/>
+      <c r="B67" s="32"/>
+      <c r="C67" s="17">
+        <v>1</v>
+      </c>
+      <c r="D67" s="33">
+        <f>D83</f>
+        <v>7.8229198415117347</v>
+      </c>
+      <c r="E67" s="33">
+        <f>F83/2</f>
+        <v>1</v>
+      </c>
+      <c r="F67" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="G67" s="33">
+        <f t="shared" si="5"/>
+        <v>0.39114599207558676</v>
+      </c>
+      <c r="H67" s="17"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="18"/>
+      <c r="K67" s="17"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="16"/>
+      <c r="B68" s="32"/>
+      <c r="C68" s="17">
+        <v>1</v>
+      </c>
+      <c r="D68" s="33">
+        <f>D83</f>
+        <v>7.8229198415117347</v>
+      </c>
+      <c r="E68" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F68" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="G68" s="33">
+        <f t="shared" si="5"/>
+        <v>0.17601569643401405</v>
+      </c>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="18"/>
+      <c r="K68" s="17"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="16"/>
+      <c r="B69" s="32" t="str">
+        <f>B56</f>
+        <v>-for footing of vertical post</v>
+      </c>
+      <c r="C69" s="17">
+        <v>4</v>
+      </c>
+      <c r="D69" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="E69" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F69" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="G69" s="33">
+        <f t="shared" si="5"/>
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="H69" s="17"/>
+      <c r="I69" s="17"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="17"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="16"/>
+      <c r="B70" s="32" t="str">
+        <f>B57</f>
+        <v>-for plinth level</v>
+      </c>
+      <c r="C70" s="17">
+        <f>C57</f>
+        <v>4</v>
+      </c>
+      <c r="D70" s="33">
+        <f>D57</f>
+        <v>3.4044498628466928</v>
+      </c>
+      <c r="E70" s="17">
+        <f>E57</f>
+        <v>0.45</v>
+      </c>
+      <c r="F70" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G70" s="33">
+        <f t="shared" si="5"/>
+        <v>0.30640048765620237</v>
+      </c>
+      <c r="H70" s="17"/>
+      <c r="I70" s="17"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="17"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="16"/>
+      <c r="B71" s="32"/>
+      <c r="C71" s="17">
+        <v>1</v>
+      </c>
+      <c r="D71" s="33">
+        <f>14.17/3.281</f>
+        <v>4.3188052423041752</v>
+      </c>
+      <c r="E71" s="33">
+        <f>14.17/3.281</f>
+        <v>4.3188052423041752</v>
+      </c>
+      <c r="F71" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G71" s="33">
+        <f t="shared" si="5"/>
+        <v>1.3989059040715519</v>
+      </c>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="17"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="16"/>
+      <c r="B72" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C72" s="17">
+        <v>-1</v>
+      </c>
+      <c r="D72" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="E72" s="33">
+        <v>1.8</v>
+      </c>
+      <c r="F72" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G72" s="33">
+        <f t="shared" si="5"/>
+        <v>-0.20250000000000001</v>
+      </c>
+      <c r="H72" s="17"/>
+      <c r="I72" s="17"/>
+      <c r="J72" s="18"/>
+      <c r="K72" s="17"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="16"/>
+      <c r="B73" s="32" t="str">
+        <f>B60</f>
+        <v>-for railing</v>
+      </c>
+      <c r="C73" s="17">
+        <v>5</v>
+      </c>
+      <c r="D73" s="33">
+        <f>D60</f>
+        <v>0.3</v>
+      </c>
+      <c r="E73" s="33">
+        <f>E60</f>
+        <v>0.3</v>
+      </c>
+      <c r="F73" s="33">
+        <v>0.3</v>
+      </c>
+      <c r="G73" s="33">
+        <f t="shared" si="5"/>
+        <v>0.13499999999999998</v>
+      </c>
+      <c r="H73" s="17"/>
+      <c r="I73" s="17"/>
+      <c r="J73" s="18"/>
+      <c r="K73" s="17"/>
+    </row>
+    <row r="74" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2"/>
+      <c r="B74" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="42">
+        <f>SUM(G65:G73)</f>
+        <v>3.4956669525323871</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I74" s="6">
+        <v>10964.46</v>
+      </c>
+      <c r="J74" s="42">
+        <f>G74*I74</f>
+        <v>38328.100474363251</v>
+      </c>
+      <c r="K74" s="5"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" s="16"/>
+      <c r="B75" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C75" s="17"/>
+      <c r="D75" s="17"/>
+      <c r="E75" s="17"/>
+      <c r="F75" s="17"/>
+      <c r="G75" s="17"/>
+      <c r="H75" s="17"/>
+      <c r="I75" s="17"/>
+      <c r="J75" s="18">
+        <f>0.13*G74*53818.03/15</f>
+        <v>1630.4592106521038</v>
+      </c>
+      <c r="K75" s="17"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" s="16"/>
+      <c r="B76" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" s="17"/>
+      <c r="D76" s="17"/>
+      <c r="E76" s="17"/>
+      <c r="F76" s="17"/>
+      <c r="G76" s="17"/>
+      <c r="H76" s="17"/>
+      <c r="I76" s="17"/>
+      <c r="J76" s="18">
+        <f>0.13*G74*21432.6/15</f>
+        <v>649.31733989932889</v>
+      </c>
+      <c r="K76" s="17"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" s="16"/>
+      <c r="B77" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C77" s="17"/>
+      <c r="D77" s="17"/>
+      <c r="E77" s="17"/>
+      <c r="F77" s="17"/>
+      <c r="G77" s="17"/>
+      <c r="H77" s="17"/>
+      <c r="I77" s="17"/>
+      <c r="J77" s="18">
+        <f>0.13*G74*(25719.12+13573.98+4286.52)/15</f>
+        <v>1320.2785911286353</v>
+      </c>
+      <c r="K77" s="17"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" s="16"/>
+      <c r="B78" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C78" s="17"/>
+      <c r="D78" s="17"/>
+      <c r="E78" s="17"/>
+      <c r="F78" s="17"/>
+      <c r="G78" s="17"/>
+      <c r="H78" s="17"/>
+      <c r="I78" s="17"/>
+      <c r="J78" s="18">
+        <f>0.13*G74*(6325.7/15)</f>
+        <v>191.64201716082906</v>
+      </c>
+      <c r="K78" s="17"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" s="16"/>
+      <c r="B79" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C79" s="17"/>
+      <c r="D79" s="17"/>
+      <c r="E79" s="17"/>
+      <c r="F79" s="17"/>
+      <c r="G79" s="17"/>
+      <c r="H79" s="17"/>
+      <c r="I79" s="17"/>
+      <c r="J79" s="18">
+        <f>0.13*G74*(310)/5</f>
+        <v>28.175075637411044</v>
+      </c>
+      <c r="K79" s="17"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" s="16"/>
+      <c r="B80" s="32"/>
+      <c r="C80" s="17"/>
+      <c r="D80" s="17"/>
+      <c r="E80" s="17"/>
+      <c r="F80" s="17"/>
+      <c r="G80" s="17"/>
+      <c r="H80" s="17"/>
+      <c r="I80" s="17"/>
+      <c r="J80" s="18"/>
+      <c r="K80" s="17"/>
+    </row>
+    <row r="81" spans="1:16" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A81" s="16">
+        <v>6</v>
+      </c>
+      <c r="B81" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="17"/>
+      <c r="K81" s="17"/>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A82" s="16"/>
+      <c r="B82" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="17">
+        <v>1</v>
+      </c>
+      <c r="D82" s="33">
+        <f>31.25/3.281</f>
+        <v>9.5245352026821095</v>
+      </c>
+      <c r="E82" s="33">
+        <f>((F82/2)+0.5)/2</f>
+        <v>1.125</v>
+      </c>
+      <c r="F82" s="33">
+        <f>7/2</f>
+        <v>3.5</v>
+      </c>
+      <c r="G82" s="33">
+        <f>PRODUCT(C82:F82)</f>
+        <v>37.502857360560803</v>
+      </c>
+      <c r="H82" s="17"/>
+      <c r="I82" s="17">
+        <f>31.25/3.281</f>
+        <v>9.5245352026821095</v>
+      </c>
+      <c r="J82" s="17"/>
+      <c r="K82" s="17"/>
+      <c r="M82" s="33">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="N82" s="33">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="O82" s="33"/>
+      <c r="P82" s="33">
+        <f>PI()*M82*SQRT(M82^2+N82^2)</f>
+        <v>160.09797821843054</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A83" s="16"/>
+      <c r="B83" s="32"/>
+      <c r="C83" s="17">
+        <v>1</v>
+      </c>
+      <c r="D83" s="33">
+        <f>(10.667+15)/3.281</f>
+        <v>7.8229198415117347</v>
+      </c>
+      <c r="E83" s="33">
+        <f>((F83/2)+0.5)/2</f>
+        <v>0.75</v>
+      </c>
+      <c r="F83" s="33">
+        <v>2</v>
+      </c>
+      <c r="G83" s="33">
+        <f>PRODUCT(C83:F83)</f>
+        <v>11.734379762267602</v>
+      </c>
+      <c r="H83" s="17"/>
+      <c r="I83" s="17">
+        <f>(10.75+15)/3.281</f>
+        <v>7.8482170070100574</v>
+      </c>
+      <c r="J83" s="17"/>
+      <c r="K83" s="17"/>
+      <c r="M83" s="35"/>
+      <c r="N83" s="35"/>
+      <c r="O83" s="35"/>
+      <c r="P83" s="35"/>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A84" s="16"/>
+      <c r="B84" s="32" t="str">
+        <f>B70</f>
+        <v>-for plinth level</v>
+      </c>
+      <c r="C84" s="17">
+        <v>2</v>
+      </c>
+      <c r="D84" s="33">
+        <f>14.17/3.281</f>
+        <v>4.3188052423041752</v>
+      </c>
+      <c r="E84" s="33">
+        <f>1.5/3.281</f>
+        <v>0.45717768972874123</v>
+      </c>
+      <c r="F84" s="33">
+        <f>1.5/3.281</f>
+        <v>0.45717768972874123</v>
+      </c>
+      <c r="G84" s="33">
+        <f>PRODUCT(C84:F84)</f>
+        <v>1.8053594054236508</v>
+      </c>
+      <c r="H84" s="17"/>
+      <c r="I84" s="17"/>
+      <c r="J84" s="17"/>
+      <c r="K84" s="17"/>
+      <c r="M84" s="35"/>
+      <c r="N84" s="35"/>
+      <c r="O84" s="35"/>
+      <c r="P84" s="35"/>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A85" s="16"/>
+      <c r="B85" s="32"/>
+      <c r="C85" s="17">
+        <v>2</v>
+      </c>
+      <c r="D85" s="33">
+        <f>(14.17-3)/3.281</f>
+        <v>3.4044498628466928</v>
+      </c>
+      <c r="E85" s="33">
+        <f>1.5/3.281</f>
+        <v>0.45717768972874123</v>
+      </c>
+      <c r="F85" s="33">
+        <f>1.5/3.281</f>
+        <v>0.45717768972874123</v>
+      </c>
+      <c r="G85" s="33">
+        <f>PRODUCT(C85:F85)</f>
+        <v>1.4231379363854748</v>
+      </c>
+      <c r="H85" s="17"/>
+      <c r="I85" s="17"/>
+      <c r="J85" s="17"/>
+      <c r="K85" s="17"/>
+      <c r="M85" s="35"/>
+      <c r="N85" s="35"/>
+      <c r="O85" s="35"/>
+      <c r="P85" s="35"/>
+    </row>
+    <row r="86" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2"/>
+      <c r="B86" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="6">
+        <f>SUM(G82:G85)</f>
+        <v>52.465734464637528</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I86" s="6">
+        <v>8987.83</v>
+      </c>
+      <c r="J86" s="18">
+        <f>G86*I86</f>
+        <v>471553.10219330312</v>
+      </c>
+      <c r="K86" s="5"/>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A87" s="16"/>
+      <c r="B87" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C87" s="17"/>
+      <c r="D87" s="17"/>
+      <c r="E87" s="17"/>
+      <c r="F87" s="17"/>
+      <c r="G87" s="17"/>
+      <c r="H87" s="17"/>
+      <c r="I87" s="17"/>
+      <c r="J87" s="18">
+        <f>0.13*G86*(5863.95)/5</f>
+        <v>7999.0675339616919</v>
+      </c>
+      <c r="K87" s="17"/>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A88" s="16"/>
+      <c r="B88" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C88" s="17"/>
+      <c r="D88" s="17"/>
+      <c r="E88" s="17"/>
+      <c r="F88" s="17"/>
+      <c r="G88" s="17"/>
+      <c r="H88" s="17"/>
+      <c r="I88" s="17"/>
+      <c r="J88" s="18">
+        <f>0.13*G86*(6604.416)/5</f>
+        <v>9009.1439399000919</v>
+      </c>
+      <c r="K88" s="17"/>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A89" s="16"/>
+      <c r="B89" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C89" s="17"/>
+      <c r="D89" s="17"/>
+      <c r="E89" s="17"/>
+      <c r="F89" s="17"/>
+      <c r="G89" s="17"/>
+      <c r="H89" s="17"/>
+      <c r="I89" s="17"/>
+      <c r="J89" s="18">
+        <f>0.13*G86*(14808.78)/5</f>
+        <v>20200.79149985611</v>
+      </c>
+      <c r="K89" s="17"/>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A90" s="16"/>
+      <c r="B90" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C90" s="17"/>
+      <c r="D90" s="17"/>
+      <c r="E90" s="17"/>
+      <c r="F90" s="17"/>
+      <c r="G90" s="17"/>
+      <c r="H90" s="17"/>
+      <c r="I90" s="17"/>
+      <c r="J90" s="18">
+        <f>0.13*G86*(310)/5</f>
+        <v>422.87381978497842</v>
+      </c>
+      <c r="K90" s="17"/>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A91" s="16"/>
+      <c r="B91" s="32"/>
+      <c r="C91" s="17"/>
+      <c r="D91" s="17"/>
+      <c r="E91" s="17"/>
+      <c r="F91" s="17"/>
+      <c r="G91" s="17"/>
+      <c r="H91" s="17"/>
+      <c r="I91" s="17"/>
+      <c r="J91" s="18"/>
+      <c r="K91" s="17"/>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A92" s="16">
+        <v>7</v>
+      </c>
+      <c r="B92" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C92" s="17"/>
+      <c r="D92" s="17"/>
+      <c r="E92" s="17"/>
+      <c r="F92" s="17"/>
+      <c r="G92" s="17"/>
+      <c r="H92" s="17"/>
+      <c r="I92" s="17"/>
+      <c r="J92" s="18"/>
+      <c r="K92" s="17"/>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A93" s="16"/>
+      <c r="B93" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C93" s="17">
+        <v>1</v>
+      </c>
+      <c r="D93" s="33">
+        <f>1.5</f>
+        <v>1.5</v>
+      </c>
+      <c r="E93" s="33">
+        <v>1.6</v>
+      </c>
+      <c r="F93" s="17"/>
+      <c r="G93" s="33">
+        <f>PRODUCT(C93:F93)</f>
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="H93" s="17"/>
+      <c r="I93" s="17"/>
+      <c r="J93" s="18"/>
+      <c r="K93" s="17"/>
+    </row>
+    <row r="94" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2"/>
+      <c r="B94" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" s="3"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="6">
+        <f>SUM(G93)</f>
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I94" s="6">
+        <v>1017.47</v>
+      </c>
+      <c r="J94" s="18">
+        <f>G94*I94</f>
+        <v>2441.9280000000003</v>
+      </c>
+      <c r="K94" s="5"/>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A95" s="16"/>
+      <c r="B95" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C95" s="17"/>
+      <c r="D95" s="17"/>
+      <c r="E95" s="17"/>
+      <c r="F95" s="17"/>
+      <c r="G95" s="17"/>
+      <c r="H95" s="17"/>
+      <c r="I95" s="17"/>
+      <c r="J95" s="18">
+        <f>0.13*G94*(8617.2)/10</f>
+        <v>268.85664000000008</v>
+      </c>
+      <c r="K95" s="17"/>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A96" s="16"/>
+      <c r="B96" s="17"/>
+      <c r="C96" s="17"/>
+      <c r="D96" s="17"/>
+      <c r="E96" s="17"/>
+      <c r="F96" s="17"/>
+      <c r="G96" s="17"/>
+      <c r="H96" s="17"/>
+      <c r="I96" s="17"/>
+      <c r="J96" s="17"/>
+      <c r="K96" s="17"/>
+    </row>
+    <row r="97" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A97" s="16">
+        <v>8</v>
+      </c>
+      <c r="B97" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C97" s="17"/>
+      <c r="D97" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E97" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="F97" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="G97" s="17"/>
+      <c r="H97" s="17"/>
+      <c r="I97" s="17"/>
+      <c r="J97" s="18"/>
+      <c r="K97" s="17"/>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A98" s="16"/>
+      <c r="B98" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C98" s="17">
+        <v>1</v>
+      </c>
+      <c r="D98" s="17">
+        <v>185</v>
+      </c>
+      <c r="E98" s="17">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="F98" s="17">
+        <f>C98*D98*E98</f>
+        <v>24.975000000000001</v>
+      </c>
+      <c r="G98" s="33">
+        <f>F98</f>
+        <v>24.975000000000001</v>
+      </c>
+      <c r="H98" s="17"/>
+      <c r="I98" s="17"/>
+      <c r="J98" s="18"/>
+      <c r="K98" s="17"/>
+    </row>
+    <row r="99" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2"/>
+      <c r="B99" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" s="3"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="5"/>
+      <c r="G99" s="6">
+        <f>SUM(G98)</f>
+        <v>24.975000000000001</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I99" s="6">
+        <v>287</v>
+      </c>
+      <c r="J99" s="18">
+        <f>G99*I99</f>
+        <v>7167.8250000000007</v>
+      </c>
+      <c r="K99" s="5"/>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A100" s="16"/>
+      <c r="B100" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C100" s="17"/>
+      <c r="D100" s="17"/>
+      <c r="E100" s="17"/>
+      <c r="F100" s="17"/>
+      <c r="G100" s="17"/>
+      <c r="H100" s="17"/>
+      <c r="I100" s="17"/>
+      <c r="J100" s="18">
+        <f>0.13*J99</f>
+        <v>931.81725000000017</v>
+      </c>
+      <c r="K100" s="17"/>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A101" s="16"/>
+      <c r="B101" s="17"/>
+      <c r="C101" s="17"/>
+      <c r="D101" s="17"/>
+      <c r="E101" s="17"/>
+      <c r="F101" s="17"/>
+      <c r="G101" s="17"/>
+      <c r="H101" s="17"/>
+      <c r="I101" s="17"/>
+      <c r="J101" s="17"/>
+      <c r="K101" s="17"/>
+    </row>
+    <row r="102" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>9</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102" s="3">
+        <v>1</v>
+      </c>
+      <c r="D102" s="4"/>
+      <c r="E102" s="5"/>
+      <c r="F102" s="5"/>
+      <c r="G102" s="7">
+        <f t="shared" ref="G102" si="6">PRODUCT(C102:F102)</f>
+        <v>1</v>
+      </c>
+      <c r="H102" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I102" s="6">
+        <v>500</v>
+      </c>
+      <c r="J102" s="7">
+        <f>G102*I102</f>
+        <v>500</v>
+      </c>
+      <c r="K102" s="5"/>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A103" s="2"/>
+      <c r="B103" s="8"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="4"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="7"/>
+      <c r="I103" s="6"/>
+      <c r="J103" s="18"/>
+      <c r="K103" s="5"/>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A104" s="21"/>
+      <c r="B104" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C104" s="23"/>
+      <c r="D104" s="24"/>
+      <c r="E104" s="24"/>
+      <c r="F104" s="24"/>
+      <c r="G104" s="18"/>
+      <c r="H104" s="18"/>
+      <c r="I104" s="18"/>
+      <c r="J104" s="18">
+        <f>SUM(J9:J102)</f>
+        <v>805286.81389120058</v>
+      </c>
+      <c r="K104" s="25"/>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M105" s="20"/>
+      <c r="N105" s="20"/>
+      <c r="O105" s="20"/>
+      <c r="P105" s="20"/>
+      <c r="Q105" s="20"/>
+      <c r="R105" s="20"/>
+      <c r="S105" s="20"/>
+    </row>
+    <row r="106" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="26"/>
+      <c r="B106" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C106" s="71">
+        <f>J104</f>
+        <v>805286.81389120058</v>
+      </c>
+      <c r="D106" s="72"/>
+      <c r="E106" s="9">
+        <v>100</v>
+      </c>
+      <c r="F106" s="26"/>
+      <c r="G106" s="28"/>
+      <c r="H106" s="26"/>
+      <c r="I106" s="29"/>
+      <c r="J106" s="30"/>
+      <c r="K106" s="31"/>
+      <c r="M106" s="19"/>
+      <c r="N106" s="19"/>
+      <c r="O106" s="19"/>
+      <c r="P106" s="19"/>
+      <c r="Q106" s="19"/>
+      <c r="R106" s="19"/>
+      <c r="S106" s="19"/>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B107" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C107" s="75">
+        <v>700000</v>
+      </c>
+      <c r="D107" s="76"/>
+      <c r="E107" s="9"/>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B108" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C108" s="75">
+        <f>C107-C110-C111</f>
+        <v>665000</v>
+      </c>
+      <c r="D108" s="76"/>
+      <c r="E108" s="9">
+        <f>C108/C106*100</f>
+        <v>82.579273437581179</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B109" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C109" s="77">
+        <f>C106-C108</f>
+        <v>140286.81389120058</v>
+      </c>
+      <c r="D109" s="77"/>
+      <c r="E109" s="9">
+        <f>100-E108</f>
+        <v>17.420726562418821</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B110" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C110" s="71">
+        <f>C107*0.03</f>
+        <v>21000</v>
+      </c>
+      <c r="D110" s="72"/>
+      <c r="E110" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B111" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C111" s="71">
+        <f>C107*0.02</f>
+        <v>14000</v>
+      </c>
+      <c r="D111" s="72"/>
+      <c r="E111" s="9">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>

--- a/बजेट माग estimate/नगर बजेट estimate/तल्लो नंग्लेद्वारे चिहानपाटी/V-devithaan.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/तल्लो नंग्लेद्वारे चिहानपाटी/V-devithaan.xlsx
@@ -3,29 +3,31 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{482DC7D8-631A-4394-97CE-E3A41A48C7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF24AE2-A688-44A6-81A4-5D200CAE1BAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="12" r:id="rId1"/>
     <sheet name="WCR" sheetId="13" r:id="rId2"/>
     <sheet name="V" sheetId="14" r:id="rId3"/>
-    <sheet name="With measurement" sheetId="15" state="hidden" r:id="rId4"/>
+    <sheet name="M" sheetId="16" r:id="rId4"/>
+    <sheet name="With measurement" sheetId="15" state="hidden" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
     <externalReference r:id="rId6"/>
     <externalReference r:id="rId7"/>
     <externalReference r:id="rId8"/>
+    <externalReference r:id="rId9"/>
   </externalReferences>
   <definedNames>
     <definedName name="description_103" localSheetId="1">#REF!</definedName>
     <definedName name="description_103">[1]Abstract!$B$16</definedName>
     <definedName name="description_124" localSheetId="0">#REF!</definedName>
+    <definedName name="description_124" localSheetId="3">#REF!</definedName>
     <definedName name="description_124" localSheetId="2">#REF!</definedName>
     <definedName name="description_124" localSheetId="1">#REF!</definedName>
-    <definedName name="description_124" localSheetId="3">#REF!</definedName>
+    <definedName name="description_124" localSheetId="4">#REF!</definedName>
     <definedName name="description_124">#REF!</definedName>
     <definedName name="description_247" localSheetId="1">#REF!</definedName>
     <definedName name="description_247">[1]Abstract!$B$22</definedName>
@@ -40,42 +42,48 @@
     <definedName name="description_3" localSheetId="1">#REF!</definedName>
     <definedName name="description_3">[1]Abstract!$B$169</definedName>
     <definedName name="description_310" localSheetId="0">#REF!</definedName>
+    <definedName name="description_310" localSheetId="3">#REF!</definedName>
     <definedName name="description_310" localSheetId="2">#REF!</definedName>
     <definedName name="description_310" localSheetId="1">#REF!</definedName>
-    <definedName name="description_310" localSheetId="3">#REF!</definedName>
+    <definedName name="description_310" localSheetId="4">#REF!</definedName>
     <definedName name="description_310">#REF!</definedName>
     <definedName name="description_312" localSheetId="0">#REF!</definedName>
+    <definedName name="description_312" localSheetId="3">#REF!</definedName>
     <definedName name="description_312" localSheetId="2">#REF!</definedName>
     <definedName name="description_312" localSheetId="1">#REF!</definedName>
-    <definedName name="description_312" localSheetId="3">#REF!</definedName>
+    <definedName name="description_312" localSheetId="4">#REF!</definedName>
     <definedName name="description_312">#REF!</definedName>
     <definedName name="description_4">#REF!</definedName>
     <definedName name="description_5" localSheetId="1">#REF!</definedName>
     <definedName name="description_5">[1]Abstract!$B$171</definedName>
     <definedName name="description_6" localSheetId="0">#REF!</definedName>
+    <definedName name="description_6" localSheetId="3">#REF!</definedName>
     <definedName name="description_6" localSheetId="2">#REF!</definedName>
     <definedName name="description_6" localSheetId="1">#REF!</definedName>
-    <definedName name="description_6" localSheetId="3">#REF!</definedName>
+    <definedName name="description_6" localSheetId="4">#REF!</definedName>
     <definedName name="description_6">#REF!</definedName>
     <definedName name="description_759" localSheetId="1">#REF!</definedName>
     <definedName name="description_759">[1]Abstract!$B$278</definedName>
     <definedName name="description_781" localSheetId="0">#REF!</definedName>
+    <definedName name="description_781" localSheetId="3">#REF!</definedName>
     <definedName name="description_781" localSheetId="2">#REF!</definedName>
     <definedName name="description_781" localSheetId="1">#REF!</definedName>
-    <definedName name="description_781" localSheetId="3">#REF!</definedName>
+    <definedName name="description_781" localSheetId="4">#REF!</definedName>
     <definedName name="description_781">#REF!</definedName>
     <definedName name="description_783" localSheetId="1">#REF!</definedName>
     <definedName name="description_783">[1]Abstract!$B$301</definedName>
     <definedName name="description_784" localSheetId="1">#REF!</definedName>
     <definedName name="description_784">[3]Abstract!$B$300</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">estimate!$A$1:$K$103</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">M!$A$1:$K$111</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">V!$A$1:$K$111</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">WCR!$A$1:$K$49</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'With measurement'!$A$1:$K$111</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'With measurement'!$A$1:$K$111</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">M!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">V!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">WCR!$1:$12</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'With measurement'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'With measurement'!$1:$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -95,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="104">
   <si>
     <t>Government of Nepal</t>
   </si>
@@ -364,9 +372,6 @@
     <t xml:space="preserve">F.Y:2082/2083            </t>
   </si>
   <si>
-    <t xml:space="preserve">Date:2083/02/18       </t>
-  </si>
-  <si>
     <t>S.No.</t>
   </si>
   <si>
@@ -395,6 +400,21 @@
   </si>
   <si>
     <t>-MS square pipe horizontal of 1.5" * 1.5" of 2mm thickness for railing</t>
+  </si>
+  <si>
+    <t>Total Valuated</t>
+  </si>
+  <si>
+    <t>Detail Valuated Sheet</t>
+  </si>
+  <si>
+    <t>Date:2083/03/15</t>
+  </si>
+  <si>
+    <t>Detail Quantity Mesurement Sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:2083/03/15       </t>
   </si>
 </sst>
 </file>
@@ -631,7 +651,7 @@
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -796,22 +816,17 @@
     <xf numFmtId="2" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="14" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -832,6 +847,45 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="43" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -850,101 +904,11 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1530,113 +1494,113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="69"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="69" t="s">
+      <c r="A4" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="69"/>
-      <c r="G4" s="69"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="69"/>
-      <c r="K4" s="69"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
     </row>
     <row r="5" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="70" t="s">
+      <c r="A5" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="70"/>
-      <c r="C5" s="70"/>
-      <c r="D5" s="70"/>
-      <c r="E5" s="70"/>
-      <c r="F5" s="70"/>
-      <c r="G5" s="70"/>
-      <c r="H5" s="70"/>
-      <c r="I5" s="70"/>
-      <c r="J5" s="70"/>
-      <c r="K5" s="70"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
     </row>
     <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="65" t="s">
+      <c r="A6" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
-      <c r="E6" s="65"/>
-      <c r="F6" s="65"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="66" t="s">
+      <c r="H6" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="66"/>
-      <c r="J6" s="66"/>
-      <c r="K6" s="66"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="78"/>
+      <c r="K6" s="78"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="72" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="73"/>
-      <c r="C7" s="73"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
       <c r="G7" s="11"/>
-      <c r="H7" s="74" t="s">
+      <c r="H7" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="74"/>
-      <c r="J7" s="74"/>
-      <c r="K7" s="74"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="73"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
@@ -3733,11 +3697,11 @@
       <c r="B98" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C98" s="71">
+      <c r="C98" s="70">
         <f>J96</f>
         <v>786973.54597297299</v>
       </c>
-      <c r="D98" s="72"/>
+      <c r="D98" s="71"/>
       <c r="E98" s="9">
         <v>100</v>
       </c>
@@ -3759,21 +3723,21 @@
       <c r="B99" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C99" s="75">
+      <c r="C99" s="74">
         <v>700000</v>
       </c>
-      <c r="D99" s="76"/>
+      <c r="D99" s="75"/>
       <c r="E99" s="9"/>
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B100" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C100" s="75">
+      <c r="C100" s="74">
         <f>C99-C102-C103</f>
         <v>665000</v>
       </c>
-      <c r="D100" s="76"/>
+      <c r="D100" s="75"/>
       <c r="E100" s="9">
         <f>C100/C98*100</f>
         <v>84.500934421858958</v>
@@ -3783,11 +3747,11 @@
       <c r="B101" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C101" s="77">
+      <c r="C101" s="76">
         <f>C98-C100</f>
         <v>121973.54597297299</v>
       </c>
-      <c r="D101" s="77"/>
+      <c r="D101" s="76"/>
       <c r="E101" s="9">
         <f>100-E100</f>
         <v>15.499065578141042</v>
@@ -3797,11 +3761,11 @@
       <c r="B102" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C102" s="71">
+      <c r="C102" s="70">
         <f>C99*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D102" s="72"/>
+      <c r="D102" s="71"/>
       <c r="E102" s="9">
         <v>3</v>
       </c>
@@ -3810,17 +3774,24 @@
       <c r="B103" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C103" s="71">
+      <c r="C103" s="70">
         <f>C99*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D103" s="72"/>
+      <c r="D103" s="71"/>
       <c r="E103" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C102:D102"/>
     <mergeCell ref="C103:D103"/>
     <mergeCell ref="A7:F7"/>
@@ -3829,13 +3800,6 @@
     <mergeCell ref="C99:D99"/>
     <mergeCell ref="C100:D100"/>
     <mergeCell ref="C101:D101"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -3865,90 +3829,90 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="80"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="80"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="92"/>
     </row>
     <row r="2" spans="1:13" ht="25.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="93"/>
     </row>
     <row r="3" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="94" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="E3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="J3" s="82"/>
-      <c r="K3" s="82"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="94"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="94"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
+      <c r="K3" s="94"/>
     </row>
     <row r="4" spans="1:13" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="82" t="s">
+      <c r="A4" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="94"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="94"/>
     </row>
     <row r="5" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="95" t="s">
         <v>83</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="83"/>
-      <c r="K5" s="83"/>
+      <c r="B5" s="95"/>
+      <c r="C5" s="95"/>
+      <c r="D5" s="95"/>
+      <c r="E5" s="95"/>
+      <c r="F5" s="95"/>
+      <c r="G5" s="95"/>
+      <c r="H5" s="95"/>
+      <c r="I5" s="95"/>
+      <c r="J5" s="95"/>
+      <c r="K5" s="95"/>
     </row>
     <row r="6" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="47" t="s">
         <v>84</v>
       </c>
       <c r="B6" s="47"/>
-      <c r="C6" s="78">
+      <c r="C6" s="90">
         <f>F49</f>
         <v>786973.54597297299</v>
       </c>
-      <c r="D6" s="79"/>
+      <c r="D6" s="91"/>
       <c r="E6" s="48"/>
       <c r="F6" s="47"/>
       <c r="G6" s="47"/>
@@ -3956,11 +3920,11 @@
         <v>85</v>
       </c>
       <c r="I6" s="47"/>
-      <c r="J6" s="78">
+      <c r="J6" s="90">
         <f>I49</f>
-        <v>805280.71818867093</v>
-      </c>
-      <c r="K6" s="79"/>
+        <v>789632.08517511096</v>
+      </c>
+      <c r="K6" s="91"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="49" t="s">
@@ -3969,78 +3933,78 @@
       <c r="B7" s="49"/>
       <c r="C7" s="49"/>
       <c r="D7" s="49"/>
-      <c r="F7" s="84"/>
-      <c r="G7" s="84"/>
-      <c r="I7" s="85" t="s">
+      <c r="F7" s="86"/>
+      <c r="G7" s="86"/>
+      <c r="I7" s="87" t="s">
         <v>87</v>
       </c>
-      <c r="J7" s="85"/>
-      <c r="K7" s="85"/>
+      <c r="J7" s="87"/>
+      <c r="K7" s="87"/>
     </row>
     <row r="8" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A8" s="65" t="str">
+      <c r="A8" s="77" t="str">
         <f>estimate!A6</f>
         <v xml:space="preserve">Project:- तल्लो नाङ्गलेद्वारे चिहानपाटी </v>
       </c>
-      <c r="B8" s="65"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
-      <c r="I8" s="86" t="s">
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77"/>
+      <c r="I8" s="88" t="s">
         <v>88</v>
       </c>
-      <c r="J8" s="86"/>
-      <c r="K8" s="86"/>
+      <c r="J8" s="88"/>
+      <c r="K8" s="88"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="87" t="s">
+      <c r="A9" s="89" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="87"/>
-      <c r="C9" s="87"/>
-      <c r="D9" s="87"/>
-      <c r="E9" s="87"/>
-      <c r="F9" s="87"/>
-      <c r="I9" s="86" t="s">
+      <c r="B9" s="89"/>
+      <c r="C9" s="89"/>
+      <c r="D9" s="89"/>
+      <c r="E9" s="89"/>
+      <c r="F9" s="89"/>
+      <c r="I9" s="88" t="s">
+        <v>103</v>
+      </c>
+      <c r="J9" s="88"/>
+      <c r="K9" s="88"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="84" t="s">
         <v>89</v>
       </c>
-      <c r="J9" s="86"/>
-      <c r="K9" s="86"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="89" t="s">
+      <c r="B11" s="84" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="89" t="s">
+      <c r="C11" s="84" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="85" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="89" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="90" t="s">
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="90"/>
-      <c r="F11" s="90"/>
-      <c r="G11" s="90" t="s">
+      <c r="H11" s="85"/>
+      <c r="I11" s="85"/>
+      <c r="J11" s="84" t="s">
         <v>93</v>
       </c>
-      <c r="H11" s="90"/>
-      <c r="I11" s="90"/>
-      <c r="J11" s="89" t="s">
+      <c r="K11" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="K11" s="88" t="s">
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="84"/>
+      <c r="B12" s="84"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="50" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="89"/>
-      <c r="B12" s="89"/>
-      <c r="C12" s="89"/>
-      <c r="D12" s="50" t="s">
-        <v>96</v>
       </c>
       <c r="E12" s="50" t="s">
         <v>13</v>
@@ -4049,7 +4013,7 @@
         <v>14</v>
       </c>
       <c r="G12" s="50" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H12" s="50" t="s">
         <v>13</v>
@@ -4057,8 +4021,8 @@
       <c r="I12" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="89"/>
-      <c r="K12" s="88"/>
+      <c r="J12" s="84"/>
+      <c r="K12" s="83"/>
     </row>
     <row r="13" spans="1:13" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
@@ -4340,7 +4304,7 @@
       </c>
       <c r="G22" s="52">
         <f>V!G50</f>
-        <v>23.338318500457184</v>
+        <v>22.882157985370316</v>
       </c>
       <c r="H22" s="52">
         <f>V!I50</f>
@@ -4348,11 +4312,11 @@
       </c>
       <c r="I22" s="52">
         <f>G22*H22</f>
-        <v>1469.1471496037798</v>
+        <v>1440.4318451790614</v>
       </c>
       <c r="J22" s="53">
         <f>I22-F22</f>
-        <v>9.3224901706796572</v>
+        <v>-19.39281425403874</v>
       </c>
       <c r="K22" s="54"/>
       <c r="M22" s="36">
@@ -4377,11 +4341,11 @@
       <c r="H23" s="52"/>
       <c r="I23" s="52">
         <f>V!J51</f>
-        <v>156.85683864157275</v>
+        <v>153.7909838196739</v>
       </c>
       <c r="J23" s="53">
         <f>I23-F23</f>
-        <v>0.995336877476376</v>
+        <v>-2.0705179444224768</v>
       </c>
       <c r="K23" s="54"/>
       <c r="M23" s="36">
@@ -4429,7 +4393,7 @@
       </c>
       <c r="G25" s="52">
         <f>V!G61</f>
-        <v>6.1153717601949502</v>
+        <v>6.0110163578785833</v>
       </c>
       <c r="H25" s="52">
         <f>V!I61</f>
@@ -4437,11 +4401,11 @@
       </c>
       <c r="I25" s="52">
         <f>G25*H25</f>
-        <v>27265.507300264391</v>
+        <v>26800.236651928823</v>
       </c>
       <c r="J25" s="53">
         <f>I25-F25</f>
-        <v>1910.3597276292239</v>
+        <v>1445.0890792936552</v>
       </c>
       <c r="K25" s="54"/>
       <c r="M25" s="36">
@@ -4466,11 +4430,11 @@
       <c r="H26" s="52"/>
       <c r="I26" s="52">
         <f>V!J62</f>
-        <v>2456.9645951879311</v>
+        <v>2415.0378671226317</v>
       </c>
       <c r="J26" s="53">
         <f>I26-F26</f>
-        <v>172.14740085955964</v>
+        <v>130.22067279426028</v>
       </c>
       <c r="K26" s="54"/>
       <c r="M26" s="36">
@@ -4518,7 +4482,7 @@
       </c>
       <c r="G28" s="52">
         <f>V!G74</f>
-        <v>3.4956669525323871</v>
+        <v>3.3959918184269315</v>
       </c>
       <c r="H28" s="52">
         <f>V!I74</f>
@@ -4526,11 +4490,11 @@
       </c>
       <c r="I28" s="52">
         <f>G28*H28</f>
-        <v>38328.100474363251</v>
+        <v>37235.216453469351</v>
       </c>
       <c r="J28" s="53">
         <f>I28-F28</f>
-        <v>80.367630554523203</v>
+        <v>-1012.5163903393768</v>
       </c>
       <c r="K28" s="54"/>
       <c r="M28" s="36">
@@ -4555,11 +4519,11 @@
       <c r="H29" s="52"/>
       <c r="I29" s="52">
         <f>V!J75</f>
-        <v>1630.4592106521038</v>
+        <v>1583.9684428867447</v>
       </c>
       <c r="J29" s="53">
         <f>I29-F29</f>
-        <v>3.4188008759670083</v>
+        <v>-43.071966889392115</v>
       </c>
       <c r="K29" s="54"/>
       <c r="M29" s="36">
@@ -4584,11 +4548,11 @@
       <c r="H30" s="52"/>
       <c r="I30" s="52">
         <f>V!J76</f>
-        <v>649.31733989932889</v>
+        <v>630.80276347934773</v>
       </c>
       <c r="J30" s="53">
         <f t="shared" ref="J30:J33" si="4">I30-F30</f>
-        <v>1.3615101045922984</v>
+        <v>-17.153066315388855</v>
       </c>
       <c r="K30" s="54"/>
     </row>
@@ -4609,11 +4573,11 @@
       <c r="H31" s="52"/>
       <c r="I31" s="52">
         <f>V!J77</f>
-        <v>1320.2785911286353</v>
+        <v>1282.6322857413404</v>
       </c>
       <c r="J31" s="53">
         <f t="shared" si="4"/>
-        <v>2.7684038793379386</v>
+        <v>-34.877901507956949</v>
       </c>
       <c r="K31" s="54"/>
     </row>
@@ -4634,11 +4598,11 @@
       <c r="H32" s="52"/>
       <c r="I32" s="52">
         <f>V!J78</f>
-        <v>191.64201716082906</v>
+        <v>186.17755386380142</v>
       </c>
       <c r="J32" s="53">
         <f t="shared" si="4"/>
-        <v>0.40184132903240766</v>
+        <v>-5.0626219679952271</v>
       </c>
       <c r="K32" s="54"/>
     </row>
@@ -4659,11 +4623,11 @@
       <c r="H33" s="52"/>
       <c r="I33" s="52">
         <f>V!J79</f>
-        <v>28.175075637411044</v>
+        <v>27.371694056521068</v>
       </c>
       <c r="J33" s="53">
         <f t="shared" si="4"/>
-        <v>5.9078431794130637E-2</v>
+        <v>-0.74430314909584538</v>
       </c>
       <c r="K33" s="54"/>
     </row>
@@ -4707,7 +4671,7 @@
       </c>
       <c r="G35" s="52">
         <f>V!G86</f>
-        <v>52.465734464637528</v>
+        <v>51.032688232543656</v>
       </c>
       <c r="H35" s="52">
         <f>V!I86</f>
@@ -4715,11 +4679,11 @@
       </c>
       <c r="I35" s="52">
         <f>G35*H35</f>
-        <v>471553.10219330312</v>
+        <v>458673.12627710286</v>
       </c>
       <c r="J35" s="53">
         <f>I35-F35</f>
-        <v>244.28154502512189</v>
+        <v>-12635.694371175137</v>
       </c>
       <c r="K35" s="54"/>
       <c r="M35" s="36">
@@ -4744,11 +4708,11 @@
       <c r="H36" s="52"/>
       <c r="I36" s="52">
         <f>V!J87</f>
-        <v>7999.0675339616919</v>
+        <v>7780.5814361918337</v>
       </c>
       <c r="J36" s="53">
         <f>I36-F36</f>
-        <v>4.1438060037507967</v>
+        <v>-214.34229176610734</v>
       </c>
       <c r="K36" s="54"/>
       <c r="M36" s="36">
@@ -4773,11 +4737,11 @@
       <c r="H37" s="52"/>
       <c r="I37" s="52">
         <f>V!J88</f>
-        <v>9009.1439399000919</v>
+        <v>8763.0686698366007</v>
       </c>
       <c r="J37" s="53">
         <f t="shared" ref="J37:J39" si="6">I37-F37</f>
-        <v>4.6670620779623277</v>
+        <v>-241.40820798552886</v>
       </c>
       <c r="K37" s="54"/>
     </row>
@@ -4798,11 +4762,11 @@
       <c r="H38" s="52"/>
       <c r="I38" s="52">
         <f>V!J89</f>
-        <v>20200.79149985611</v>
+        <v>19649.028173952527</v>
       </c>
       <c r="J38" s="53">
         <f t="shared" si="6"/>
-        <v>10.464739889022894</v>
+        <v>-541.29858601455999</v>
       </c>
       <c r="K38" s="54"/>
     </row>
@@ -4823,11 +4787,11 @@
       <c r="H39" s="52"/>
       <c r="I39" s="52">
         <f>V!J90</f>
-        <v>422.87381978497842</v>
+        <v>411.32346715430185</v>
       </c>
       <c r="J39" s="53">
         <f t="shared" si="6"/>
-        <v>0.21906391786467339</v>
+        <v>-11.331288712811897</v>
       </c>
       <c r="K39" s="54"/>
     </row>
@@ -5087,16 +5051,29 @@
       <c r="H49" s="63"/>
       <c r="I49" s="63">
         <f>SUM(I13:I47)</f>
-        <v>805280.71818867093</v>
+        <v>789632.08517511096</v>
       </c>
       <c r="J49" s="64">
         <f>I49-F49</f>
-        <v>18307.172215697938</v>
+        <v>2658.5392021379666</v>
       </c>
       <c r="K49" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="I9:K9"/>
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="B11:B12"/>
@@ -5104,23 +5081,10 @@
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="G11:I11"/>
     <mergeCell ref="J11:J12"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="85" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup scale="80" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;LPrepared By:
 &amp;CChecked By:
@@ -5151,230 +5115,230 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="93" t="s">
+      <c r="A4" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="93"/>
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="93"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
     </row>
     <row r="5" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="94" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="94"/>
-      <c r="K5" s="94"/>
+      <c r="A5" s="82" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
     </row>
     <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="95" t="s">
+      <c r="A6" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="96"/>
-      <c r="H6" s="97" t="s">
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="97"/>
-      <c r="J6" s="97"/>
-      <c r="K6" s="97"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="78"/>
+      <c r="K6" s="78"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="98" t="s">
+      <c r="A7" s="72" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="98"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="100" t="s">
-        <v>78</v>
-      </c>
-      <c r="I7" s="100"/>
-      <c r="J7" s="100"/>
-      <c r="K7" s="100"/>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="73" t="s">
+        <v>101</v>
+      </c>
+      <c r="I7" s="73"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="73"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="101" t="s">
+      <c r="A8" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="102" t="s">
+      <c r="B8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="101" t="s">
+      <c r="C8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="103" t="s">
+      <c r="D8" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="103" t="s">
+      <c r="E8" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="103" t="s">
+      <c r="F8" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="103" t="s">
+      <c r="G8" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="101" t="s">
+      <c r="H8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="103" t="s">
+      <c r="I8" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="103" t="s">
+      <c r="J8" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="K8" s="104" t="s">
+      <c r="K8" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="105">
+      <c r="A9" s="2">
         <v>1</v>
       </c>
-      <c r="B9" s="106" t="s">
+      <c r="B9" s="69" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="107" t="s">
+      <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="108" t="s">
+      <c r="E9" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="108" t="s">
+      <c r="F9" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="108"/>
-      <c r="H9" s="109"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="7"/>
       <c r="I9" s="6"/>
-      <c r="J9" s="110"/>
-      <c r="K9" s="111"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="5"/>
     </row>
     <row r="10" spans="1:18" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="112"/>
-      <c r="B10" s="113" t="s">
+      <c r="A10" s="16"/>
+      <c r="B10" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="114">
+      <c r="C10" s="44">
         <f>4</f>
         <v>4</v>
       </c>
-      <c r="D10" s="115">
+      <c r="D10" s="9">
         <f>(12+1)/3.281</f>
         <v>3.9622066443157573</v>
       </c>
-      <c r="E10" s="115">
+      <c r="E10" s="9">
         <v>6.5</v>
       </c>
-      <c r="F10" s="115">
+      <c r="F10" s="9">
         <f t="shared" ref="F10:F31" si="0">PRODUCT(C10:E10)</f>
         <v>103.0173727522097</v>
       </c>
-      <c r="G10" s="115">
+      <c r="G10" s="9">
         <f t="shared" ref="G10:G31" si="1">F10</f>
         <v>103.0173727522097</v>
       </c>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="110"/>
-      <c r="K10" s="116"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="27"/>
     </row>
     <row r="11" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="112"/>
-      <c r="B11" s="113" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="114">
+      <c r="C11" s="44">
         <v>4</v>
       </c>
-      <c r="D11" s="115">
+      <c r="D11" s="9">
         <f>11.5/3.281</f>
         <v>3.5050289545870159</v>
       </c>
-      <c r="E11" s="115">
+      <c r="E11" s="9">
         <v>6.5</v>
       </c>
-      <c r="F11" s="115">
+      <c r="F11" s="9">
         <f t="shared" si="0"/>
         <v>91.130752819262412</v>
       </c>
-      <c r="G11" s="115">
+      <c r="G11" s="9">
         <f t="shared" si="1"/>
         <v>91.130752819262412</v>
       </c>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="110"/>
-      <c r="K11" s="116"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="27"/>
       <c r="Q11" s="36">
         <f>PRODUCT(C11:D11)</f>
         <v>14.020115818348064</v>
@@ -5385,592 +5349,592 @@
       </c>
     </row>
     <row r="12" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="112"/>
-      <c r="B12" s="113" t="s">
+      <c r="A12" s="16"/>
+      <c r="B12" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="114">
+      <c r="C12" s="44">
         <v>2</v>
       </c>
-      <c r="D12" s="115">
+      <c r="D12" s="9">
         <f>11.5/3.281</f>
         <v>3.5050289545870159</v>
       </c>
-      <c r="E12" s="115">
+      <c r="E12" s="9">
         <v>6.5</v>
       </c>
-      <c r="F12" s="115">
+      <c r="F12" s="9">
         <f t="shared" si="0"/>
         <v>45.565376409631206</v>
       </c>
-      <c r="G12" s="115">
+      <c r="G12" s="9">
         <f t="shared" si="1"/>
         <v>45.565376409631206</v>
       </c>
-      <c r="H12" s="110"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="110"/>
-      <c r="K12" s="116"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="27"/>
     </row>
     <row r="13" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="112"/>
-      <c r="B13" s="113" t="s">
+      <c r="A13" s="16"/>
+      <c r="B13" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="114">
+      <c r="C13" s="44">
         <v>4</v>
       </c>
-      <c r="D13" s="115">
+      <c r="D13" s="9">
         <v>1.5</v>
       </c>
-      <c r="E13" s="115">
+      <c r="E13" s="9">
         <v>6.5</v>
       </c>
-      <c r="F13" s="115">
+      <c r="F13" s="9">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="G13" s="115">
+      <c r="G13" s="9">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="H13" s="110"/>
-      <c r="I13" s="110"/>
-      <c r="J13" s="110"/>
-      <c r="K13" s="116"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="27"/>
     </row>
     <row r="14" spans="1:18" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="112"/>
-      <c r="B14" s="113"/>
-      <c r="C14" s="114">
+      <c r="A14" s="16"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="44">
         <v>1</v>
       </c>
-      <c r="D14" s="115">
+      <c r="D14" s="9">
         <f>0.45</f>
         <v>0.45</v>
       </c>
-      <c r="E14" s="115">
+      <c r="E14" s="9">
         <v>6.5</v>
       </c>
-      <c r="F14" s="115">
+      <c r="F14" s="9">
         <f t="shared" ref="F14" si="2">PRODUCT(C14:E14)</f>
         <v>2.9250000000000003</v>
       </c>
-      <c r="G14" s="115">
+      <c r="G14" s="9">
         <f t="shared" ref="G14" si="3">F14</f>
         <v>2.9250000000000003</v>
       </c>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110"/>
-      <c r="J14" s="110"/>
-      <c r="K14" s="116"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="27"/>
     </row>
     <row r="15" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="112"/>
-      <c r="B15" s="113" t="s">
+      <c r="A15" s="16"/>
+      <c r="B15" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="114">
+      <c r="C15" s="44">
         <v>2</v>
       </c>
-      <c r="D15" s="115">
+      <c r="D15" s="9">
         <f>9/3.281</f>
         <v>2.7430661383724475</v>
       </c>
-      <c r="E15" s="115">
+      <c r="E15" s="9">
         <v>4.43</v>
       </c>
-      <c r="F15" s="115">
+      <c r="F15" s="9">
         <f t="shared" si="0"/>
         <v>24.303565985979883</v>
       </c>
-      <c r="G15" s="115">
+      <c r="G15" s="9">
         <f t="shared" si="1"/>
         <v>24.303565985979883</v>
       </c>
-      <c r="H15" s="110"/>
-      <c r="I15" s="110"/>
-      <c r="J15" s="110"/>
-      <c r="K15" s="116"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="27"/>
     </row>
     <row r="16" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="112"/>
-      <c r="B16" s="113" t="s">
+      <c r="A16" s="16"/>
+      <c r="B16" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="114">
+      <c r="C16" s="44">
         <v>4</v>
       </c>
-      <c r="D16" s="115">
+      <c r="D16" s="9">
         <f>5.75/3.281</f>
         <v>1.752514477293508</v>
       </c>
-      <c r="E16" s="115">
+      <c r="E16" s="9">
         <v>4.43</v>
       </c>
-      <c r="F16" s="115">
+      <c r="F16" s="9">
         <f t="shared" si="0"/>
         <v>31.054556537640959</v>
       </c>
-      <c r="G16" s="115">
+      <c r="G16" s="9">
         <f t="shared" si="1"/>
         <v>31.054556537640959</v>
       </c>
-      <c r="H16" s="110"/>
-      <c r="I16" s="110"/>
-      <c r="J16" s="110"/>
-      <c r="K16" s="116"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="27"/>
     </row>
     <row r="17" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="112"/>
-      <c r="B17" s="113"/>
-      <c r="C17" s="114">
+      <c r="A17" s="16"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="44">
         <v>4</v>
       </c>
-      <c r="D17" s="115">
+      <c r="D17" s="9">
         <f>77/12/3.281</f>
         <v>1.9557045616173931</v>
       </c>
-      <c r="E17" s="115">
+      <c r="E17" s="9">
         <v>4.43</v>
       </c>
-      <c r="F17" s="115">
+      <c r="F17" s="9">
         <f t="shared" ref="F17" si="4">PRODUCT(C17:E17)</f>
         <v>34.655084831860208</v>
       </c>
-      <c r="G17" s="115">
+      <c r="G17" s="9">
         <f t="shared" ref="G17" si="5">F17</f>
         <v>34.655084831860208</v>
       </c>
-      <c r="H17" s="110"/>
-      <c r="I17" s="110"/>
-      <c r="J17" s="110"/>
-      <c r="K17" s="116"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="27"/>
     </row>
     <row r="18" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="112"/>
-      <c r="B18" s="113" t="s">
+      <c r="A18" s="16"/>
+      <c r="B18" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="114">
+      <c r="C18" s="44">
         <f>4</f>
         <v>4</v>
       </c>
-      <c r="D18" s="115">
+      <c r="D18" s="9">
         <f>10.67/3.281</f>
         <v>3.2520572996037793</v>
       </c>
-      <c r="E18" s="115">
+      <c r="E18" s="9">
         <v>4.43</v>
       </c>
-      <c r="F18" s="115">
+      <c r="F18" s="9">
         <f t="shared" si="0"/>
         <v>57.626455348978965</v>
       </c>
-      <c r="G18" s="115">
+      <c r="G18" s="9">
         <f t="shared" si="1"/>
         <v>57.626455348978965</v>
       </c>
-      <c r="H18" s="110"/>
-      <c r="I18" s="110"/>
-      <c r="J18" s="110"/>
-      <c r="K18" s="116"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="27"/>
     </row>
     <row r="19" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="112"/>
-      <c r="B19" s="113"/>
-      <c r="C19" s="114">
+      <c r="A19" s="16"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="44">
         <f>4</f>
         <v>4</v>
       </c>
-      <c r="D19" s="115">
+      <c r="D19" s="9">
         <f>15/3.281</f>
         <v>4.5717768972874122</v>
       </c>
-      <c r="E19" s="115">
+      <c r="E19" s="9">
         <v>4.43</v>
       </c>
-      <c r="F19" s="115">
+      <c r="F19" s="9">
         <f t="shared" si="0"/>
         <v>81.011886619932937</v>
       </c>
-      <c r="G19" s="115">
+      <c r="G19" s="9">
         <f t="shared" si="1"/>
         <v>81.011886619932937</v>
       </c>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="116"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="27"/>
     </row>
     <row r="20" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="112"/>
-      <c r="B20" s="113" t="s">
+      <c r="A20" s="16"/>
+      <c r="B20" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="114">
+      <c r="C20" s="44">
         <f>4*1</f>
         <v>4</v>
       </c>
-      <c r="D20" s="115">
+      <c r="D20" s="9">
         <f>6.42/3.281</f>
         <v>1.9567205120390123</v>
       </c>
-      <c r="E20" s="115">
+      <c r="E20" s="9">
         <v>4.43</v>
       </c>
-      <c r="F20" s="115">
+      <c r="F20" s="9">
         <f t="shared" si="0"/>
         <v>34.673087473331293</v>
       </c>
-      <c r="G20" s="115">
+      <c r="G20" s="9">
         <f t="shared" si="1"/>
         <v>34.673087473331293</v>
       </c>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="116"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="27"/>
     </row>
     <row r="21" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="112"/>
-      <c r="B21" s="113"/>
-      <c r="C21" s="114">
+      <c r="A21" s="16"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="44">
         <f>4*2</f>
         <v>8</v>
       </c>
-      <c r="D21" s="115">
+      <c r="D21" s="9">
         <f>6.42/3.281</f>
         <v>1.9567205120390123</v>
       </c>
-      <c r="E21" s="115">
+      <c r="E21" s="9">
         <v>4.43</v>
       </c>
-      <c r="F21" s="115">
+      <c r="F21" s="9">
         <f t="shared" ref="F21" si="6">PRODUCT(C21:E21)</f>
         <v>69.346174946662586</v>
       </c>
-      <c r="G21" s="115">
+      <c r="G21" s="9">
         <f t="shared" ref="G21" si="7">F21</f>
         <v>69.346174946662586</v>
       </c>
-      <c r="H21" s="110"/>
-      <c r="I21" s="110"/>
-      <c r="J21" s="110"/>
-      <c r="K21" s="116"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="27"/>
     </row>
     <row r="22" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="112"/>
-      <c r="B22" s="113" t="s">
+      <c r="A22" s="16"/>
+      <c r="B22" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="114">
+      <c r="C22" s="44">
         <v>4</v>
       </c>
-      <c r="D22" s="115">
+      <c r="D22" s="9">
         <f>8/12/3.281</f>
         <v>0.20319008432388497</v>
       </c>
-      <c r="E22" s="115">
+      <c r="E22" s="9">
         <v>4.43</v>
       </c>
-      <c r="F22" s="115">
+      <c r="F22" s="9">
         <f t="shared" si="0"/>
         <v>3.6005282942192416</v>
       </c>
-      <c r="G22" s="115">
+      <c r="G22" s="9">
         <f t="shared" si="1"/>
         <v>3.6005282942192416</v>
       </c>
-      <c r="H22" s="110"/>
-      <c r="I22" s="110"/>
-      <c r="J22" s="110"/>
-      <c r="K22" s="116"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="27"/>
     </row>
     <row r="23" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="112"/>
-      <c r="B23" s="113"/>
-      <c r="C23" s="114">
+      <c r="A23" s="16"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="44">
         <v>4</v>
       </c>
-      <c r="D23" s="115">
+      <c r="D23" s="9">
         <f>54/12/3.281</f>
         <v>1.3715330691862238</v>
       </c>
-      <c r="E23" s="115">
+      <c r="E23" s="9">
         <v>4.43</v>
       </c>
-      <c r="F23" s="115">
+      <c r="F23" s="9">
         <f t="shared" si="0"/>
         <v>24.303565985979883</v>
       </c>
-      <c r="G23" s="115">
+      <c r="G23" s="9">
         <f t="shared" si="1"/>
         <v>24.303565985979883</v>
       </c>
-      <c r="H23" s="110"/>
-      <c r="I23" s="110"/>
-      <c r="J23" s="110"/>
-      <c r="K23" s="116"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="27"/>
     </row>
     <row r="24" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="112"/>
-      <c r="B24" s="113"/>
-      <c r="C24" s="114">
+      <c r="A24" s="16"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="44">
         <v>4</v>
       </c>
-      <c r="D24" s="115">
+      <c r="D24" s="9">
         <f>105/12/3.281</f>
         <v>2.6668698567509903</v>
       </c>
-      <c r="E24" s="115">
+      <c r="E24" s="9">
         <v>4.43</v>
       </c>
-      <c r="F24" s="115">
+      <c r="F24" s="9">
         <f t="shared" ref="F24" si="8">PRODUCT(C24:E24)</f>
         <v>47.256933861627545</v>
       </c>
-      <c r="G24" s="115">
+      <c r="G24" s="9">
         <f t="shared" ref="G24" si="9">F24</f>
         <v>47.256933861627545</v>
       </c>
-      <c r="H24" s="110"/>
-      <c r="I24" s="110"/>
-      <c r="J24" s="110"/>
-      <c r="K24" s="116"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="27"/>
     </row>
     <row r="25" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="112"/>
-      <c r="B25" s="113" t="s">
+      <c r="A25" s="16"/>
+      <c r="B25" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="114">
+      <c r="C25" s="44">
         <v>4</v>
       </c>
-      <c r="D25" s="115">
+      <c r="D25" s="9">
         <f>75/12/3.281</f>
         <v>1.9049070405364217</v>
       </c>
-      <c r="E25" s="115">
+      <c r="E25" s="9">
         <v>4.43</v>
       </c>
-      <c r="F25" s="115">
+      <c r="F25" s="9">
         <f t="shared" si="0"/>
         <v>33.754952758305393</v>
       </c>
-      <c r="G25" s="115">
+      <c r="G25" s="9">
         <f t="shared" si="1"/>
         <v>33.754952758305393</v>
       </c>
-      <c r="H25" s="110"/>
-      <c r="I25" s="110"/>
-      <c r="J25" s="110"/>
-      <c r="K25" s="116"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="27"/>
     </row>
     <row r="26" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="112"/>
-      <c r="B26" s="113"/>
-      <c r="C26" s="114">
+      <c r="A26" s="16"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="44">
         <f>4*2</f>
         <v>8</v>
       </c>
-      <c r="D26" s="115">
+      <c r="D26" s="9">
         <f>(36+37)/12/3.281</f>
         <v>1.8541095194554504</v>
       </c>
-      <c r="E26" s="115">
+      <c r="E26" s="9">
         <v>4.43</v>
       </c>
-      <c r="F26" s="115">
+      <c r="F26" s="9">
         <f t="shared" ref="F26" si="10">PRODUCT(C26:E26)</f>
         <v>65.709641369501156</v>
       </c>
-      <c r="G26" s="115">
+      <c r="G26" s="9">
         <f t="shared" ref="G26" si="11">F26</f>
         <v>65.709641369501156</v>
       </c>
-      <c r="H26" s="110"/>
-      <c r="I26" s="110"/>
-      <c r="J26" s="110"/>
-      <c r="K26" s="116"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="27"/>
     </row>
     <row r="27" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="112"/>
-      <c r="B27" s="113" t="s">
+      <c r="A27" s="16"/>
+      <c r="B27" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="114">
+      <c r="C27" s="44">
         <v>1</v>
       </c>
-      <c r="D27" s="115">
+      <c r="D27" s="9">
         <f>6/3.281</f>
         <v>1.8287107589149649</v>
       </c>
-      <c r="E27" s="115">
+      <c r="E27" s="9">
         <v>3.01</v>
       </c>
-      <c r="F27" s="115">
+      <c r="F27" s="9">
         <f t="shared" si="0"/>
         <v>5.5044193843340441</v>
       </c>
-      <c r="G27" s="115">
+      <c r="G27" s="9">
         <f t="shared" si="1"/>
         <v>5.5044193843340441</v>
       </c>
-      <c r="H27" s="110"/>
-      <c r="I27" s="110"/>
-      <c r="J27" s="110"/>
-      <c r="K27" s="116"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="27"/>
     </row>
     <row r="28" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="112"/>
-      <c r="B28" s="113"/>
-      <c r="C28" s="114">
+      <c r="A28" s="16"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="44">
         <v>4</v>
       </c>
-      <c r="D28" s="115">
+      <c r="D28" s="9">
         <v>1.5</v>
       </c>
-      <c r="E28" s="115">
+      <c r="E28" s="9">
         <v>3.01</v>
       </c>
-      <c r="F28" s="115">
+      <c r="F28" s="9">
         <f t="shared" si="0"/>
         <v>18.059999999999999</v>
       </c>
-      <c r="G28" s="115">
+      <c r="G28" s="9">
         <f t="shared" si="1"/>
         <v>18.059999999999999</v>
       </c>
-      <c r="H28" s="110"/>
-      <c r="I28" s="110"/>
-      <c r="J28" s="110"/>
-      <c r="K28" s="116"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="27"/>
     </row>
     <row r="29" spans="1:11" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="112"/>
-      <c r="B29" s="113" t="s">
-        <v>99</v>
-      </c>
-      <c r="C29" s="114">
+      <c r="A29" s="16"/>
+      <c r="B29" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" s="44">
         <v>1</v>
       </c>
-      <c r="D29" s="115">
+      <c r="D29" s="9">
         <f>(7+65/12+76/12+74/12+6)/3.281</f>
         <v>9.4229401605201666</v>
       </c>
-      <c r="E29" s="115">
+      <c r="E29" s="9">
         <v>2.2599999999999998</v>
       </c>
-      <c r="F29" s="115">
+      <c r="F29" s="9">
         <f t="shared" si="0"/>
         <v>21.295844762775573</v>
       </c>
-      <c r="G29" s="115">
+      <c r="G29" s="9">
         <f t="shared" si="1"/>
         <v>21.295844762775573</v>
       </c>
-      <c r="H29" s="110"/>
-      <c r="I29" s="110"/>
-      <c r="J29" s="110"/>
-      <c r="K29" s="116"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="27"/>
     </row>
     <row r="30" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="112"/>
-      <c r="B30" s="113"/>
-      <c r="C30" s="114">
+      <c r="A30" s="16"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="44">
         <v>2</v>
       </c>
-      <c r="D30" s="115">
+      <c r="D30" s="9">
         <f>(69+72+75+64+82)/12/3.281</f>
         <v>9.1943513156557959</v>
       </c>
-      <c r="E30" s="115">
+      <c r="E30" s="9">
         <v>2.2599999999999998</v>
       </c>
-      <c r="F30" s="115">
+      <c r="F30" s="9">
         <f t="shared" si="0"/>
         <v>41.558467946764196</v>
       </c>
-      <c r="G30" s="115">
+      <c r="G30" s="9">
         <f t="shared" si="1"/>
         <v>41.558467946764196</v>
       </c>
-      <c r="H30" s="110"/>
-      <c r="I30" s="110"/>
-      <c r="J30" s="110"/>
-      <c r="K30" s="116"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="27"/>
     </row>
     <row r="31" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="112"/>
-      <c r="B31" s="113"/>
-      <c r="C31" s="114">
+      <c r="A31" s="16"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="44">
         <v>1</v>
       </c>
-      <c r="D31" s="115">
+      <c r="D31" s="9">
         <f>82/12/3.281</f>
         <v>2.0826983643198211</v>
       </c>
-      <c r="E31" s="115">
+      <c r="E31" s="9">
         <v>2.2599999999999998</v>
       </c>
-      <c r="F31" s="115">
+      <c r="F31" s="9">
         <f t="shared" si="0"/>
         <v>4.7068983033627951</v>
       </c>
-      <c r="G31" s="115">
+      <c r="G31" s="9">
         <f t="shared" si="1"/>
         <v>4.7068983033627951</v>
       </c>
-      <c r="H31" s="110"/>
-      <c r="I31" s="110"/>
-      <c r="J31" s="110"/>
-      <c r="K31" s="116"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="27"/>
     </row>
     <row r="32" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="105"/>
-      <c r="B32" s="113" t="s">
+      <c r="A32" s="2"/>
+      <c r="B32" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="107"/>
+      <c r="C32" s="3"/>
       <c r="D32" s="4"/>
-      <c r="E32" s="111"/>
-      <c r="F32" s="111"/>
-      <c r="G32" s="110">
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="42">
         <f>SUM(G10:G31)</f>
         <v>880.06056639235987</v>
       </c>
-      <c r="H32" s="109" t="s">
+      <c r="H32" s="7" t="s">
         <v>40</v>
       </c>
       <c r="I32" s="6">
         <v>182.51</v>
       </c>
-      <c r="J32" s="110">
+      <c r="J32" s="42">
         <f>G32*I32</f>
         <v>160619.8539722696</v>
       </c>
-      <c r="K32" s="111"/>
-    </row>
-    <row r="33" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="105"/>
-      <c r="B33" s="113" t="s">
+      <c r="K32" s="5"/>
+    </row>
+    <row r="33" spans="1:18" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="107"/>
+      <c r="C33" s="3"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="111"/>
-      <c r="F33" s="111"/>
-      <c r="G33" s="110"/>
-      <c r="H33" s="109"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="7"/>
       <c r="I33" s="6"/>
-      <c r="J33" s="110">
+      <c r="J33" s="42">
         <f>0.13*G32*(1871.42/18.94)</f>
         <v>11304.391915023165</v>
       </c>
-      <c r="K33" s="111"/>
-    </row>
-    <row r="34" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K33" s="5"/>
+    </row>
+    <row r="34" spans="1:18" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="43"/>
       <c r="C34" s="3"/>
@@ -5982,8 +5946,9 @@
       <c r="I34" s="6"/>
       <c r="J34" s="42"/>
       <c r="K34" s="5"/>
-    </row>
-    <row r="35" spans="1:11" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="R34" s="96"/>
+    </row>
+    <row r="35" spans="1:18" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>2</v>
       </c>
@@ -5999,8 +5964,9 @@
       <c r="I35" s="6"/>
       <c r="J35" s="42"/>
       <c r="K35" s="5"/>
-    </row>
-    <row r="36" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="R35" s="96"/>
+    </row>
+    <row r="36" spans="1:18" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="43" t="s">
         <v>52</v>
@@ -6026,7 +5992,7 @@
       <c r="J36" s="42"/>
       <c r="K36" s="5"/>
     </row>
-    <row r="37" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="43" t="s">
         <v>53</v>
@@ -6052,7 +6018,7 @@
       <c r="J37" s="42"/>
       <c r="K37" s="5"/>
     </row>
-    <row r="38" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="43" t="s">
         <v>39</v>
@@ -6077,7 +6043,7 @@
       </c>
       <c r="K38" s="5"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="16"/>
       <c r="B39" s="32" t="s">
         <v>55</v>
@@ -6095,7 +6061,7 @@
       </c>
       <c r="K39" s="17"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="16"/>
       <c r="B40" s="32" t="s">
         <v>56</v>
@@ -6113,7 +6079,7 @@
       </c>
       <c r="K40" s="17"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="16"/>
       <c r="B41" s="32" t="s">
         <v>57</v>
@@ -6131,7 +6097,7 @@
       </c>
       <c r="K41" s="17"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="16"/>
       <c r="B42" s="32" t="s">
         <v>58</v>
@@ -6149,7 +6115,7 @@
       </c>
       <c r="K42" s="17"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="16"/>
       <c r="B43" s="32"/>
       <c r="C43" s="17"/>
@@ -6162,7 +6128,7 @@
       <c r="J43" s="18"/>
       <c r="K43" s="17"/>
     </row>
-    <row r="44" spans="1:11" ht="150" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="150" x14ac:dyDescent="0.25">
       <c r="A44" s="16">
         <v>3</v>
       </c>
@@ -6179,7 +6145,7 @@
       <c r="J44" s="18"/>
       <c r="K44" s="17"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="16"/>
       <c r="B45" s="32" t="s">
         <v>61</v>
@@ -6193,21 +6159,21 @@
       </c>
       <c r="E45" s="17">
         <f>E54</f>
-        <v>1.75</v>
+        <v>1.7375</v>
       </c>
       <c r="F45" s="33">
         <v>0.9</v>
       </c>
       <c r="G45" s="33">
         <f t="shared" ref="G45:G49" si="13">PRODUCT(C45:F45)</f>
-        <v>15.001142944224325</v>
+        <v>14.89399192319415</v>
       </c>
       <c r="H45" s="17"/>
       <c r="I45" s="17"/>
       <c r="J45" s="18"/>
       <c r="K45" s="17"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="16"/>
       <c r="B46" s="32"/>
       <c r="C46" s="17">
@@ -6219,21 +6185,21 @@
       </c>
       <c r="E46" s="33">
         <f>E55</f>
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F46" s="17">
         <v>0.75</v>
       </c>
       <c r="G46" s="33">
         <f t="shared" si="13"/>
-        <v>5.8671898811338012</v>
+        <v>5.5738303870771109</v>
       </c>
       <c r="H46" s="17"/>
       <c r="I46" s="17"/>
       <c r="J46" s="18"/>
       <c r="K46" s="17"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="16"/>
       <c r="B47" s="32" t="s">
         <v>65</v>
@@ -6259,7 +6225,7 @@
       <c r="J47" s="18"/>
       <c r="K47" s="17"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="16"/>
       <c r="B48" s="32" t="s">
         <v>66</v>
@@ -6295,17 +6261,17 @@
         <v>5</v>
       </c>
       <c r="D49" s="33">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="E49" s="33">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="F49" s="33">
         <v>0.3</v>
       </c>
       <c r="G49" s="33">
         <f t="shared" si="13"/>
-        <v>0.13499999999999998</v>
+        <v>7.9350000000000018E-2</v>
       </c>
       <c r="H49" s="17"/>
       <c r="I49" s="17"/>
@@ -6323,7 +6289,7 @@
       <c r="F50" s="5"/>
       <c r="G50" s="42">
         <f>SUM(G45:G49)</f>
-        <v>23.338318500457184</v>
+        <v>22.882157985370316</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>63</v>
@@ -6333,7 +6299,7 @@
       </c>
       <c r="J50" s="42">
         <f>G50*I50</f>
-        <v>1469.1471496037798</v>
+        <v>1440.4318451790614</v>
       </c>
       <c r="K50" s="5"/>
     </row>
@@ -6351,7 +6317,7 @@
       <c r="I51" s="17"/>
       <c r="J51" s="18">
         <f>0.13*G50*18612/360</f>
-        <v>156.85683864157275</v>
+        <v>153.7909838196739</v>
       </c>
       <c r="K51" s="17"/>
     </row>
@@ -6399,14 +6365,14 @@
       </c>
       <c r="E54" s="17">
         <f>E65</f>
-        <v>1.75</v>
+        <v>1.7375</v>
       </c>
       <c r="F54" s="17">
         <v>0.15</v>
       </c>
       <c r="G54" s="33">
         <f t="shared" ref="G54:G60" si="14">PRODUCT(C54:F54)</f>
-        <v>2.5001904907040537</v>
+        <v>2.4823319871990246</v>
       </c>
       <c r="H54" s="17"/>
       <c r="I54" s="17"/>
@@ -6425,14 +6391,14 @@
       </c>
       <c r="E55" s="33">
         <f>E67</f>
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F55" s="17">
         <v>0.15</v>
       </c>
       <c r="G55" s="33">
         <f t="shared" si="14"/>
-        <v>1.1734379762267602</v>
+        <v>1.1147660774154222</v>
       </c>
       <c r="H55" s="17"/>
       <c r="I55" s="17"/>
@@ -6559,18 +6525,18 @@
       </c>
       <c r="D60" s="33">
         <f>D49</f>
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="E60" s="33">
         <f>E49</f>
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="F60" s="17">
         <v>0.15</v>
       </c>
       <c r="G60" s="33">
         <f t="shared" si="14"/>
-        <v>6.7499999999999991E-2</v>
+        <v>3.9675000000000009E-2</v>
       </c>
       <c r="H60" s="17"/>
       <c r="I60" s="17"/>
@@ -6588,7 +6554,7 @@
       <c r="F61" s="5"/>
       <c r="G61" s="42">
         <f>SUM(G54:G60)</f>
-        <v>6.1153717601949502</v>
+        <v>6.0110163578785833</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>63</v>
@@ -6598,7 +6564,7 @@
       </c>
       <c r="J61" s="42">
         <f>G61*I61</f>
-        <v>27265.507300264391</v>
+        <v>26800.236651928823</v>
       </c>
       <c r="K61" s="5"/>
     </row>
@@ -6616,7 +6582,7 @@
       <c r="I62" s="17"/>
       <c r="J62" s="18">
         <f>0.13*G61*15452.64/5</f>
-        <v>2456.9645951879311</v>
+        <v>2415.0378671226317</v>
       </c>
       <c r="K62" s="17"/>
     </row>
@@ -6633,7 +6599,7 @@
       <c r="J63" s="18"/>
       <c r="K63" s="17"/>
     </row>
-    <row r="64" spans="1:11" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A64" s="16">
         <v>5</v>
       </c>
@@ -6664,14 +6630,14 @@
       </c>
       <c r="E65" s="33">
         <f>F82/2</f>
-        <v>1.75</v>
+        <v>1.7375</v>
       </c>
       <c r="F65" s="17">
         <v>0.05</v>
       </c>
       <c r="G65" s="33">
         <f t="shared" ref="G65:G73" si="15">PRODUCT(C65:F65)</f>
-        <v>0.83339683023468469</v>
+        <v>0.82744399573300831</v>
       </c>
       <c r="H65" s="17"/>
       <c r="I65" s="17"/>
@@ -6715,14 +6681,14 @@
       </c>
       <c r="E67" s="33">
         <f>F83/2</f>
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="F67" s="17">
         <v>0.05</v>
       </c>
       <c r="G67" s="33">
         <f t="shared" si="15"/>
-        <v>0.39114599207558676</v>
+        <v>0.37158869247180742</v>
       </c>
       <c r="H67" s="17"/>
       <c r="I67" s="17"/>
@@ -6874,18 +6840,18 @@
       </c>
       <c r="D73" s="33">
         <f>D60</f>
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="E73" s="33">
         <f>E60</f>
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="F73" s="33">
-        <v>0.3</v>
+        <v>0.23</v>
       </c>
       <c r="G73" s="33">
         <f t="shared" si="15"/>
-        <v>0.13499999999999998</v>
+        <v>6.0835000000000021E-2</v>
       </c>
       <c r="H73" s="17"/>
       <c r="I73" s="17"/>
@@ -6903,7 +6869,7 @@
       <c r="F74" s="5"/>
       <c r="G74" s="42">
         <f>SUM(G65:G73)</f>
-        <v>3.4956669525323871</v>
+        <v>3.3959918184269315</v>
       </c>
       <c r="H74" s="7" t="s">
         <v>63</v>
@@ -6913,7 +6879,7 @@
       </c>
       <c r="J74" s="42">
         <f>G74*I74</f>
-        <v>38328.100474363251</v>
+        <v>37235.216453469351</v>
       </c>
       <c r="K74" s="5"/>
     </row>
@@ -6931,7 +6897,7 @@
       <c r="I75" s="17"/>
       <c r="J75" s="18">
         <f>0.13*G74*53818.03/15</f>
-        <v>1630.4592106521038</v>
+        <v>1583.9684428867447</v>
       </c>
       <c r="K75" s="17"/>
     </row>
@@ -6949,7 +6915,7 @@
       <c r="I76" s="17"/>
       <c r="J76" s="18">
         <f>0.13*G74*21432.6/15</f>
-        <v>649.31733989932889</v>
+        <v>630.80276347934773</v>
       </c>
       <c r="K76" s="17"/>
     </row>
@@ -6967,7 +6933,7 @@
       <c r="I77" s="17"/>
       <c r="J77" s="18">
         <f>0.13*G74*(25719.12+13573.98+4286.52)/15</f>
-        <v>1320.2785911286353</v>
+        <v>1282.6322857413404</v>
       </c>
       <c r="K77" s="17"/>
     </row>
@@ -6985,7 +6951,7 @@
       <c r="I78" s="17"/>
       <c r="J78" s="18">
         <f>0.13*G74*(6325.7/15)</f>
-        <v>191.64201716082906</v>
+        <v>186.17755386380142</v>
       </c>
       <c r="K78" s="17"/>
     </row>
@@ -7003,7 +6969,7 @@
       <c r="I79" s="17"/>
       <c r="J79" s="18">
         <f>0.13*G74*(310)/5</f>
-        <v>28.175075637411044</v>
+        <v>27.371694056521068</v>
       </c>
       <c r="K79" s="17"/>
     </row>
@@ -7051,15 +7017,15 @@
       </c>
       <c r="E82" s="33">
         <f>((F82/2)+0.5)/2</f>
-        <v>1.125</v>
+        <v>1.1187499999999999</v>
       </c>
       <c r="F82" s="33">
-        <f>7/2</f>
-        <v>3.5</v>
+        <f>6.95/2</f>
+        <v>3.4750000000000001</v>
       </c>
       <c r="G82" s="33">
         <f>PRODUCT(C82:F82)</f>
-        <v>37.502857360560803</v>
+        <v>37.028118809052117</v>
       </c>
       <c r="H82" s="17"/>
       <c r="I82" s="17"/>
@@ -7091,14 +7057,14 @@
       </c>
       <c r="E83" s="33">
         <f>((F83/2)+0.5)/2</f>
-        <v>0.75</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="F83" s="33">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="G83" s="33">
         <f>PRODUCT(C83:F83)</f>
-        <v>11.734379762267602</v>
+        <v>10.776072081682413</v>
       </c>
       <c r="H83" s="17"/>
       <c r="I83" s="17"/>
@@ -7185,7 +7151,7 @@
       <c r="F86" s="5"/>
       <c r="G86" s="6">
         <f>SUM(G82:G85)</f>
-        <v>52.465734464637528</v>
+        <v>51.032688232543656</v>
       </c>
       <c r="H86" s="7" t="s">
         <v>63</v>
@@ -7195,7 +7161,7 @@
       </c>
       <c r="J86" s="18">
         <f>G86*I86</f>
-        <v>471553.10219330312</v>
+        <v>458673.12627710286</v>
       </c>
       <c r="K86" s="5"/>
     </row>
@@ -7213,7 +7179,7 @@
       <c r="I87" s="17"/>
       <c r="J87" s="18">
         <f>0.13*G86*(5863.95)/5</f>
-        <v>7999.0675339616919</v>
+        <v>7780.5814361918337</v>
       </c>
       <c r="K87" s="17"/>
     </row>
@@ -7231,7 +7197,7 @@
       <c r="I88" s="17"/>
       <c r="J88" s="18">
         <f>0.13*G86*(6604.416)/5</f>
-        <v>9009.1439399000919</v>
+        <v>8763.0686698366007</v>
       </c>
       <c r="K88" s="17"/>
     </row>
@@ -7249,7 +7215,7 @@
       <c r="I89" s="17"/>
       <c r="J89" s="18">
         <f>0.13*G86*(14808.78)/5</f>
-        <v>20200.79149985611</v>
+        <v>19649.028173952527</v>
       </c>
       <c r="K89" s="17"/>
     </row>
@@ -7267,7 +7233,7 @@
       <c r="I90" s="17"/>
       <c r="J90" s="18">
         <f>0.13*G86*(310)/5</f>
-        <v>422.87381978497842</v>
+        <v>411.32346715430185</v>
       </c>
       <c r="K90" s="17"/>
     </row>
@@ -7544,7 +7510,7 @@
       <c r="I104" s="18"/>
       <c r="J104" s="18">
         <f>SUM(J9:J102)</f>
-        <v>805280.71818867093</v>
+        <v>789632.08517511096</v>
       </c>
       <c r="K104" s="25"/>
     </row>
@@ -7560,13 +7526,13 @@
     <row r="106" spans="1:19" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="26"/>
       <c r="B106" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="C106" s="71">
+        <v>99</v>
+      </c>
+      <c r="C106" s="70">
         <f>J104</f>
-        <v>805280.71818867093</v>
-      </c>
-      <c r="D106" s="72"/>
+        <v>789632.08517511096</v>
+      </c>
+      <c r="D106" s="71"/>
       <c r="E106" s="9">
         <v>100</v>
       </c>
@@ -7588,49 +7554,49 @@
       <c r="B107" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C107" s="75">
+      <c r="C107" s="74">
         <v>700000</v>
       </c>
-      <c r="D107" s="76"/>
+      <c r="D107" s="75"/>
       <c r="E107" s="9"/>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B108" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C108" s="75">
+      <c r="C108" s="74">
         <f>C107-C110-C111</f>
         <v>665000</v>
       </c>
-      <c r="D108" s="76"/>
+      <c r="D108" s="75"/>
       <c r="E108" s="9">
         <f>C108/C106*100</f>
-        <v>82.579898534736273</v>
+        <v>84.21643604470907</v>
       </c>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B109" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C109" s="77">
+      <c r="C109" s="76">
         <f>C106-C108</f>
-        <v>140280.71818867093</v>
-      </c>
-      <c r="D109" s="77"/>
+        <v>124632.08517511096</v>
+      </c>
+      <c r="D109" s="76"/>
       <c r="E109" s="9">
         <f>100-E108</f>
-        <v>17.420101465263727</v>
+        <v>15.78356395529093</v>
       </c>
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B110" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C110" s="71">
+      <c r="C110" s="70">
         <f>C107*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D110" s="72"/>
+      <c r="D110" s="71"/>
       <c r="E110" s="9">
         <v>3</v>
       </c>
@@ -7639,17 +7605,24 @@
       <c r="B111" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C111" s="71">
+      <c r="C111" s="70">
         <f>C107*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D111" s="72"/>
+      <c r="D111" s="71"/>
       <c r="E111" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C110:D110"/>
     <mergeCell ref="C111:D111"/>
     <mergeCell ref="A7:F7"/>
@@ -7658,13 +7631,6 @@
     <mergeCell ref="C107:D107"/>
     <mergeCell ref="C108:D108"/>
     <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
@@ -7675,6 +7641,2548 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45A85263-E899-4633-BF0C-CE33042030BF}">
+  <dimension ref="A1:S111"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.7109375" style="19" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="19" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="19" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="19"/>
+    <col min="8" max="8" width="5" style="19" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" style="19" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="19" hidden="1" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" style="19"/>
+    <col min="13" max="16" width="0" style="19" hidden="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+    </row>
+    <row r="2" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="80" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="81" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="81" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+    </row>
+    <row r="5" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="82" t="s">
+        <v>102</v>
+      </c>
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
+    </row>
+    <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="77" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="10"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="98"/>
+      <c r="K6" s="65" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="72" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="67"/>
+      <c r="I7" s="97"/>
+      <c r="J7" s="97"/>
+      <c r="K7" s="66" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="68" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="68" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="68" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="68" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>1</v>
+      </c>
+      <c r="B9" s="69" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="41"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="5"/>
+    </row>
+    <row r="10" spans="1:18" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="16"/>
+      <c r="B10" s="43" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="44">
+        <f>4</f>
+        <v>4</v>
+      </c>
+      <c r="D10" s="9">
+        <f>(12+1)/3.281</f>
+        <v>3.9622066443157573</v>
+      </c>
+      <c r="E10" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="F10" s="9">
+        <f t="shared" ref="F10:F31" si="0">PRODUCT(C10:E10)</f>
+        <v>103.0173727522097</v>
+      </c>
+      <c r="G10" s="9">
+        <f t="shared" ref="G10:G31" si="1">F10</f>
+        <v>103.0173727522097</v>
+      </c>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="27"/>
+    </row>
+    <row r="11" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="16"/>
+      <c r="B11" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="44">
+        <v>4</v>
+      </c>
+      <c r="D11" s="9">
+        <f>11.5/3.281</f>
+        <v>3.5050289545870159</v>
+      </c>
+      <c r="E11" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="F11" s="9">
+        <f t="shared" si="0"/>
+        <v>91.130752819262412</v>
+      </c>
+      <c r="G11" s="9">
+        <f t="shared" si="1"/>
+        <v>91.130752819262412</v>
+      </c>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="27"/>
+      <c r="Q11" s="36">
+        <f>PRODUCT(C11:D11)</f>
+        <v>14.020115818348064</v>
+      </c>
+      <c r="R11" s="36">
+        <f>CONVERT(Q11,"m","ft")</f>
+        <v>45.997755309540885</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="16"/>
+      <c r="B12" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="44">
+        <v>2</v>
+      </c>
+      <c r="D12" s="9">
+        <f>11.5/3.281</f>
+        <v>3.5050289545870159</v>
+      </c>
+      <c r="E12" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="F12" s="9">
+        <f t="shared" si="0"/>
+        <v>45.565376409631206</v>
+      </c>
+      <c r="G12" s="9">
+        <f t="shared" si="1"/>
+        <v>45.565376409631206</v>
+      </c>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="27"/>
+    </row>
+    <row r="13" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="16"/>
+      <c r="B13" s="43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="44">
+        <v>4</v>
+      </c>
+      <c r="D13" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="E13" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="F13" s="9">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="G13" s="9">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="27"/>
+    </row>
+    <row r="14" spans="1:18" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="44">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9">
+        <f>0.45</f>
+        <v>0.45</v>
+      </c>
+      <c r="E14" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="F14" s="9">
+        <f t="shared" si="0"/>
+        <v>2.9250000000000003</v>
+      </c>
+      <c r="G14" s="9">
+        <f t="shared" si="1"/>
+        <v>2.9250000000000003</v>
+      </c>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="27"/>
+    </row>
+    <row r="15" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="16"/>
+      <c r="B15" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="44">
+        <v>2</v>
+      </c>
+      <c r="D15" s="9">
+        <f>9/3.281</f>
+        <v>2.7430661383724475</v>
+      </c>
+      <c r="E15" s="9">
+        <v>4.43</v>
+      </c>
+      <c r="F15" s="9">
+        <f t="shared" si="0"/>
+        <v>24.303565985979883</v>
+      </c>
+      <c r="G15" s="9">
+        <f t="shared" si="1"/>
+        <v>24.303565985979883</v>
+      </c>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="27"/>
+    </row>
+    <row r="16" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="16"/>
+      <c r="B16" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="44">
+        <v>4</v>
+      </c>
+      <c r="D16" s="9">
+        <f>5.75/3.281</f>
+        <v>1.752514477293508</v>
+      </c>
+      <c r="E16" s="9">
+        <v>4.43</v>
+      </c>
+      <c r="F16" s="9">
+        <f t="shared" si="0"/>
+        <v>31.054556537640959</v>
+      </c>
+      <c r="G16" s="9">
+        <f t="shared" si="1"/>
+        <v>31.054556537640959</v>
+      </c>
+      <c r="H16" s="42"/>
+      <c r="I16" s="42"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="27"/>
+    </row>
+    <row r="17" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="16"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="44">
+        <v>4</v>
+      </c>
+      <c r="D17" s="9">
+        <f>77/12/3.281</f>
+        <v>1.9557045616173931</v>
+      </c>
+      <c r="E17" s="9">
+        <v>4.43</v>
+      </c>
+      <c r="F17" s="9">
+        <f t="shared" si="0"/>
+        <v>34.655084831860208</v>
+      </c>
+      <c r="G17" s="9">
+        <f t="shared" si="1"/>
+        <v>34.655084831860208</v>
+      </c>
+      <c r="H17" s="42"/>
+      <c r="I17" s="42"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="27"/>
+    </row>
+    <row r="18" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="16"/>
+      <c r="B18" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="44">
+        <f>4</f>
+        <v>4</v>
+      </c>
+      <c r="D18" s="9">
+        <f>10.67/3.281</f>
+        <v>3.2520572996037793</v>
+      </c>
+      <c r="E18" s="9">
+        <v>4.43</v>
+      </c>
+      <c r="F18" s="9">
+        <f t="shared" si="0"/>
+        <v>57.626455348978965</v>
+      </c>
+      <c r="G18" s="9">
+        <f t="shared" si="1"/>
+        <v>57.626455348978965</v>
+      </c>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="27"/>
+    </row>
+    <row r="19" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="16"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="44">
+        <f>4</f>
+        <v>4</v>
+      </c>
+      <c r="D19" s="9">
+        <f>15/3.281</f>
+        <v>4.5717768972874122</v>
+      </c>
+      <c r="E19" s="9">
+        <v>4.43</v>
+      </c>
+      <c r="F19" s="9">
+        <f t="shared" si="0"/>
+        <v>81.011886619932937</v>
+      </c>
+      <c r="G19" s="9">
+        <f t="shared" si="1"/>
+        <v>81.011886619932937</v>
+      </c>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="27"/>
+    </row>
+    <row r="20" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="16"/>
+      <c r="B20" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="44">
+        <f>4*1</f>
+        <v>4</v>
+      </c>
+      <c r="D20" s="9">
+        <f>6.42/3.281</f>
+        <v>1.9567205120390123</v>
+      </c>
+      <c r="E20" s="9">
+        <v>4.43</v>
+      </c>
+      <c r="F20" s="9">
+        <f t="shared" si="0"/>
+        <v>34.673087473331293</v>
+      </c>
+      <c r="G20" s="9">
+        <f t="shared" si="1"/>
+        <v>34.673087473331293</v>
+      </c>
+      <c r="H20" s="42"/>
+      <c r="I20" s="42"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="27"/>
+    </row>
+    <row r="21" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="16"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="44">
+        <f>4*2</f>
+        <v>8</v>
+      </c>
+      <c r="D21" s="9">
+        <f>6.42/3.281</f>
+        <v>1.9567205120390123</v>
+      </c>
+      <c r="E21" s="9">
+        <v>4.43</v>
+      </c>
+      <c r="F21" s="9">
+        <f t="shared" si="0"/>
+        <v>69.346174946662586</v>
+      </c>
+      <c r="G21" s="9">
+        <f t="shared" si="1"/>
+        <v>69.346174946662586</v>
+      </c>
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="27"/>
+    </row>
+    <row r="22" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="16"/>
+      <c r="B22" s="43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="44">
+        <v>4</v>
+      </c>
+      <c r="D22" s="9">
+        <f>8/12/3.281</f>
+        <v>0.20319008432388497</v>
+      </c>
+      <c r="E22" s="9">
+        <v>4.43</v>
+      </c>
+      <c r="F22" s="9">
+        <f t="shared" si="0"/>
+        <v>3.6005282942192416</v>
+      </c>
+      <c r="G22" s="9">
+        <f t="shared" si="1"/>
+        <v>3.6005282942192416</v>
+      </c>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="27"/>
+    </row>
+    <row r="23" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="16"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="44">
+        <v>4</v>
+      </c>
+      <c r="D23" s="9">
+        <f>54/12/3.281</f>
+        <v>1.3715330691862238</v>
+      </c>
+      <c r="E23" s="9">
+        <v>4.43</v>
+      </c>
+      <c r="F23" s="9">
+        <f t="shared" si="0"/>
+        <v>24.303565985979883</v>
+      </c>
+      <c r="G23" s="9">
+        <f t="shared" si="1"/>
+        <v>24.303565985979883</v>
+      </c>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="27"/>
+    </row>
+    <row r="24" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="16"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="44">
+        <v>4</v>
+      </c>
+      <c r="D24" s="9">
+        <f>105/12/3.281</f>
+        <v>2.6668698567509903</v>
+      </c>
+      <c r="E24" s="9">
+        <v>4.43</v>
+      </c>
+      <c r="F24" s="9">
+        <f t="shared" si="0"/>
+        <v>47.256933861627545</v>
+      </c>
+      <c r="G24" s="9">
+        <f t="shared" si="1"/>
+        <v>47.256933861627545</v>
+      </c>
+      <c r="H24" s="42"/>
+      <c r="I24" s="42"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="27"/>
+    </row>
+    <row r="25" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A25" s="16"/>
+      <c r="B25" s="43" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="44">
+        <v>4</v>
+      </c>
+      <c r="D25" s="9">
+        <f>75/12/3.281</f>
+        <v>1.9049070405364217</v>
+      </c>
+      <c r="E25" s="9">
+        <v>4.43</v>
+      </c>
+      <c r="F25" s="9">
+        <f t="shared" si="0"/>
+        <v>33.754952758305393</v>
+      </c>
+      <c r="G25" s="9">
+        <f t="shared" si="1"/>
+        <v>33.754952758305393</v>
+      </c>
+      <c r="H25" s="42"/>
+      <c r="I25" s="42"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="27"/>
+    </row>
+    <row r="26" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="16"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="44">
+        <f>4*2</f>
+        <v>8</v>
+      </c>
+      <c r="D26" s="9">
+        <f>(36+37)/12/3.281</f>
+        <v>1.8541095194554504</v>
+      </c>
+      <c r="E26" s="9">
+        <v>4.43</v>
+      </c>
+      <c r="F26" s="9">
+        <f t="shared" si="0"/>
+        <v>65.709641369501156</v>
+      </c>
+      <c r="G26" s="9">
+        <f t="shared" si="1"/>
+        <v>65.709641369501156</v>
+      </c>
+      <c r="H26" s="42"/>
+      <c r="I26" s="42"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="27"/>
+    </row>
+    <row r="27" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="16"/>
+      <c r="B27" s="43" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="44">
+        <v>1</v>
+      </c>
+      <c r="D27" s="9">
+        <f>6/3.281</f>
+        <v>1.8287107589149649</v>
+      </c>
+      <c r="E27" s="9">
+        <v>3.01</v>
+      </c>
+      <c r="F27" s="9">
+        <f t="shared" si="0"/>
+        <v>5.5044193843340441</v>
+      </c>
+      <c r="G27" s="9">
+        <f t="shared" si="1"/>
+        <v>5.5044193843340441</v>
+      </c>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42"/>
+      <c r="J27" s="42"/>
+      <c r="K27" s="27"/>
+    </row>
+    <row r="28" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="16"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="44">
+        <v>4</v>
+      </c>
+      <c r="D28" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="E28" s="9">
+        <v>3.01</v>
+      </c>
+      <c r="F28" s="9">
+        <f t="shared" si="0"/>
+        <v>18.059999999999999</v>
+      </c>
+      <c r="G28" s="9">
+        <f t="shared" si="1"/>
+        <v>18.059999999999999</v>
+      </c>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="27"/>
+    </row>
+    <row r="29" spans="1:11" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="16"/>
+      <c r="B29" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" s="44">
+        <v>1</v>
+      </c>
+      <c r="D29" s="9">
+        <f>(7+65/12+76/12+74/12+6)/3.281</f>
+        <v>9.4229401605201666</v>
+      </c>
+      <c r="E29" s="9">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="F29" s="9">
+        <f t="shared" si="0"/>
+        <v>21.295844762775573</v>
+      </c>
+      <c r="G29" s="9">
+        <f t="shared" si="1"/>
+        <v>21.295844762775573</v>
+      </c>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="27"/>
+    </row>
+    <row r="30" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="16"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="44">
+        <v>2</v>
+      </c>
+      <c r="D30" s="9">
+        <f>(69+72+75+64+82)/12/3.281</f>
+        <v>9.1943513156557959</v>
+      </c>
+      <c r="E30" s="9">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="F30" s="9">
+        <f t="shared" si="0"/>
+        <v>41.558467946764196</v>
+      </c>
+      <c r="G30" s="9">
+        <f t="shared" si="1"/>
+        <v>41.558467946764196</v>
+      </c>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="27"/>
+    </row>
+    <row r="31" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="16"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="44">
+        <v>1</v>
+      </c>
+      <c r="D31" s="9">
+        <f>82/12/3.281</f>
+        <v>2.0826983643198211</v>
+      </c>
+      <c r="E31" s="9">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="F31" s="9">
+        <f t="shared" si="0"/>
+        <v>4.7068983033627951</v>
+      </c>
+      <c r="G31" s="9">
+        <f t="shared" si="1"/>
+        <v>4.7068983033627951</v>
+      </c>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="27"/>
+    </row>
+    <row r="32" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2"/>
+      <c r="B32" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="3"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="42">
+        <f>SUM(G10:G31)</f>
+        <v>880.06056639235987</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I32" s="6">
+        <v>182.51</v>
+      </c>
+      <c r="J32" s="42">
+        <f>G32*I32</f>
+        <v>160619.8539722696</v>
+      </c>
+      <c r="K32" s="5"/>
+    </row>
+    <row r="33" spans="1:18" s="36" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2"/>
+      <c r="B33" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="42">
+        <f>0.13*G32*(1871.42/18.94)</f>
+        <v>11304.391915023165</v>
+      </c>
+      <c r="K33" s="5"/>
+    </row>
+    <row r="34" spans="1:18" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2"/>
+      <c r="B34" s="43"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="42"/>
+      <c r="K34" s="5"/>
+      <c r="R34" s="96"/>
+    </row>
+    <row r="35" spans="1:18" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>2</v>
+      </c>
+      <c r="B35" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="42"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="42"/>
+      <c r="K35" s="5"/>
+      <c r="R35" s="96"/>
+    </row>
+    <row r="36" spans="1:18" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2"/>
+      <c r="B36" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="3">
+        <v>4</v>
+      </c>
+      <c r="D36" s="4">
+        <f>(15+6)/2/3.281</f>
+        <v>3.2002438281011885</v>
+      </c>
+      <c r="E36" s="5">
+        <f>5.583/3.281</f>
+        <v>1.7016153611703748</v>
+      </c>
+      <c r="F36" s="5"/>
+      <c r="G36" s="33">
+        <f t="shared" ref="G36:G37" si="2">PRODUCT(C36:F36)</f>
+        <v>21.782336229550666</v>
+      </c>
+      <c r="H36" s="7"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="42"/>
+      <c r="K36" s="5"/>
+    </row>
+    <row r="37" spans="1:18" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="3">
+        <v>4</v>
+      </c>
+      <c r="D37" s="4">
+        <f>5/3.281</f>
+        <v>1.5239256324291375</v>
+      </c>
+      <c r="E37" s="5">
+        <f>5.583/3.281</f>
+        <v>1.7016153611703748</v>
+      </c>
+      <c r="F37" s="5"/>
+      <c r="G37" s="33">
+        <f t="shared" si="2"/>
+        <v>10.372541061690795</v>
+      </c>
+      <c r="H37" s="7"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="42"/>
+      <c r="K37" s="5"/>
+    </row>
+    <row r="38" spans="1:18" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2"/>
+      <c r="B38" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="42">
+        <f>SUM(G36:G37)</f>
+        <v>32.154877291241462</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I38" s="6">
+        <v>1112.58</v>
+      </c>
+      <c r="J38" s="42">
+        <f>G38*I38</f>
+        <v>35774.873376689422</v>
+      </c>
+      <c r="K38" s="5"/>
+    </row>
+    <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="16"/>
+      <c r="B39" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="18">
+        <f>0.13*G38*7050.67/10</f>
+        <v>2947.2745727234869</v>
+      </c>
+      <c r="K39" s="17"/>
+    </row>
+    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="16"/>
+      <c r="B40" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="18">
+        <f>0.13*G38*1023.75/10</f>
+        <v>427.94122314980984</v>
+      </c>
+      <c r="K40" s="17"/>
+    </row>
+    <row r="41" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="16"/>
+      <c r="B41" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="18">
+        <f>0.13*G38*348.21/10</f>
+        <v>145.55644768058147</v>
+      </c>
+      <c r="K41" s="17"/>
+    </row>
+    <row r="42" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="16"/>
+      <c r="B42" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="18">
+        <f>0.13*G38*165/10</f>
+        <v>68.972211789712929</v>
+      </c>
+      <c r="K42" s="17"/>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A43" s="16"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="17"/>
+    </row>
+    <row r="44" spans="1:18" ht="150" x14ac:dyDescent="0.25">
+      <c r="A44" s="16">
+        <v>3</v>
+      </c>
+      <c r="B44" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="17"/>
+      <c r="D44" s="17"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="17"/>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A45" s="16"/>
+      <c r="B45" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C45" s="17">
+        <v>1</v>
+      </c>
+      <c r="D45" s="33">
+        <f>D54</f>
+        <v>9.5245352026821095</v>
+      </c>
+      <c r="E45" s="17">
+        <f>E54</f>
+        <v>1.7375</v>
+      </c>
+      <c r="F45" s="33">
+        <v>0.9</v>
+      </c>
+      <c r="G45" s="33">
+        <f t="shared" ref="G45:G49" si="3">PRODUCT(C45:F45)</f>
+        <v>14.89399192319415</v>
+      </c>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="17"/>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A46" s="16"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="17">
+        <v>1</v>
+      </c>
+      <c r="D46" s="33">
+        <f>D55</f>
+        <v>7.8229198415117347</v>
+      </c>
+      <c r="E46" s="33">
+        <f>E55</f>
+        <v>0.95</v>
+      </c>
+      <c r="F46" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="G46" s="33">
+        <f t="shared" si="3"/>
+        <v>5.5738303870771109</v>
+      </c>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="17"/>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A47" s="16"/>
+      <c r="B47" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" s="17">
+        <v>4</v>
+      </c>
+      <c r="D47" s="33">
+        <v>0.6</v>
+      </c>
+      <c r="E47" s="33">
+        <v>0.6</v>
+      </c>
+      <c r="F47" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="G47" s="33">
+        <f t="shared" si="3"/>
+        <v>0.64800000000000002</v>
+      </c>
+      <c r="H47" s="17"/>
+      <c r="I47" s="17"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="17"/>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A48" s="16"/>
+      <c r="B48" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="17">
+        <v>4</v>
+      </c>
+      <c r="D48" s="33">
+        <f>10.25/3.281</f>
+        <v>3.1240475464797317</v>
+      </c>
+      <c r="E48" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F48" s="33">
+        <v>0.3</v>
+      </c>
+      <c r="G48" s="33">
+        <f t="shared" si="3"/>
+        <v>1.6869856750990553</v>
+      </c>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="17"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="16"/>
+      <c r="B49" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C49" s="17">
+        <v>5</v>
+      </c>
+      <c r="D49" s="33">
+        <v>0.23</v>
+      </c>
+      <c r="E49" s="33">
+        <v>0.23</v>
+      </c>
+      <c r="F49" s="33">
+        <v>0.3</v>
+      </c>
+      <c r="G49" s="33">
+        <f t="shared" si="3"/>
+        <v>7.9350000000000018E-2</v>
+      </c>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="17"/>
+    </row>
+    <row r="50" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2"/>
+      <c r="B50" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="G50" s="42">
+        <f>SUM(G45:G49)</f>
+        <v>22.882157985370316</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I50" s="6">
+        <v>62.95</v>
+      </c>
+      <c r="J50" s="42">
+        <f>G50*I50</f>
+        <v>1440.4318451790614</v>
+      </c>
+      <c r="K50" s="5"/>
+    </row>
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="16"/>
+      <c r="B51" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="18">
+        <f>0.13*G50*18612/360</f>
+        <v>153.7909838196739</v>
+      </c>
+      <c r="K51" s="17"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="16"/>
+      <c r="B52" s="32"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="17"/>
+    </row>
+    <row r="53" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="A53" s="16">
+        <v>4</v>
+      </c>
+      <c r="B53" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="17"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="16"/>
+      <c r="B54" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C54" s="17">
+        <v>1</v>
+      </c>
+      <c r="D54" s="33">
+        <f>D65</f>
+        <v>9.5245352026821095</v>
+      </c>
+      <c r="E54" s="17">
+        <f>E65</f>
+        <v>1.7375</v>
+      </c>
+      <c r="F54" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="G54" s="33">
+        <f t="shared" ref="G54:G60" si="4">PRODUCT(C54:F54)</f>
+        <v>2.4823319871990246</v>
+      </c>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="17"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="16"/>
+      <c r="B55" s="32"/>
+      <c r="C55" s="17">
+        <v>1</v>
+      </c>
+      <c r="D55" s="33">
+        <f>D67</f>
+        <v>7.8229198415117347</v>
+      </c>
+      <c r="E55" s="33">
+        <f>E67</f>
+        <v>0.95</v>
+      </c>
+      <c r="F55" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="G55" s="33">
+        <f t="shared" si="4"/>
+        <v>1.1147660774154222</v>
+      </c>
+      <c r="H55" s="17"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="17"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="16"/>
+      <c r="B56" s="32" t="str">
+        <f>B47</f>
+        <v>-for footing of vertical post</v>
+      </c>
+      <c r="C56" s="17">
+        <f>C47</f>
+        <v>4</v>
+      </c>
+      <c r="D56" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="E56" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F56" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="G56" s="33">
+        <f t="shared" si="4"/>
+        <v>0.1215</v>
+      </c>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="17"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="16"/>
+      <c r="B57" s="32" t="str">
+        <f>B48</f>
+        <v>-for plinth level</v>
+      </c>
+      <c r="C57" s="17">
+        <f>C48</f>
+        <v>4</v>
+      </c>
+      <c r="D57" s="33">
+        <f>11.17/3.281</f>
+        <v>3.4044498628466928</v>
+      </c>
+      <c r="E57" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F57" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="G57" s="33">
+        <f t="shared" si="4"/>
+        <v>0.91920146296860705</v>
+      </c>
+      <c r="H57" s="17"/>
+      <c r="I57" s="17"/>
+      <c r="J57" s="18"/>
+      <c r="K57" s="17"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="16"/>
+      <c r="B58" s="32"/>
+      <c r="C58" s="17">
+        <v>1</v>
+      </c>
+      <c r="D58" s="33">
+        <f>11.17/3.281</f>
+        <v>3.4044498628466928</v>
+      </c>
+      <c r="E58" s="33">
+        <f>11.17/3.281</f>
+        <v>3.4044498628466928</v>
+      </c>
+      <c r="F58" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="G58" s="33">
+        <f t="shared" si="4"/>
+        <v>1.7385418302955298</v>
+      </c>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="18"/>
+      <c r="K58" s="17"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="16"/>
+      <c r="B59" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C59" s="17">
+        <v>-1</v>
+      </c>
+      <c r="D59" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="E59" s="33">
+        <v>1.8</v>
+      </c>
+      <c r="F59" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="G59" s="33">
+        <f t="shared" si="4"/>
+        <v>-0.40500000000000003</v>
+      </c>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="18"/>
+      <c r="K59" s="17"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="16"/>
+      <c r="B60" s="32" t="str">
+        <f>B49</f>
+        <v>-for railing</v>
+      </c>
+      <c r="C60" s="17">
+        <v>5</v>
+      </c>
+      <c r="D60" s="33">
+        <f>D49</f>
+        <v>0.23</v>
+      </c>
+      <c r="E60" s="33">
+        <f>E49</f>
+        <v>0.23</v>
+      </c>
+      <c r="F60" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="G60" s="33">
+        <f t="shared" si="4"/>
+        <v>3.9675000000000009E-2</v>
+      </c>
+      <c r="H60" s="17"/>
+      <c r="I60" s="17"/>
+      <c r="J60" s="18"/>
+      <c r="K60" s="17"/>
+    </row>
+    <row r="61" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2"/>
+      <c r="B61" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C61" s="3"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="42">
+        <f>SUM(G54:G60)</f>
+        <v>6.0110163578785833</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I61" s="6">
+        <v>4458.5200000000004</v>
+      </c>
+      <c r="J61" s="42">
+        <f>G61*I61</f>
+        <v>26800.236651928823</v>
+      </c>
+      <c r="K61" s="5"/>
+    </row>
+    <row r="62" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="16"/>
+      <c r="B62" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="18">
+        <f>0.13*G61*15452.64/5</f>
+        <v>2415.0378671226317</v>
+      </c>
+      <c r="K62" s="17"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="16"/>
+      <c r="B63" s="45"/>
+      <c r="C63" s="17"/>
+      <c r="D63" s="17"/>
+      <c r="E63" s="17"/>
+      <c r="F63" s="17"/>
+      <c r="G63" s="17"/>
+      <c r="H63" s="17"/>
+      <c r="I63" s="17"/>
+      <c r="J63" s="18"/>
+      <c r="K63" s="17"/>
+    </row>
+    <row r="64" spans="1:11" ht="94.5" x14ac:dyDescent="0.25">
+      <c r="A64" s="16">
+        <v>5</v>
+      </c>
+      <c r="B64" s="46" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" s="17"/>
+      <c r="D64" s="17"/>
+      <c r="E64" s="17"/>
+      <c r="F64" s="17"/>
+      <c r="G64" s="17"/>
+      <c r="H64" s="17"/>
+      <c r="I64" s="17"/>
+      <c r="J64" s="17"/>
+      <c r="K64" s="17"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="16"/>
+      <c r="B65" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C65" s="17">
+        <v>1</v>
+      </c>
+      <c r="D65" s="33">
+        <f>D82</f>
+        <v>9.5245352026821095</v>
+      </c>
+      <c r="E65" s="33">
+        <f>F82/2</f>
+        <v>1.7375</v>
+      </c>
+      <c r="F65" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="G65" s="33">
+        <f t="shared" ref="G65:G73" si="5">PRODUCT(C65:F65)</f>
+        <v>0.82744399573300831</v>
+      </c>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
+      <c r="J65" s="18"/>
+      <c r="K65" s="17"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="16"/>
+      <c r="B66" s="32"/>
+      <c r="C66" s="17">
+        <v>1</v>
+      </c>
+      <c r="D66" s="33">
+        <f>D65</f>
+        <v>9.5245352026821095</v>
+      </c>
+      <c r="E66" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F66" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="G66" s="33">
+        <f t="shared" si="5"/>
+        <v>0.21430204206034748</v>
+      </c>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="18"/>
+      <c r="K66" s="17"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="16"/>
+      <c r="B67" s="32"/>
+      <c r="C67" s="17">
+        <v>1</v>
+      </c>
+      <c r="D67" s="33">
+        <f>D83</f>
+        <v>7.8229198415117347</v>
+      </c>
+      <c r="E67" s="33">
+        <f>F83/2</f>
+        <v>0.95</v>
+      </c>
+      <c r="F67" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="G67" s="33">
+        <f t="shared" si="5"/>
+        <v>0.37158869247180742</v>
+      </c>
+      <c r="H67" s="17"/>
+      <c r="I67" s="17"/>
+      <c r="J67" s="18"/>
+      <c r="K67" s="17"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="16"/>
+      <c r="B68" s="32"/>
+      <c r="C68" s="17">
+        <v>1</v>
+      </c>
+      <c r="D68" s="33">
+        <f>D83</f>
+        <v>7.8229198415117347</v>
+      </c>
+      <c r="E68" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F68" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="G68" s="33">
+        <f t="shared" si="5"/>
+        <v>0.17601569643401405</v>
+      </c>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="18"/>
+      <c r="K68" s="17"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="16"/>
+      <c r="B69" s="32" t="str">
+        <f>B56</f>
+        <v>-for footing of vertical post</v>
+      </c>
+      <c r="C69" s="17">
+        <v>4</v>
+      </c>
+      <c r="D69" s="33">
+        <v>0.45</v>
+      </c>
+      <c r="E69" s="17">
+        <v>0.45</v>
+      </c>
+      <c r="F69" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="G69" s="33">
+        <f t="shared" si="5"/>
+        <v>0.24299999999999999</v>
+      </c>
+      <c r="H69" s="17"/>
+      <c r="I69" s="17"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="17"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="16"/>
+      <c r="B70" s="32" t="str">
+        <f>B57</f>
+        <v>-for plinth level</v>
+      </c>
+      <c r="C70" s="17">
+        <f>C57</f>
+        <v>4</v>
+      </c>
+      <c r="D70" s="33">
+        <f>D57</f>
+        <v>3.4044498628466928</v>
+      </c>
+      <c r="E70" s="17">
+        <f>E57</f>
+        <v>0.45</v>
+      </c>
+      <c r="F70" s="33">
+        <v>0.05</v>
+      </c>
+      <c r="G70" s="33">
+        <f t="shared" si="5"/>
+        <v>0.30640048765620237</v>
+      </c>
+      <c r="H70" s="17"/>
+      <c r="I70" s="17"/>
+      <c r="J70" s="18"/>
+      <c r="K70" s="17"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="16"/>
+      <c r="B71" s="32"/>
+      <c r="C71" s="17">
+        <v>1</v>
+      </c>
+      <c r="D71" s="33">
+        <f>14.17/3.281</f>
+        <v>4.3188052423041752</v>
+      </c>
+      <c r="E71" s="33">
+        <f>14.17/3.281</f>
+        <v>4.3188052423041752</v>
+      </c>
+      <c r="F71" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G71" s="33">
+        <f t="shared" si="5"/>
+        <v>1.3989059040715519</v>
+      </c>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="17"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="16"/>
+      <c r="B72" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C72" s="17">
+        <v>-1</v>
+      </c>
+      <c r="D72" s="33">
+        <v>1.5</v>
+      </c>
+      <c r="E72" s="33">
+        <v>1.8</v>
+      </c>
+      <c r="F72" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G72" s="33">
+        <f t="shared" si="5"/>
+        <v>-0.20250000000000001</v>
+      </c>
+      <c r="H72" s="17"/>
+      <c r="I72" s="17"/>
+      <c r="J72" s="18"/>
+      <c r="K72" s="17"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="16"/>
+      <c r="B73" s="32" t="str">
+        <f>B60</f>
+        <v>-for railing</v>
+      </c>
+      <c r="C73" s="17">
+        <v>5</v>
+      </c>
+      <c r="D73" s="33">
+        <f>D60</f>
+        <v>0.23</v>
+      </c>
+      <c r="E73" s="33">
+        <f>E60</f>
+        <v>0.23</v>
+      </c>
+      <c r="F73" s="33">
+        <v>0.23</v>
+      </c>
+      <c r="G73" s="33">
+        <f t="shared" si="5"/>
+        <v>6.0835000000000021E-2</v>
+      </c>
+      <c r="H73" s="17"/>
+      <c r="I73" s="17"/>
+      <c r="J73" s="18"/>
+      <c r="K73" s="17"/>
+    </row>
+    <row r="74" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2"/>
+      <c r="B74" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="42">
+        <f>SUM(G65:G73)</f>
+        <v>3.3959918184269315</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I74" s="6">
+        <v>10964.46</v>
+      </c>
+      <c r="J74" s="42">
+        <f>G74*I74</f>
+        <v>37235.216453469351</v>
+      </c>
+      <c r="K74" s="5"/>
+    </row>
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="16"/>
+      <c r="B75" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C75" s="17"/>
+      <c r="D75" s="17"/>
+      <c r="E75" s="17"/>
+      <c r="F75" s="17"/>
+      <c r="G75" s="17"/>
+      <c r="H75" s="17"/>
+      <c r="I75" s="17"/>
+      <c r="J75" s="18">
+        <f>0.13*G74*53818.03/15</f>
+        <v>1583.9684428867447</v>
+      </c>
+      <c r="K75" s="17"/>
+    </row>
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="16"/>
+      <c r="B76" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C76" s="17"/>
+      <c r="D76" s="17"/>
+      <c r="E76" s="17"/>
+      <c r="F76" s="17"/>
+      <c r="G76" s="17"/>
+      <c r="H76" s="17"/>
+      <c r="I76" s="17"/>
+      <c r="J76" s="18">
+        <f>0.13*G74*21432.6/15</f>
+        <v>630.80276347934773</v>
+      </c>
+      <c r="K76" s="17"/>
+    </row>
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="16"/>
+      <c r="B77" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C77" s="17"/>
+      <c r="D77" s="17"/>
+      <c r="E77" s="17"/>
+      <c r="F77" s="17"/>
+      <c r="G77" s="17"/>
+      <c r="H77" s="17"/>
+      <c r="I77" s="17"/>
+      <c r="J77" s="18">
+        <f>0.13*G74*(25719.12+13573.98+4286.52)/15</f>
+        <v>1282.6322857413404</v>
+      </c>
+      <c r="K77" s="17"/>
+    </row>
+    <row r="78" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="16"/>
+      <c r="B78" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C78" s="17"/>
+      <c r="D78" s="17"/>
+      <c r="E78" s="17"/>
+      <c r="F78" s="17"/>
+      <c r="G78" s="17"/>
+      <c r="H78" s="17"/>
+      <c r="I78" s="17"/>
+      <c r="J78" s="18">
+        <f>0.13*G74*(6325.7/15)</f>
+        <v>186.17755386380142</v>
+      </c>
+      <c r="K78" s="17"/>
+    </row>
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="16"/>
+      <c r="B79" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C79" s="17"/>
+      <c r="D79" s="17"/>
+      <c r="E79" s="17"/>
+      <c r="F79" s="17"/>
+      <c r="G79" s="17"/>
+      <c r="H79" s="17"/>
+      <c r="I79" s="17"/>
+      <c r="J79" s="18">
+        <f>0.13*G74*(310)/5</f>
+        <v>27.371694056521068</v>
+      </c>
+      <c r="K79" s="17"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" s="16"/>
+      <c r="B80" s="32"/>
+      <c r="C80" s="17"/>
+      <c r="D80" s="17"/>
+      <c r="E80" s="17"/>
+      <c r="F80" s="17"/>
+      <c r="G80" s="17"/>
+      <c r="H80" s="17"/>
+      <c r="I80" s="17"/>
+      <c r="J80" s="18"/>
+      <c r="K80" s="17"/>
+    </row>
+    <row r="81" spans="1:16" ht="110.25" x14ac:dyDescent="0.25">
+      <c r="A81" s="16">
+        <v>6</v>
+      </c>
+      <c r="B81" s="46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="17"/>
+      <c r="F81" s="17"/>
+      <c r="G81" s="17"/>
+      <c r="H81" s="17"/>
+      <c r="I81" s="17"/>
+      <c r="J81" s="17"/>
+      <c r="K81" s="17"/>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A82" s="16"/>
+      <c r="B82" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C82" s="17">
+        <v>1</v>
+      </c>
+      <c r="D82" s="33">
+        <f>31.25/3.281</f>
+        <v>9.5245352026821095</v>
+      </c>
+      <c r="E82" s="33">
+        <f>((F82/2)+0.5)/2</f>
+        <v>1.1187499999999999</v>
+      </c>
+      <c r="F82" s="33">
+        <f>6.95/2</f>
+        <v>3.4750000000000001</v>
+      </c>
+      <c r="G82" s="33">
+        <f>PRODUCT(C82:F82)</f>
+        <v>37.028118809052117</v>
+      </c>
+      <c r="H82" s="17"/>
+      <c r="I82" s="17"/>
+      <c r="J82" s="17"/>
+      <c r="K82" s="17"/>
+      <c r="M82" s="33">
+        <f>7</f>
+        <v>7</v>
+      </c>
+      <c r="N82" s="33">
+        <f>2</f>
+        <v>2</v>
+      </c>
+      <c r="O82" s="33"/>
+      <c r="P82" s="33">
+        <f>PI()*M82*SQRT(M82^2+N82^2)</f>
+        <v>160.09797821843054</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A83" s="16"/>
+      <c r="B83" s="32"/>
+      <c r="C83" s="17">
+        <v>1</v>
+      </c>
+      <c r="D83" s="33">
+        <f>(10.667+15)/3.281</f>
+        <v>7.8229198415117347</v>
+      </c>
+      <c r="E83" s="33">
+        <f>((F83/2)+0.5)/2</f>
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="F83" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="G83" s="33">
+        <f>PRODUCT(C83:F83)</f>
+        <v>10.776072081682413</v>
+      </c>
+      <c r="H83" s="17"/>
+      <c r="I83" s="17"/>
+      <c r="J83" s="17"/>
+      <c r="K83" s="17"/>
+      <c r="M83" s="35"/>
+      <c r="N83" s="35"/>
+      <c r="O83" s="35"/>
+      <c r="P83" s="35"/>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A84" s="16"/>
+      <c r="B84" s="32" t="str">
+        <f>B70</f>
+        <v>-for plinth level</v>
+      </c>
+      <c r="C84" s="17">
+        <v>2</v>
+      </c>
+      <c r="D84" s="33">
+        <f>14.17/3.281</f>
+        <v>4.3188052423041752</v>
+      </c>
+      <c r="E84" s="33">
+        <f>1.5/3.281</f>
+        <v>0.45717768972874123</v>
+      </c>
+      <c r="F84" s="33">
+        <f>1.5/3.281</f>
+        <v>0.45717768972874123</v>
+      </c>
+      <c r="G84" s="33">
+        <f>PRODUCT(C84:F84)</f>
+        <v>1.8053594054236508</v>
+      </c>
+      <c r="H84" s="17"/>
+      <c r="I84" s="17"/>
+      <c r="J84" s="17"/>
+      <c r="K84" s="17"/>
+      <c r="M84" s="35"/>
+      <c r="N84" s="35"/>
+      <c r="O84" s="35"/>
+      <c r="P84" s="35"/>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A85" s="16"/>
+      <c r="B85" s="32"/>
+      <c r="C85" s="17">
+        <v>2</v>
+      </c>
+      <c r="D85" s="33">
+        <f>(14.17-3)/3.281</f>
+        <v>3.4044498628466928</v>
+      </c>
+      <c r="E85" s="33">
+        <f>1.5/3.281</f>
+        <v>0.45717768972874123</v>
+      </c>
+      <c r="F85" s="33">
+        <f>1.5/3.281</f>
+        <v>0.45717768972874123</v>
+      </c>
+      <c r="G85" s="33">
+        <f>PRODUCT(C85:F85)</f>
+        <v>1.4231379363854748</v>
+      </c>
+      <c r="H85" s="17"/>
+      <c r="I85" s="17"/>
+      <c r="J85" s="17"/>
+      <c r="K85" s="17"/>
+      <c r="M85" s="35"/>
+      <c r="N85" s="35"/>
+      <c r="O85" s="35"/>
+      <c r="P85" s="35"/>
+    </row>
+    <row r="86" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2"/>
+      <c r="B86" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="5"/>
+      <c r="G86" s="6">
+        <f>SUM(G82:G85)</f>
+        <v>51.032688232543656</v>
+      </c>
+      <c r="H86" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I86" s="6">
+        <v>8987.83</v>
+      </c>
+      <c r="J86" s="18">
+        <f>G86*I86</f>
+        <v>458673.12627710286</v>
+      </c>
+      <c r="K86" s="5"/>
+    </row>
+    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="16"/>
+      <c r="B87" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C87" s="17"/>
+      <c r="D87" s="17"/>
+      <c r="E87" s="17"/>
+      <c r="F87" s="17"/>
+      <c r="G87" s="17"/>
+      <c r="H87" s="17"/>
+      <c r="I87" s="17"/>
+      <c r="J87" s="18">
+        <f>0.13*G86*(5863.95)/5</f>
+        <v>7780.5814361918337</v>
+      </c>
+      <c r="K87" s="17"/>
+    </row>
+    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="16"/>
+      <c r="B88" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C88" s="17"/>
+      <c r="D88" s="17"/>
+      <c r="E88" s="17"/>
+      <c r="F88" s="17"/>
+      <c r="G88" s="17"/>
+      <c r="H88" s="17"/>
+      <c r="I88" s="17"/>
+      <c r="J88" s="18">
+        <f>0.13*G86*(6604.416)/5</f>
+        <v>8763.0686698366007</v>
+      </c>
+      <c r="K88" s="17"/>
+    </row>
+    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="16"/>
+      <c r="B89" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="C89" s="17"/>
+      <c r="D89" s="17"/>
+      <c r="E89" s="17"/>
+      <c r="F89" s="17"/>
+      <c r="G89" s="17"/>
+      <c r="H89" s="17"/>
+      <c r="I89" s="17"/>
+      <c r="J89" s="18">
+        <f>0.13*G86*(14808.78)/5</f>
+        <v>19649.028173952527</v>
+      </c>
+      <c r="K89" s="17"/>
+    </row>
+    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="16"/>
+      <c r="B90" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C90" s="17"/>
+      <c r="D90" s="17"/>
+      <c r="E90" s="17"/>
+      <c r="F90" s="17"/>
+      <c r="G90" s="17"/>
+      <c r="H90" s="17"/>
+      <c r="I90" s="17"/>
+      <c r="J90" s="18">
+        <f>0.13*G86*(310)/5</f>
+        <v>411.32346715430185</v>
+      </c>
+      <c r="K90" s="17"/>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A91" s="16"/>
+      <c r="B91" s="32"/>
+      <c r="C91" s="17"/>
+      <c r="D91" s="17"/>
+      <c r="E91" s="17"/>
+      <c r="F91" s="17"/>
+      <c r="G91" s="17"/>
+      <c r="H91" s="17"/>
+      <c r="I91" s="17"/>
+      <c r="J91" s="18"/>
+      <c r="K91" s="17"/>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A92" s="16">
+        <v>7</v>
+      </c>
+      <c r="B92" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C92" s="17"/>
+      <c r="D92" s="17"/>
+      <c r="E92" s="17"/>
+      <c r="F92" s="17"/>
+      <c r="G92" s="17"/>
+      <c r="H92" s="17"/>
+      <c r="I92" s="17"/>
+      <c r="J92" s="18"/>
+      <c r="K92" s="17"/>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A93" s="16"/>
+      <c r="B93" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="C93" s="17">
+        <v>1</v>
+      </c>
+      <c r="D93" s="33">
+        <f>1.5</f>
+        <v>1.5</v>
+      </c>
+      <c r="E93" s="33">
+        <v>1.6</v>
+      </c>
+      <c r="F93" s="17"/>
+      <c r="G93" s="33">
+        <f>PRODUCT(C93:F93)</f>
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="H93" s="17"/>
+      <c r="I93" s="17"/>
+      <c r="J93" s="18"/>
+      <c r="K93" s="17"/>
+    </row>
+    <row r="94" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2"/>
+      <c r="B94" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" s="3"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5"/>
+      <c r="G94" s="6">
+        <f>SUM(G93)</f>
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="H94" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="I94" s="6">
+        <v>1017.47</v>
+      </c>
+      <c r="J94" s="18">
+        <f>G94*I94</f>
+        <v>2441.9280000000003</v>
+      </c>
+      <c r="K94" s="5"/>
+    </row>
+    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="16"/>
+      <c r="B95" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C95" s="17"/>
+      <c r="D95" s="17"/>
+      <c r="E95" s="17"/>
+      <c r="F95" s="17"/>
+      <c r="G95" s="17"/>
+      <c r="H95" s="17"/>
+      <c r="I95" s="17"/>
+      <c r="J95" s="18">
+        <f>0.13*G94*(8617.2)/10</f>
+        <v>268.85664000000008</v>
+      </c>
+      <c r="K95" s="17"/>
+    </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A96" s="16"/>
+      <c r="B96" s="17"/>
+      <c r="C96" s="17"/>
+      <c r="D96" s="17"/>
+      <c r="E96" s="17"/>
+      <c r="F96" s="17"/>
+      <c r="G96" s="17"/>
+      <c r="H96" s="17"/>
+      <c r="I96" s="17"/>
+      <c r="J96" s="17"/>
+      <c r="K96" s="17"/>
+    </row>
+    <row r="97" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="A97" s="16">
+        <v>8</v>
+      </c>
+      <c r="B97" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C97" s="17"/>
+      <c r="D97" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="E97" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="F97" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="G97" s="17"/>
+      <c r="H97" s="17"/>
+      <c r="I97" s="17"/>
+      <c r="J97" s="18"/>
+      <c r="K97" s="17"/>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A98" s="16"/>
+      <c r="B98" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C98" s="17">
+        <v>1</v>
+      </c>
+      <c r="D98" s="17">
+        <v>185</v>
+      </c>
+      <c r="E98" s="17">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="F98" s="17">
+        <f>C98*D98*E98</f>
+        <v>24.975000000000001</v>
+      </c>
+      <c r="G98" s="33">
+        <f>F98</f>
+        <v>24.975000000000001</v>
+      </c>
+      <c r="H98" s="17"/>
+      <c r="I98" s="17"/>
+      <c r="J98" s="18"/>
+      <c r="K98" s="17"/>
+    </row>
+    <row r="99" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2"/>
+      <c r="B99" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" s="3"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="5"/>
+      <c r="G99" s="6">
+        <f>SUM(G98)</f>
+        <v>24.975000000000001</v>
+      </c>
+      <c r="H99" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="I99" s="6">
+        <v>287</v>
+      </c>
+      <c r="J99" s="18">
+        <f>G99*I99</f>
+        <v>7167.8250000000007</v>
+      </c>
+      <c r="K99" s="5"/>
+    </row>
+    <row r="100" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="16"/>
+      <c r="B100" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C100" s="17"/>
+      <c r="D100" s="17"/>
+      <c r="E100" s="17"/>
+      <c r="F100" s="17"/>
+      <c r="G100" s="17"/>
+      <c r="H100" s="17"/>
+      <c r="I100" s="17"/>
+      <c r="J100" s="18">
+        <f>0.13*J99</f>
+        <v>931.81725000000017</v>
+      </c>
+      <c r="K100" s="17"/>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A101" s="16"/>
+      <c r="B101" s="17"/>
+      <c r="C101" s="17"/>
+      <c r="D101" s="17"/>
+      <c r="E101" s="17"/>
+      <c r="F101" s="17"/>
+      <c r="G101" s="17"/>
+      <c r="H101" s="17"/>
+      <c r="I101" s="17"/>
+      <c r="J101" s="17"/>
+      <c r="K101" s="17"/>
+    </row>
+    <row r="102" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>9</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102" s="3">
+        <v>1</v>
+      </c>
+      <c r="D102" s="4"/>
+      <c r="E102" s="5"/>
+      <c r="F102" s="5"/>
+      <c r="G102" s="7">
+        <f t="shared" ref="G102" si="6">PRODUCT(C102:F102)</f>
+        <v>1</v>
+      </c>
+      <c r="H102" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I102" s="6">
+        <v>500</v>
+      </c>
+      <c r="J102" s="7">
+        <f>G102*I102</f>
+        <v>500</v>
+      </c>
+      <c r="K102" s="5"/>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A103" s="2"/>
+      <c r="B103" s="8"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="4"/>
+      <c r="E103" s="5"/>
+      <c r="F103" s="5"/>
+      <c r="G103" s="6"/>
+      <c r="H103" s="7"/>
+      <c r="I103" s="6"/>
+      <c r="J103" s="18"/>
+      <c r="K103" s="5"/>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A104" s="21"/>
+      <c r="B104" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C104" s="23"/>
+      <c r="D104" s="24"/>
+      <c r="E104" s="24"/>
+      <c r="F104" s="24"/>
+      <c r="G104" s="18"/>
+      <c r="H104" s="18"/>
+      <c r="I104" s="18"/>
+      <c r="J104" s="18">
+        <f>SUM(J9:J102)</f>
+        <v>789632.08517511096</v>
+      </c>
+      <c r="K104" s="25"/>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M105" s="20"/>
+      <c r="N105" s="20"/>
+      <c r="O105" s="20"/>
+      <c r="P105" s="20"/>
+      <c r="Q105" s="20"/>
+      <c r="R105" s="20"/>
+      <c r="S105" s="20"/>
+    </row>
+    <row r="106" spans="1:19" s="20" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="26"/>
+      <c r="B106" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C106" s="70">
+        <f>J104</f>
+        <v>789632.08517511096</v>
+      </c>
+      <c r="D106" s="71"/>
+      <c r="E106" s="9">
+        <v>100</v>
+      </c>
+      <c r="F106" s="26"/>
+      <c r="G106" s="28"/>
+      <c r="H106" s="26"/>
+      <c r="I106" s="29"/>
+      <c r="J106" s="30"/>
+      <c r="K106" s="31"/>
+      <c r="M106" s="19"/>
+      <c r="N106" s="19"/>
+      <c r="O106" s="19"/>
+      <c r="P106" s="19"/>
+      <c r="Q106" s="19"/>
+      <c r="R106" s="19"/>
+      <c r="S106" s="19"/>
+    </row>
+    <row r="107" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B107" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="C107" s="74">
+        <v>700000</v>
+      </c>
+      <c r="D107" s="75"/>
+      <c r="E107" s="9"/>
+    </row>
+    <row r="108" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B108" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C108" s="74">
+        <f>C107-C110-C111</f>
+        <v>665000</v>
+      </c>
+      <c r="D108" s="75"/>
+      <c r="E108" s="9">
+        <f>C108/C106*100</f>
+        <v>84.21643604470907</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B109" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C109" s="76">
+        <f>C106-C108</f>
+        <v>124632.08517511096</v>
+      </c>
+      <c r="D109" s="76"/>
+      <c r="E109" s="9">
+        <f>100-E108</f>
+        <v>15.78356395529093</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B110" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="C110" s="70">
+        <f>C107*0.03</f>
+        <v>21000</v>
+      </c>
+      <c r="D110" s="71"/>
+      <c r="E110" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B111" s="27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C111" s="70">
+        <f>C107*0.02</f>
+        <v>14000</v>
+      </c>
+      <c r="D111" s="71"/>
+      <c r="E111" s="9">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="C110:D110"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="C106:D106"/>
+    <mergeCell ref="C107:D107"/>
+    <mergeCell ref="C108:D108"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" scale="90" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{599ED376-89D8-4E35-8A2B-E6A997628D72}">
   <dimension ref="A1:S111"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7695,235 +10203,235 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="91" t="s">
+      <c r="A1" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
     </row>
     <row r="2" spans="1:18" ht="22.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="92"/>
-      <c r="C2" s="92"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="92"/>
-      <c r="F2" s="92"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="92"/>
-      <c r="I2" s="92"/>
-      <c r="J2" s="92"/>
-      <c r="K2" s="92"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="80"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="93" t="s">
+      <c r="A3" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="93"/>
-      <c r="C3" s="93"/>
-      <c r="D3" s="93"/>
-      <c r="E3" s="93"/>
-      <c r="F3" s="93"/>
-      <c r="G3" s="93"/>
-      <c r="H3" s="93"/>
-      <c r="I3" s="93"/>
-      <c r="J3" s="93"/>
-      <c r="K3" s="93"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="93" t="s">
+      <c r="A4" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="93"/>
-      <c r="C4" s="93"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="93"/>
-      <c r="I4" s="93"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="93"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
     </row>
     <row r="5" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="94"/>
-      <c r="C5" s="94"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="94"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="94"/>
-      <c r="K5" s="94"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="82"/>
+      <c r="J5" s="82"/>
+      <c r="K5" s="82"/>
     </row>
     <row r="6" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="95" t="s">
+      <c r="A6" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="95"/>
-      <c r="C6" s="95"/>
-      <c r="D6" s="95"/>
-      <c r="E6" s="95"/>
-      <c r="F6" s="95"/>
-      <c r="G6" s="96"/>
-      <c r="H6" s="97" t="s">
+      <c r="B6" s="77"/>
+      <c r="C6" s="77"/>
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="78" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="97"/>
-      <c r="J6" s="97"/>
-      <c r="K6" s="97"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="78"/>
+      <c r="K6" s="78"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="98" t="s">
+      <c r="A7" s="72" t="s">
         <v>80</v>
       </c>
-      <c r="B7" s="98"/>
-      <c r="C7" s="98"/>
-      <c r="D7" s="98"/>
-      <c r="E7" s="98"/>
-      <c r="F7" s="98"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="100" t="s">
+      <c r="B7" s="72"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="73" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="100"/>
-      <c r="J7" s="100"/>
-      <c r="K7" s="100"/>
+      <c r="I7" s="73"/>
+      <c r="J7" s="73"/>
+      <c r="K7" s="73"/>
     </row>
     <row r="8" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="101" t="s">
+      <c r="A8" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="102" t="s">
+      <c r="B8" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="101" t="s">
+      <c r="C8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="103" t="s">
+      <c r="D8" s="68" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="103" t="s">
+      <c r="E8" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="103" t="s">
+      <c r="F8" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="103" t="s">
+      <c r="G8" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="H8" s="101" t="s">
+      <c r="H8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="103" t="s">
+      <c r="I8" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="103" t="s">
+      <c r="J8" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="K8" s="104" t="s">
+      <c r="K8" s="15" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="105">
+      <c r="A9" s="2">
         <v>1</v>
       </c>
-      <c r="B9" s="106" t="s">
+      <c r="B9" s="69" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="107" t="s">
+      <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D9" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="108" t="s">
+      <c r="E9" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="108" t="s">
+      <c r="F9" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="108"/>
-      <c r="H9" s="109"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="7"/>
       <c r="I9" s="6"/>
-      <c r="J9" s="110"/>
-      <c r="K9" s="111"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="5"/>
     </row>
     <row r="10" spans="1:18" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="112"/>
-      <c r="B10" s="113" t="s">
+      <c r="A10" s="16"/>
+      <c r="B10" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="114">
+      <c r="C10" s="44">
         <f>4</f>
         <v>4</v>
       </c>
-      <c r="D10" s="115">
+      <c r="D10" s="9">
         <f>(12+1)/3.281</f>
         <v>3.9622066443157573</v>
       </c>
-      <c r="E10" s="115">
+      <c r="E10" s="9">
         <v>6.5</v>
       </c>
-      <c r="F10" s="115">
+      <c r="F10" s="9">
         <f t="shared" ref="F10:F31" si="0">PRODUCT(C10:E10)</f>
         <v>103.0173727522097</v>
       </c>
-      <c r="G10" s="115">
+      <c r="G10" s="9">
         <f t="shared" ref="G10:G31" si="1">F10</f>
         <v>103.0173727522097</v>
       </c>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="110" t="s">
-        <v>97</v>
-      </c>
-      <c r="K10" s="116"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="K10" s="27"/>
     </row>
     <row r="11" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="112"/>
-      <c r="B11" s="113" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="114">
+      <c r="C11" s="44">
         <v>4</v>
       </c>
-      <c r="D11" s="115">
+      <c r="D11" s="9">
         <f>11.5/3.281</f>
         <v>3.5050289545870159</v>
       </c>
-      <c r="E11" s="115">
+      <c r="E11" s="9">
         <v>6.5</v>
       </c>
-      <c r="F11" s="115">
+      <c r="F11" s="9">
         <f t="shared" si="0"/>
         <v>91.130752819262412</v>
       </c>
-      <c r="G11" s="115">
+      <c r="G11" s="9">
         <f t="shared" si="1"/>
         <v>91.130752819262412</v>
       </c>
-      <c r="H11" s="110"/>
-      <c r="I11" s="110"/>
-      <c r="J11" s="110">
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42">
         <f>20/3.281</f>
         <v>6.0957025297165499</v>
       </c>
-      <c r="K11" s="116"/>
+      <c r="K11" s="27"/>
       <c r="Q11" s="36">
         <f>PRODUCT(C11:D11)</f>
         <v>14.020115818348064</v>
@@ -7934,631 +10442,631 @@
       </c>
     </row>
     <row r="12" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="112"/>
-      <c r="B12" s="113" t="s">
+      <c r="A12" s="16"/>
+      <c r="B12" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="114">
+      <c r="C12" s="44">
         <v>2</v>
       </c>
-      <c r="D12" s="115">
+      <c r="D12" s="9">
         <f>11.5/3.281</f>
         <v>3.5050289545870159</v>
       </c>
-      <c r="E12" s="115">
+      <c r="E12" s="9">
         <v>6.5</v>
       </c>
-      <c r="F12" s="115">
+      <c r="F12" s="9">
         <f t="shared" si="0"/>
         <v>45.565376409631206</v>
       </c>
-      <c r="G12" s="115">
+      <c r="G12" s="9">
         <f t="shared" si="1"/>
         <v>45.565376409631206</v>
       </c>
-      <c r="H12" s="110"/>
-      <c r="I12" s="110"/>
-      <c r="J12" s="110"/>
-      <c r="K12" s="116"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="27"/>
     </row>
     <row r="13" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="112"/>
-      <c r="B13" s="113" t="s">
+      <c r="A13" s="16"/>
+      <c r="B13" s="43" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="114">
+      <c r="C13" s="44">
         <v>4</v>
       </c>
-      <c r="D13" s="115">
+      <c r="D13" s="9">
         <v>1.5</v>
       </c>
-      <c r="E13" s="115">
+      <c r="E13" s="9">
         <v>6.5</v>
       </c>
-      <c r="F13" s="115">
+      <c r="F13" s="9">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="G13" s="115">
+      <c r="G13" s="9">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
-      <c r="H13" s="110"/>
-      <c r="I13" s="110"/>
-      <c r="J13" s="110"/>
-      <c r="K13" s="116"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="42"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="27"/>
     </row>
     <row r="14" spans="1:18" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="112"/>
-      <c r="B14" s="113"/>
-      <c r="C14" s="114">
+      <c r="A14" s="16"/>
+      <c r="B14" s="43"/>
+      <c r="C14" s="44">
         <v>1</v>
       </c>
-      <c r="D14" s="115">
+      <c r="D14" s="9">
         <f>0.45</f>
         <v>0.45</v>
       </c>
-      <c r="E14" s="115">
+      <c r="E14" s="9">
         <v>6.5</v>
       </c>
-      <c r="F14" s="115">
+      <c r="F14" s="9">
         <f t="shared" si="0"/>
         <v>2.9250000000000003</v>
       </c>
-      <c r="G14" s="115">
+      <c r="G14" s="9">
         <f t="shared" si="1"/>
         <v>2.9250000000000003</v>
       </c>
-      <c r="H14" s="110"/>
-      <c r="I14" s="110">
+      <c r="H14" s="42"/>
+      <c r="I14" s="42">
         <f>22/12</f>
         <v>1.8333333333333333</v>
       </c>
-      <c r="J14" s="110"/>
-      <c r="K14" s="116"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="27"/>
     </row>
     <row r="15" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="112"/>
-      <c r="B15" s="113" t="s">
+      <c r="A15" s="16"/>
+      <c r="B15" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="114">
+      <c r="C15" s="44">
         <v>2</v>
       </c>
-      <c r="D15" s="115">
+      <c r="D15" s="9">
         <f>9/3.281</f>
         <v>2.7430661383724475</v>
       </c>
-      <c r="E15" s="115">
+      <c r="E15" s="9">
         <v>4.43</v>
       </c>
-      <c r="F15" s="115">
+      <c r="F15" s="9">
         <f t="shared" si="0"/>
         <v>24.303565985979883</v>
       </c>
-      <c r="G15" s="115">
+      <c r="G15" s="9">
         <f t="shared" si="1"/>
         <v>24.303565985979883</v>
       </c>
-      <c r="H15" s="110"/>
-      <c r="I15" s="110">
+      <c r="H15" s="42"/>
+      <c r="I15" s="42">
         <f>110/12</f>
         <v>9.1666666666666661</v>
       </c>
-      <c r="J15" s="110"/>
-      <c r="K15" s="116"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="27"/>
     </row>
     <row r="16" spans="1:18" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="112"/>
-      <c r="B16" s="113" t="s">
+      <c r="A16" s="16"/>
+      <c r="B16" s="43" t="s">
         <v>47</v>
       </c>
-      <c r="C16" s="114">
+      <c r="C16" s="44">
         <v>4</v>
       </c>
-      <c r="D16" s="115">
+      <c r="D16" s="9">
         <f>5.75/3.281</f>
         <v>1.752514477293508</v>
       </c>
-      <c r="E16" s="115">
+      <c r="E16" s="9">
         <v>4.43</v>
       </c>
-      <c r="F16" s="115">
+      <c r="F16" s="9">
         <f t="shared" si="0"/>
         <v>31.054556537640959</v>
       </c>
-      <c r="G16" s="115">
+      <c r="G16" s="9">
         <f t="shared" si="1"/>
         <v>31.054556537640959</v>
       </c>
-      <c r="H16" s="110"/>
-      <c r="I16" s="110">
+      <c r="H16" s="42"/>
+      <c r="I16" s="42">
         <f>71/12</f>
         <v>5.916666666666667</v>
       </c>
-      <c r="J16" s="110"/>
-      <c r="K16" s="116"/>
+      <c r="J16" s="42"/>
+      <c r="K16" s="27"/>
     </row>
     <row r="17" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="112"/>
-      <c r="B17" s="113"/>
-      <c r="C17" s="114">
+      <c r="A17" s="16"/>
+      <c r="B17" s="43"/>
+      <c r="C17" s="44">
         <v>4</v>
       </c>
-      <c r="D17" s="115">
+      <c r="D17" s="9">
         <f>77/12/3.281</f>
         <v>1.9557045616173931</v>
       </c>
-      <c r="E17" s="115">
+      <c r="E17" s="9">
         <v>4.43</v>
       </c>
-      <c r="F17" s="115">
+      <c r="F17" s="9">
         <f t="shared" si="0"/>
         <v>34.655084831860208</v>
       </c>
-      <c r="G17" s="115">
+      <c r="G17" s="9">
         <f t="shared" si="1"/>
         <v>34.655084831860208</v>
       </c>
-      <c r="H17" s="110"/>
-      <c r="I17" s="110">
+      <c r="H17" s="42"/>
+      <c r="I17" s="42">
         <f>77/12</f>
         <v>6.416666666666667</v>
       </c>
-      <c r="J17" s="110"/>
-      <c r="K17" s="116"/>
+      <c r="J17" s="42"/>
+      <c r="K17" s="27"/>
     </row>
     <row r="18" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="112"/>
-      <c r="B18" s="113" t="s">
+      <c r="A18" s="16"/>
+      <c r="B18" s="43" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="114">
+      <c r="C18" s="44">
         <f>4</f>
         <v>4</v>
       </c>
-      <c r="D18" s="115">
+      <c r="D18" s="9">
         <f>10.67/3.281</f>
         <v>3.2520572996037793</v>
       </c>
-      <c r="E18" s="115">
+      <c r="E18" s="9">
         <v>4.43</v>
       </c>
-      <c r="F18" s="115">
+      <c r="F18" s="9">
         <f t="shared" si="0"/>
         <v>57.626455348978965</v>
       </c>
-      <c r="G18" s="115">
+      <c r="G18" s="9">
         <f t="shared" si="1"/>
         <v>57.626455348978965</v>
       </c>
-      <c r="H18" s="110"/>
-      <c r="I18" s="110">
+      <c r="H18" s="42"/>
+      <c r="I18" s="42">
         <f>128/12</f>
         <v>10.666666666666666</v>
       </c>
-      <c r="J18" s="110"/>
-      <c r="K18" s="116"/>
+      <c r="J18" s="42"/>
+      <c r="K18" s="27"/>
     </row>
     <row r="19" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="112"/>
-      <c r="B19" s="113"/>
-      <c r="C19" s="114">
+      <c r="A19" s="16"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="44">
         <f>4</f>
         <v>4</v>
       </c>
-      <c r="D19" s="115">
+      <c r="D19" s="9">
         <f>15/3.281</f>
         <v>4.5717768972874122</v>
       </c>
-      <c r="E19" s="115">
+      <c r="E19" s="9">
         <v>4.43</v>
       </c>
-      <c r="F19" s="115">
+      <c r="F19" s="9">
         <f t="shared" si="0"/>
         <v>81.011886619932937</v>
       </c>
-      <c r="G19" s="115">
+      <c r="G19" s="9">
         <f t="shared" si="1"/>
         <v>81.011886619932937</v>
       </c>
-      <c r="H19" s="110"/>
-      <c r="I19" s="110">
+      <c r="H19" s="42"/>
+      <c r="I19" s="42">
         <f>183/12</f>
         <v>15.25</v>
       </c>
-      <c r="J19" s="110"/>
-      <c r="K19" s="116"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="27"/>
     </row>
     <row r="20" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A20" s="112"/>
-      <c r="B20" s="113" t="s">
+      <c r="A20" s="16"/>
+      <c r="B20" s="43" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="114">
+      <c r="C20" s="44">
         <f>4*1</f>
         <v>4</v>
       </c>
-      <c r="D20" s="115">
+      <c r="D20" s="9">
         <f>6.42/3.281</f>
         <v>1.9567205120390123</v>
       </c>
-      <c r="E20" s="115">
+      <c r="E20" s="9">
         <v>4.43</v>
       </c>
-      <c r="F20" s="115">
+      <c r="F20" s="9">
         <f t="shared" si="0"/>
         <v>34.673087473331293</v>
       </c>
-      <c r="G20" s="115">
+      <c r="G20" s="9">
         <f t="shared" si="1"/>
         <v>34.673087473331293</v>
       </c>
-      <c r="H20" s="110"/>
-      <c r="I20" s="110">
+      <c r="H20" s="42"/>
+      <c r="I20" s="42">
         <f>82/12</f>
         <v>6.833333333333333</v>
       </c>
-      <c r="J20" s="110"/>
-      <c r="K20" s="116"/>
+      <c r="J20" s="42"/>
+      <c r="K20" s="27"/>
     </row>
     <row r="21" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="112"/>
-      <c r="B21" s="113"/>
-      <c r="C21" s="114">
+      <c r="A21" s="16"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="44">
         <f>4*2</f>
         <v>8</v>
       </c>
-      <c r="D21" s="115">
+      <c r="D21" s="9">
         <f>6.42/3.281</f>
         <v>1.9567205120390123</v>
       </c>
-      <c r="E21" s="115">
+      <c r="E21" s="9">
         <v>4.43</v>
       </c>
-      <c r="F21" s="115">
+      <c r="F21" s="9">
         <f t="shared" si="0"/>
         <v>69.346174946662586</v>
       </c>
-      <c r="G21" s="115">
+      <c r="G21" s="9">
         <f t="shared" si="1"/>
         <v>69.346174946662586</v>
       </c>
-      <c r="H21" s="110"/>
-      <c r="I21" s="110">
+      <c r="H21" s="42"/>
+      <c r="I21" s="42">
         <f>(38+41)/12</f>
         <v>6.583333333333333</v>
       </c>
-      <c r="J21" s="110"/>
-      <c r="K21" s="116"/>
+      <c r="J21" s="42"/>
+      <c r="K21" s="27"/>
     </row>
     <row r="22" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="112"/>
-      <c r="B22" s="113" t="s">
+      <c r="A22" s="16"/>
+      <c r="B22" s="43" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="114">
+      <c r="C22" s="44">
         <v>4</v>
       </c>
-      <c r="D22" s="115">
+      <c r="D22" s="9">
         <f>8/12/3.281</f>
         <v>0.20319008432388497</v>
       </c>
-      <c r="E22" s="115">
+      <c r="E22" s="9">
         <v>4.43</v>
       </c>
-      <c r="F22" s="115">
+      <c r="F22" s="9">
         <f t="shared" si="0"/>
         <v>3.6005282942192416</v>
       </c>
-      <c r="G22" s="115">
+      <c r="G22" s="9">
         <f t="shared" si="1"/>
         <v>3.6005282942192416</v>
       </c>
-      <c r="H22" s="110"/>
-      <c r="I22" s="110">
+      <c r="H22" s="42"/>
+      <c r="I22" s="42">
         <f>8/12</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="J22" s="110"/>
-      <c r="K22" s="116"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="27"/>
     </row>
     <row r="23" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="112"/>
-      <c r="B23" s="113"/>
-      <c r="C23" s="114">
+      <c r="A23" s="16"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="44">
         <v>4</v>
       </c>
-      <c r="D23" s="115">
+      <c r="D23" s="9">
         <f>54/12/3.281</f>
         <v>1.3715330691862238</v>
       </c>
-      <c r="E23" s="115">
+      <c r="E23" s="9">
         <v>4.43</v>
       </c>
-      <c r="F23" s="115">
+      <c r="F23" s="9">
         <f t="shared" si="0"/>
         <v>24.303565985979883</v>
       </c>
-      <c r="G23" s="115">
+      <c r="G23" s="9">
         <f t="shared" si="1"/>
         <v>24.303565985979883</v>
       </c>
-      <c r="H23" s="110"/>
-      <c r="I23" s="110">
+      <c r="H23" s="42"/>
+      <c r="I23" s="42">
         <f>54/12</f>
         <v>4.5</v>
       </c>
-      <c r="J23" s="110"/>
-      <c r="K23" s="116"/>
+      <c r="J23" s="42"/>
+      <c r="K23" s="27"/>
     </row>
     <row r="24" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="112"/>
-      <c r="B24" s="113"/>
-      <c r="C24" s="114">
+      <c r="A24" s="16"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="44">
         <v>4</v>
       </c>
-      <c r="D24" s="115">
+      <c r="D24" s="9">
         <f>105/12/3.281</f>
         <v>2.6668698567509903</v>
       </c>
-      <c r="E24" s="115">
+      <c r="E24" s="9">
         <v>4.43</v>
       </c>
-      <c r="F24" s="115">
+      <c r="F24" s="9">
         <f t="shared" si="0"/>
         <v>47.256933861627545</v>
       </c>
-      <c r="G24" s="115">
+      <c r="G24" s="9">
         <f t="shared" si="1"/>
         <v>47.256933861627545</v>
       </c>
-      <c r="H24" s="110"/>
-      <c r="I24" s="110">
+      <c r="H24" s="42"/>
+      <c r="I24" s="42">
         <f>105/12</f>
         <v>8.75</v>
       </c>
-      <c r="J24" s="110"/>
-      <c r="K24" s="116"/>
+      <c r="J24" s="42"/>
+      <c r="K24" s="27"/>
     </row>
     <row r="25" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A25" s="112"/>
-      <c r="B25" s="113" t="s">
+      <c r="A25" s="16"/>
+      <c r="B25" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="114">
+      <c r="C25" s="44">
         <v>4</v>
       </c>
-      <c r="D25" s="115">
+      <c r="D25" s="9">
         <f>75/12/3.281</f>
         <v>1.9049070405364217</v>
       </c>
-      <c r="E25" s="115">
+      <c r="E25" s="9">
         <v>4.43</v>
       </c>
-      <c r="F25" s="115">
+      <c r="F25" s="9">
         <f t="shared" si="0"/>
         <v>33.754952758305393</v>
       </c>
-      <c r="G25" s="115">
+      <c r="G25" s="9">
         <f t="shared" si="1"/>
         <v>33.754952758305393</v>
       </c>
-      <c r="H25" s="110"/>
-      <c r="I25" s="110">
+      <c r="H25" s="42"/>
+      <c r="I25" s="42">
         <f>75/12</f>
         <v>6.25</v>
       </c>
-      <c r="J25" s="110"/>
-      <c r="K25" s="116"/>
+      <c r="J25" s="42"/>
+      <c r="K25" s="27"/>
     </row>
     <row r="26" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="112"/>
-      <c r="B26" s="113"/>
-      <c r="C26" s="114">
+      <c r="A26" s="16"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="44">
         <f>4*2</f>
         <v>8</v>
       </c>
-      <c r="D26" s="115">
+      <c r="D26" s="9">
         <f>(36+37)/12/3.281</f>
         <v>1.8541095194554504</v>
       </c>
-      <c r="E26" s="115">
+      <c r="E26" s="9">
         <v>4.43</v>
       </c>
-      <c r="F26" s="115">
+      <c r="F26" s="9">
         <f t="shared" si="0"/>
         <v>65.709641369501156</v>
       </c>
-      <c r="G26" s="115">
+      <c r="G26" s="9">
         <f t="shared" si="1"/>
         <v>65.709641369501156</v>
       </c>
-      <c r="H26" s="110"/>
-      <c r="I26" s="110">
+      <c r="H26" s="42"/>
+      <c r="I26" s="42">
         <f>(36+37)/12</f>
         <v>6.083333333333333</v>
       </c>
-      <c r="J26" s="110"/>
-      <c r="K26" s="116"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="27"/>
     </row>
     <row r="27" spans="1:11" s="36" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="112"/>
-      <c r="B27" s="113" t="s">
+      <c r="A27" s="16"/>
+      <c r="B27" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="114">
+      <c r="C27" s="44">
         <v>1</v>
       </c>
-      <c r="D27" s="115">
+      <c r="D27" s="9">
         <f>6/3.281</f>
         <v>1.8287107589149649</v>
       </c>
-      <c r="E27" s="115">
+      <c r="E27" s="9">
         <v>3.01</v>
       </c>
-      <c r="F27" s="115">
+      <c r="F27" s="9">
         <f t="shared" si="0"/>
         <v>5.5044193843340441</v>
       </c>
-      <c r="G27" s="115">
+      <c r="G27" s="9">
         <f t="shared" si="1"/>
         <v>5.5044193843340441</v>
       </c>
-      <c r="H27" s="110"/>
-      <c r="I27" s="110" t="s">
-        <v>98</v>
-      </c>
-      <c r="J27" s="110"/>
-      <c r="K27" s="116"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="J27" s="42"/>
+      <c r="K27" s="27"/>
     </row>
     <row r="28" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="112"/>
-      <c r="B28" s="113"/>
-      <c r="C28" s="114">
+      <c r="A28" s="16"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="44">
         <v>4</v>
       </c>
-      <c r="D28" s="115">
+      <c r="D28" s="9">
         <v>1.5</v>
       </c>
-      <c r="E28" s="115">
+      <c r="E28" s="9">
         <v>3.01</v>
       </c>
-      <c r="F28" s="115">
+      <c r="F28" s="9">
         <f t="shared" si="0"/>
         <v>18.059999999999999</v>
       </c>
-      <c r="G28" s="115">
+      <c r="G28" s="9">
         <f t="shared" si="1"/>
         <v>18.059999999999999</v>
       </c>
-      <c r="H28" s="110"/>
-      <c r="I28" s="110"/>
-      <c r="J28" s="110"/>
-      <c r="K28" s="116"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
+      <c r="J28" s="42"/>
+      <c r="K28" s="27"/>
     </row>
     <row r="29" spans="1:11" s="36" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="112"/>
-      <c r="B29" s="113" t="s">
-        <v>99</v>
-      </c>
-      <c r="C29" s="114">
+      <c r="A29" s="16"/>
+      <c r="B29" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" s="44">
         <v>1</v>
       </c>
-      <c r="D29" s="115">
+      <c r="D29" s="9">
         <f>(7+65/12+76/12+74/12+6)/3.281</f>
         <v>9.4229401605201666</v>
       </c>
-      <c r="E29" s="115">
+      <c r="E29" s="9">
         <v>2.2599999999999998</v>
       </c>
-      <c r="F29" s="115">
+      <c r="F29" s="9">
         <f t="shared" si="0"/>
         <v>21.295844762775573</v>
       </c>
-      <c r="G29" s="115">
+      <c r="G29" s="9">
         <f t="shared" si="1"/>
         <v>21.295844762775573</v>
       </c>
-      <c r="H29" s="110"/>
-      <c r="I29" s="110"/>
-      <c r="J29" s="110"/>
-      <c r="K29" s="116"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
+      <c r="J29" s="42"/>
+      <c r="K29" s="27"/>
     </row>
     <row r="30" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="112"/>
-      <c r="B30" s="113"/>
-      <c r="C30" s="114">
+      <c r="A30" s="16"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="44">
         <v>2</v>
       </c>
-      <c r="D30" s="115">
+      <c r="D30" s="9">
         <f>(69+72+75+64+82)/12/3.281</f>
         <v>9.1943513156557959</v>
       </c>
-      <c r="E30" s="115">
+      <c r="E30" s="9">
         <v>2.2599999999999998</v>
       </c>
-      <c r="F30" s="115">
+      <c r="F30" s="9">
         <f t="shared" si="0"/>
         <v>41.558467946764196</v>
       </c>
-      <c r="G30" s="115">
+      <c r="G30" s="9">
         <f t="shared" si="1"/>
         <v>41.558467946764196</v>
       </c>
-      <c r="H30" s="110"/>
-      <c r="I30" s="110"/>
-      <c r="J30" s="110"/>
-      <c r="K30" s="116"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="42"/>
+      <c r="K30" s="27"/>
     </row>
     <row r="31" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="112"/>
-      <c r="B31" s="113"/>
-      <c r="C31" s="114">
+      <c r="A31" s="16"/>
+      <c r="B31" s="43"/>
+      <c r="C31" s="44">
         <v>1</v>
       </c>
-      <c r="D31" s="115">
+      <c r="D31" s="9">
         <f>82/12/3.281</f>
         <v>2.0826983643198211</v>
       </c>
-      <c r="E31" s="115">
+      <c r="E31" s="9">
         <v>2.2599999999999998</v>
       </c>
-      <c r="F31" s="115">
+      <c r="F31" s="9">
         <f t="shared" si="0"/>
         <v>4.7068983033627951</v>
       </c>
-      <c r="G31" s="115">
+      <c r="G31" s="9">
         <f t="shared" si="1"/>
         <v>4.7068983033627951</v>
       </c>
-      <c r="H31" s="110"/>
-      <c r="I31" s="110"/>
-      <c r="J31" s="110"/>
-      <c r="K31" s="116"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="42"/>
+      <c r="K31" s="27"/>
     </row>
     <row r="32" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="105"/>
-      <c r="B32" s="113" t="s">
+      <c r="A32" s="2"/>
+      <c r="B32" s="43" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="107"/>
+      <c r="C32" s="3"/>
       <c r="D32" s="4"/>
-      <c r="E32" s="111"/>
-      <c r="F32" s="111"/>
-      <c r="G32" s="110">
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="42">
         <f>SUM(G10:G31)</f>
         <v>880.06056639235987</v>
       </c>
-      <c r="H32" s="109" t="s">
+      <c r="H32" s="7" t="s">
         <v>40</v>
       </c>
       <c r="I32" s="6">
         <v>182.51</v>
       </c>
-      <c r="J32" s="110">
+      <c r="J32" s="42">
         <f>G32*I32</f>
         <v>160619.8539722696</v>
       </c>
-      <c r="K32" s="111"/>
+      <c r="K32" s="5"/>
     </row>
     <row r="33" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="105"/>
-      <c r="B33" s="113" t="s">
+      <c r="A33" s="2"/>
+      <c r="B33" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="107"/>
+      <c r="C33" s="3"/>
       <c r="D33" s="4"/>
-      <c r="E33" s="111"/>
-      <c r="F33" s="111"/>
-      <c r="G33" s="110"/>
-      <c r="H33" s="109"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="7"/>
       <c r="I33" s="6"/>
-      <c r="J33" s="110">
+      <c r="J33" s="42">
         <f>0.13*G32*(1871.42/18.94)</f>
         <v>11304.391915023165</v>
       </c>
-      <c r="K33" s="111"/>
+      <c r="K33" s="5"/>
     </row>
     <row r="34" spans="1:11" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
@@ -9226,7 +11734,7 @@
       <c r="J63" s="18"/>
       <c r="K63" s="17"/>
     </row>
-    <row r="64" spans="1:11" ht="78.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:11" ht="94.5" x14ac:dyDescent="0.25">
       <c r="A64" s="16">
         <v>5</v>
       </c>
@@ -10161,11 +12669,11 @@
       <c r="B106" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C106" s="71">
+      <c r="C106" s="70">
         <f>J104</f>
         <v>805286.81389120058</v>
       </c>
-      <c r="D106" s="72"/>
+      <c r="D106" s="71"/>
       <c r="E106" s="9">
         <v>100</v>
       </c>
@@ -10187,21 +12695,21 @@
       <c r="B107" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C107" s="75">
+      <c r="C107" s="74">
         <v>700000</v>
       </c>
-      <c r="D107" s="76"/>
+      <c r="D107" s="75"/>
       <c r="E107" s="9"/>
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.25">
       <c r="B108" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="C108" s="75">
+      <c r="C108" s="74">
         <f>C107-C110-C111</f>
         <v>665000</v>
       </c>
-      <c r="D108" s="76"/>
+      <c r="D108" s="75"/>
       <c r="E108" s="9">
         <f>C108/C106*100</f>
         <v>82.579273437581179</v>
@@ -10211,11 +12719,11 @@
       <c r="B109" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C109" s="77">
+      <c r="C109" s="76">
         <f>C106-C108</f>
         <v>140286.81389120058</v>
       </c>
-      <c r="D109" s="77"/>
+      <c r="D109" s="76"/>
       <c r="E109" s="9">
         <f>100-E108</f>
         <v>17.420726562418821</v>
@@ -10225,11 +12733,11 @@
       <c r="B110" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C110" s="71">
+      <c r="C110" s="70">
         <f>C107*0.03</f>
         <v>21000</v>
       </c>
-      <c r="D110" s="72"/>
+      <c r="D110" s="71"/>
       <c r="E110" s="9">
         <v>3</v>
       </c>
@@ -10238,17 +12746,24 @@
       <c r="B111" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="C111" s="71">
+      <c r="C111" s="70">
         <f>C107*0.02</f>
         <v>14000</v>
       </c>
-      <c r="D111" s="72"/>
+      <c r="D111" s="71"/>
       <c r="E111" s="9">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C110:D110"/>
     <mergeCell ref="C111:D111"/>
     <mergeCell ref="A7:F7"/>
@@ -10257,13 +12772,6 @@
     <mergeCell ref="C107:D107"/>
     <mergeCell ref="C108:D108"/>
     <mergeCell ref="C109:D109"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
